--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5877C5CC-9D5A-854C-B017-94E76F180BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BEBF3-B826-2B4C-BD56-CDD892AA7009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="760" windowWidth="27700" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1700" yWindow="1320" windowWidth="27700" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -16956,7 +16956,7 @@
       <c r="H135" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="I135" s="4" t="s">
+      <c r="I135" s="234" t="s">
         <v>691</v>
       </c>
       <c r="J135" s="1" t="s">

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BEBF3-B826-2B4C-BD56-CDD892AA7009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A4215-9231-8F4E-8D55-735F1D4ABE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="1320" windowWidth="27700" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36023,24 +36023,26 @@
       <c r="X560" s="1"/>
       <c r="Y560" s="1"/>
     </row>
-    <row r="561" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="562" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="563" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="564" spans="9:9" ht="15.75" customHeight="1">
+    <row r="561" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A561" s="2"/>
+    </row>
+    <row r="562" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="563" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="564" spans="1:9" ht="15.75" customHeight="1">
       <c r="I564" s="223"/>
     </row>
-    <row r="565" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="566" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="567" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="568" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="569" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="570" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="571" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="572" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="573" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="574" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="575" spans="9:9" ht="15.75" customHeight="1"/>
-    <row r="576" spans="9:9" ht="15.75" customHeight="1"/>
+    <row r="565" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="566" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="567" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="568" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="569" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="570" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="571" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="572" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="573" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="574" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="575" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="576" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="577" ht="15.75" customHeight="1"/>
     <row r="578" ht="15.75" customHeight="1"/>
     <row r="579" ht="15.75" customHeight="1"/>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/GitHub/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A4215-9231-8F4E-8D55-735F1D4ABE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BD2BA4-3428-FF42-8418-25660561DF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3993" uniqueCount="2995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3993" uniqueCount="2996">
   <si>
     <t>Nachname</t>
   </si>
@@ -9169,6 +9169,9 @@
   </si>
   <si>
     <t xml:space="preserve">ZephyrescuPauline </t>
+  </si>
+  <si>
+    <t>Wilhelm II. Franz</t>
   </si>
 </sst>
 </file>
@@ -21289,7 +21292,7 @@
         <v>454</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1152</v>
+        <v>2995</v>
       </c>
       <c r="D233" s="1">
         <v>1859</v>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4030B0-89D1-0B49-AB5B-01BC2023D5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3AC494-8727-B644-9193-36E505F70F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="7660" windowWidth="29300" windowHeight="9600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -13965,7 +13965,7 @@
       <c r="H31" s="237" t="s">
         <v>3005</v>
       </c>
-      <c r="I31" s="204" t="s">
+      <c r="I31" s="262" t="s">
         <v>3006</v>
       </c>
       <c r="J31" s="320" t="s">
@@ -14403,7 +14403,7 @@
       <c r="X41" s="36"/>
       <c r="Y41" s="36"/>
     </row>
-    <row r="42" spans="1:25" ht="128">
+    <row r="42" spans="1:25" ht="112">
       <c r="A42" s="24" t="s">
         <v>197</v>
       </c>
@@ -14690,7 +14690,7 @@
       <c r="H48" s="170" t="s">
         <v>3010</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="154" t="s">
         <v>3011</v>
       </c>
       <c r="J48" t="s">
@@ -15028,7 +15028,7 @@
       <c r="H56" s="170" t="s">
         <v>3015</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="16" t="s">
         <v>3016</v>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
       <c r="X64" s="26"/>
       <c r="Y64" s="26"/>
     </row>
-    <row r="65" spans="1:25" ht="176">
+    <row r="65" spans="1:25" ht="160">
       <c r="A65" s="26" t="s">
         <v>317</v>
       </c>
@@ -41910,11 +41910,13 @@
     <hyperlink ref="I607" r:id="rId352" tooltip="https://d-nb.info/gnd/124988474" xr:uid="{401D3009-0210-9848-9CCB-0E3F514B9049}"/>
     <hyperlink ref="I625" r:id="rId353" tooltip="https://d-nb.info/gnd/1161676309" xr:uid="{B504558A-7E8A-6541-BD89-24216F1563A3}"/>
     <hyperlink ref="I483" r:id="rId354" tooltip="https://d-nb.info/gnd/1027648614" xr:uid="{221A4C73-7808-AC48-BF73-3828D29E4245}"/>
+    <hyperlink ref="I31" r:id="rId355" xr:uid="{5DEF1CC6-62D4-F048-AC18-7C085AB5C8B9}"/>
+    <hyperlink ref="I48" r:id="rId356" xr:uid="{DA33FA54-A209-634C-9E1B-0335CEA4F7F6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId355"/>
+    <tablePart r:id="rId357"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B522DD6B-B3EE-CF41-9CF4-5D137C1F86E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42CF728-526C-F742-84F3-46147654B7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="100" yWindow="9440" windowWidth="29300" windowHeight="7820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="3539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="3542">
   <si>
     <t>Nachname</t>
   </si>
@@ -10761,12 +10761,6 @@
     <t>EhrhardAlbert</t>
   </si>
   <si>
-    <t>Fries</t>
-  </si>
-  <si>
-    <t>Neffe von Baernreither</t>
-  </si>
-  <si>
     <t>GruntzelJosef</t>
   </si>
   <si>
@@ -10801,6 +10795,21 @@
   </si>
   <si>
     <t>ZephyrescuPauline</t>
+  </si>
+  <si>
+    <t>Fries-Skene</t>
+  </si>
+  <si>
+    <t>Budua/Budva</t>
+  </si>
+  <si>
+    <t>Beamter im MCU und Ministerium des Innern, 1909 Sektionschef im Innenmin., 1912 Landespräsident in Kärnten, 1915 Statthalter in Triest und Küstenland</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/144034190</t>
+  </si>
+  <si>
+    <t>FriesSkeneAlfred</t>
   </si>
 </sst>
 </file>
@@ -11626,7 +11635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -12389,10 +12398,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -20434,20 +20439,34 @@
     </row>
     <row r="185" spans="1:25" ht="15.75" customHeight="1">
       <c r="A185" s="26" t="s">
-        <v>3525</v>
-      </c>
-      <c r="B185" s="26"/>
-      <c r="C185" s="26"/>
-      <c r="D185" s="26"/>
-      <c r="E185" s="26"/>
-      <c r="F185" s="26"/>
-      <c r="G185" s="52"/>
+        <v>3537</v>
+      </c>
+      <c r="B185" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="C185" s="26" t="s">
+        <v>746</v>
+      </c>
+      <c r="D185" s="26">
+        <v>1870</v>
+      </c>
+      <c r="E185" s="26">
+        <v>1947</v>
+      </c>
+      <c r="F185" s="26" t="s">
+        <v>3538</v>
+      </c>
+      <c r="G185" s="52" t="s">
+        <v>20</v>
+      </c>
       <c r="H185" s="27" t="s">
-        <v>3526</v>
-      </c>
-      <c r="I185" s="48"/>
+        <v>3539</v>
+      </c>
+      <c r="I185" s="154" t="s">
+        <v>3540</v>
+      </c>
       <c r="J185" s="26" t="s">
-        <v>3525</v>
+        <v>3541</v>
       </c>
       <c r="K185" s="9"/>
       <c r="L185" s="9"/>
@@ -22029,7 +22048,7 @@
         <v>3154</v>
       </c>
       <c r="J223" s="16" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="224" spans="1:25" ht="15.75" customHeight="1">
@@ -24210,33 +24229,33 @@
       <c r="Y272" s="1"/>
     </row>
     <row r="273" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A273" s="346" t="s">
+      <c r="A273" s="1" t="s">
+        <v>3526</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D273" s="1">
+        <v>1851</v>
+      </c>
+      <c r="E273" s="1">
+        <v>1929</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>2485</v>
+      </c>
+      <c r="H273" s="1" t="s">
+        <v>3527</v>
+      </c>
+      <c r="I273" s="16"/>
+      <c r="J273" s="1" t="s">
         <v>3528</v>
-      </c>
-      <c r="B273" s="346" t="s">
-        <v>26</v>
-      </c>
-      <c r="C273" s="346" t="s">
-        <v>161</v>
-      </c>
-      <c r="D273" s="346">
-        <v>1851</v>
-      </c>
-      <c r="E273" s="346">
-        <v>1929</v>
-      </c>
-      <c r="F273" s="346" t="s">
-        <v>20</v>
-      </c>
-      <c r="G273" s="346" t="s">
-        <v>2485</v>
-      </c>
-      <c r="H273" s="346" t="s">
-        <v>3529</v>
-      </c>
-      <c r="I273" s="347"/>
-      <c r="J273" s="346" t="s">
-        <v>3530</v>
       </c>
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
@@ -24640,7 +24659,7 @@
         <v>2904</v>
       </c>
       <c r="J283" s="185" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
       <c r="K283" s="161"/>
       <c r="L283" s="161"/>
@@ -26557,7 +26576,7 @@
         <v>1506</v>
       </c>
       <c r="I327" s="154" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>1507</v>
@@ -31006,13 +31025,13 @@
     </row>
     <row r="430" spans="1:25" ht="15" customHeight="1">
       <c r="A430" s="16" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="C430" s="16" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="J430" s="16" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="431" spans="1:25" ht="15.75" customHeight="1">
@@ -32390,7 +32409,7 @@
         <v>2069</v>
       </c>
       <c r="I465" s="154" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="J465" s="71" t="s">
         <v>2070</v>
@@ -33010,7 +33029,7 @@
       <c r="I479" s="204" t="s">
         <v>3337</v>
       </c>
-      <c r="J479" s="348" t="s">
+      <c r="J479" s="346" t="s">
         <v>3338</v>
       </c>
     </row>
@@ -35243,7 +35262,7 @@
       <c r="I533" s="154" t="s">
         <v>3391</v>
       </c>
-      <c r="J533" s="349" t="s">
+      <c r="J533" s="347" t="s">
         <v>3392</v>
       </c>
     </row>
@@ -36195,7 +36214,7 @@
       <c r="I555" t="s">
         <v>3407</v>
       </c>
-      <c r="J555" s="350" t="s">
+      <c r="J555" s="348" t="s">
         <v>3408</v>
       </c>
       <c r="Z555" s="57"/>
@@ -36526,7 +36545,7 @@
         <v>3416</v>
       </c>
       <c r="J563" s="231" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="564" spans="1:25" ht="15.75" customHeight="1">
@@ -38988,7 +39007,7 @@
         <v>2704</v>
       </c>
       <c r="J622" s="144" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="K622" s="145"/>
       <c r="L622" s="145"/>
@@ -40485,7 +40504,7 @@
       </c>
       <c r="I658" s="166"/>
       <c r="J658" s="164" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="K658" s="1"/>
       <c r="L658" s="1"/>
@@ -42122,11 +42141,12 @@
     <hyperlink ref="I158" r:id="rId356" xr:uid="{5BDA1D26-72C0-F144-949E-A62C8D84D14F}"/>
     <hyperlink ref="I465" r:id="rId357" xr:uid="{7D729A8D-F8B8-884F-BFCE-643B2BC7B3CB}"/>
     <hyperlink ref="I528" r:id="rId358" xr:uid="{23C2DC74-04BE-3E4D-B068-65E1C7610998}"/>
+    <hyperlink ref="I185" r:id="rId359" xr:uid="{4B785CC9-4F46-1147-8FDC-32D3603D13FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId359"/>
+    <tablePart r:id="rId360"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233850D1-FCF2-5247-925D-07B695054731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F021BD20-23FF-AE4B-91B0-6230748FE255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -11950,9 +11950,6 @@
     <t>https://d-nb.info/gnd/118920537</t>
   </si>
   <si>
-    <t>PfueglEmmerich</t>
-  </si>
-  <si>
     <t>Pipef</t>
   </si>
   <si>
@@ -12500,6 +12497,9 @@
   </si>
   <si>
     <t>FuerstenbergEgonEmil</t>
+  </si>
+  <si>
+    <t>PflueglEmmerich</t>
   </si>
 </sst>
 </file>
@@ -16305,7 +16305,7 @@
       <c r="X47" s="34"/>
       <c r="Y47" s="34"/>
     </row>
-    <row r="48" spans="1:25" ht="128">
+    <row r="48" spans="1:25" ht="112">
       <c r="A48" s="23" t="s">
         <v>197</v>
       </c>
@@ -17243,7 +17243,7 @@
       <c r="X70" s="25"/>
       <c r="Y70" s="25"/>
     </row>
-    <row r="71" spans="1:25" ht="176">
+    <row r="71" spans="1:25" ht="160">
       <c r="A71" s="5" t="s">
         <v>317</v>
       </c>
@@ -18777,16 +18777,16 @@
         <v>20</v>
       </c>
       <c r="G107" s="25" t="s">
+        <v>4094</v>
+      </c>
+      <c r="H107" s="26" t="s">
         <v>4095</v>
       </c>
-      <c r="H107" s="26" t="s">
+      <c r="I107" s="138" t="s">
         <v>4096</v>
       </c>
-      <c r="I107" s="138" t="s">
+      <c r="J107" s="25" t="s">
         <v>4097</v>
-      </c>
-      <c r="J107" s="25" t="s">
-        <v>4098</v>
       </c>
       <c r="K107" s="9"/>
       <c r="L107" s="9"/>
@@ -19391,7 +19391,7 @@
       <c r="H121" t="s">
         <v>3624</v>
       </c>
-      <c r="I121" t="s">
+      <c r="I121" s="138" t="s">
         <v>3625</v>
       </c>
       <c r="J121" t="s">
@@ -19678,7 +19678,7 @@
       <c r="I128" t="s">
         <v>3619</v>
       </c>
-      <c r="J128" t="s">
+      <c r="J128" s="15" t="s">
         <v>3620</v>
       </c>
     </row>
@@ -22888,7 +22888,7 @@
         <v>881</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="D209">
         <v>1876</v>
@@ -22900,10 +22900,10 @@
         <v>20</v>
       </c>
       <c r="H209" s="259" t="s">
+        <v>4099</v>
+      </c>
+      <c r="J209" s="15" t="s">
         <v>4100</v>
-      </c>
-      <c r="J209" s="15" t="s">
-        <v>4101</v>
       </c>
     </row>
     <row r="210" spans="1:25" ht="15.75" customHeight="1">
@@ -27706,7 +27706,7 @@
       <c r="I325" s="138" t="s">
         <v>3730</v>
       </c>
-      <c r="J325" s="177" t="s">
+      <c r="J325" s="194" t="s">
         <v>3731</v>
       </c>
     </row>
@@ -27725,7 +27725,7 @@
       <c r="H326" s="177" t="s">
         <v>3732</v>
       </c>
-      <c r="J326" s="177" t="s">
+      <c r="J326" s="194" t="s">
         <v>3733</v>
       </c>
     </row>
@@ -28049,7 +28049,7 @@
       <c r="F335" s="177"/>
       <c r="G335" s="177"/>
       <c r="H335" s="177"/>
-      <c r="J335" s="177" t="s">
+      <c r="J335" s="194" t="s">
         <v>3748</v>
       </c>
     </row>
@@ -28450,7 +28450,7 @@
       <c r="I345" t="s">
         <v>3592</v>
       </c>
-      <c r="J345" t="s">
+      <c r="J345" s="15" t="s">
         <v>3593</v>
       </c>
     </row>
@@ -28468,19 +28468,19 @@
         <v>1972</v>
       </c>
       <c r="F346" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="G346" t="s">
         <v>3180</v>
       </c>
       <c r="H346" t="s">
+        <v>3926</v>
+      </c>
+      <c r="I346" t="s">
         <v>3927</v>
       </c>
-      <c r="I346" t="s">
+      <c r="J346" t="s">
         <v>3928</v>
-      </c>
-      <c r="J346" t="s">
-        <v>3929</v>
       </c>
     </row>
     <row r="347" spans="1:25" ht="15.75" customHeight="1">
@@ -33039,7 +33039,7 @@
       <c r="I454" s="138" t="s">
         <v>3254</v>
       </c>
-      <c r="J454" s="177" t="s">
+      <c r="J454" s="194" t="s">
         <v>3255</v>
       </c>
     </row>
@@ -34018,7 +34018,7 @@
       <c r="I478" t="s">
         <v>3832</v>
       </c>
-      <c r="J478" s="177" t="s">
+      <c r="J478" s="194" t="s">
         <v>3833</v>
       </c>
     </row>
@@ -34740,7 +34740,7 @@
       <c r="I499" t="s">
         <v>3820</v>
       </c>
-      <c r="J499" s="177" t="s">
+      <c r="J499" s="194" t="s">
         <v>3821</v>
       </c>
     </row>
@@ -34751,7 +34751,7 @@
       <c r="H500" t="s">
         <v>3822</v>
       </c>
-      <c r="J500" t="s">
+      <c r="J500" s="15" t="s">
         <v>3823</v>
       </c>
     </row>
@@ -35839,8 +35839,8 @@
       <c r="I530" t="s">
         <v>3917</v>
       </c>
-      <c r="J530" s="177" t="s">
-        <v>3918</v>
+      <c r="J530" s="194" t="s">
+        <v>4101</v>
       </c>
     </row>
     <row r="531" spans="1:25" ht="15.75" customHeight="1">
@@ -36021,7 +36021,7 @@
     </row>
     <row r="535" spans="1:25" ht="15.75" customHeight="1">
       <c r="A535" s="162" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B535" s="179"/>
       <c r="C535" s="179"/>
@@ -36030,10 +36030,10 @@
       <c r="F535" s="179"/>
       <c r="G535" s="179"/>
       <c r="H535" s="179" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="J535" s="179" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="536" spans="1:25" ht="15.75" customHeight="1">
@@ -36375,7 +36375,7 @@
     </row>
     <row r="544" spans="1:25" ht="15.75" customHeight="1">
       <c r="A544" s="159" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B544" s="177"/>
       <c r="C544" s="177" t="s">
@@ -36388,19 +36388,19 @@
         <v>1933</v>
       </c>
       <c r="F544" s="177" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="G544" s="177" t="s">
         <v>2483</v>
       </c>
       <c r="H544" s="177" t="s">
+        <v>3922</v>
+      </c>
+      <c r="I544" t="s">
         <v>3923</v>
       </c>
-      <c r="I544" t="s">
+      <c r="J544" s="336" t="s">
         <v>3924</v>
-      </c>
-      <c r="J544" s="336" t="s">
-        <v>3925</v>
       </c>
     </row>
     <row r="545" spans="1:25" ht="15.75" customHeight="1">
@@ -36634,7 +36634,7 @@
     </row>
     <row r="550" spans="1:25" ht="15.75" customHeight="1">
       <c r="A550" s="165" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B550" s="181"/>
       <c r="C550" s="181" t="s">
@@ -36647,17 +36647,17 @@
         <v>1945</v>
       </c>
       <c r="F550" s="181" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="G550" s="181"/>
       <c r="H550" s="181" t="s">
+        <v>3931</v>
+      </c>
+      <c r="I550" s="175" t="s">
         <v>3932</v>
       </c>
-      <c r="I550" s="175" t="s">
+      <c r="J550" s="242" t="s">
         <v>3933</v>
-      </c>
-      <c r="J550" s="242" t="s">
-        <v>3934</v>
       </c>
     </row>
     <row r="551" spans="1:25" ht="15.75" customHeight="1">
@@ -36838,7 +36838,7 @@
     </row>
     <row r="555" spans="1:25" ht="15.75" customHeight="1">
       <c r="A555" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="C555" t="s">
         <v>3605</v>
@@ -36850,24 +36850,24 @@
         <v>1956</v>
       </c>
       <c r="F555" t="s">
+        <v>3935</v>
+      </c>
+      <c r="H555" t="s">
         <v>3936</v>
       </c>
-      <c r="H555" t="s">
+      <c r="I555" t="s">
         <v>3937</v>
       </c>
-      <c r="I555" t="s">
+      <c r="J555" t="s">
         <v>3938</v>
-      </c>
-      <c r="J555" t="s">
-        <v>3939</v>
       </c>
     </row>
     <row r="556" spans="1:25" ht="15.75" customHeight="1">
       <c r="A556" t="s">
+        <v>3939</v>
+      </c>
+      <c r="B556" t="s">
         <v>3940</v>
-      </c>
-      <c r="B556" t="s">
-        <v>3941</v>
       </c>
       <c r="C556" t="s">
         <v>1050</v>
@@ -36879,10 +36879,10 @@
         <v>1873</v>
       </c>
       <c r="H556" t="s">
+        <v>3941</v>
+      </c>
+      <c r="J556" s="15" t="s">
         <v>3942</v>
-      </c>
-      <c r="J556" t="s">
-        <v>3943</v>
       </c>
     </row>
     <row r="557" spans="1:25" ht="15.75" customHeight="1">
@@ -37710,10 +37710,10 @@
     </row>
     <row r="577" spans="1:25" ht="15.75" customHeight="1">
       <c r="A577" t="s">
+        <v>3943</v>
+      </c>
+      <c r="C577" t="s">
         <v>3944</v>
-      </c>
-      <c r="C577" t="s">
-        <v>3945</v>
       </c>
       <c r="D577">
         <v>1859</v>
@@ -37722,16 +37722,16 @@
         <v>1930</v>
       </c>
       <c r="F577" t="s">
+        <v>3945</v>
+      </c>
+      <c r="H577" t="s">
         <v>3946</v>
       </c>
-      <c r="H577" t="s">
+      <c r="I577" t="s">
         <v>3947</v>
       </c>
-      <c r="I577" t="s">
+      <c r="J577" t="s">
         <v>3948</v>
-      </c>
-      <c r="J577" t="s">
-        <v>3949</v>
       </c>
     </row>
     <row r="578" spans="1:25" ht="15.75" customHeight="1">
@@ -38248,10 +38248,10 @@
     </row>
     <row r="592" spans="1:25" ht="15.75" customHeight="1">
       <c r="A592" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B592" t="s">
         <v>3950</v>
-      </c>
-      <c r="B592" t="s">
-        <v>3951</v>
       </c>
       <c r="C592" t="s">
         <v>1144</v>
@@ -38266,13 +38266,13 @@
         <v>683</v>
       </c>
       <c r="G592" t="s">
+        <v>3951</v>
+      </c>
+      <c r="H592" t="s">
         <v>3952</v>
       </c>
-      <c r="H592" t="s">
+      <c r="J592" s="15" t="s">
         <v>3953</v>
-      </c>
-      <c r="J592" t="s">
-        <v>3954</v>
       </c>
     </row>
     <row r="593" spans="1:25" ht="15.75" customHeight="1">
@@ -38825,7 +38825,7 @@
     </row>
     <row r="606" spans="1:25" ht="15.75" customHeight="1">
       <c r="A606" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="C606" t="s">
         <v>1843</v>
@@ -38834,13 +38834,13 @@
         <v>1875</v>
       </c>
       <c r="H606" t="s">
+        <v>3955</v>
+      </c>
+      <c r="I606" t="s">
         <v>3956</v>
       </c>
-      <c r="I606" t="s">
+      <c r="J606" t="s">
         <v>3957</v>
-      </c>
-      <c r="J606" t="s">
-        <v>3958</v>
       </c>
     </row>
     <row r="607" spans="1:25" ht="15.75" customHeight="1">
@@ -39847,10 +39847,10 @@
     </row>
     <row r="631" spans="1:25" ht="15.75" customHeight="1">
       <c r="A631" t="s">
+        <v>3958</v>
+      </c>
+      <c r="C631" t="s">
         <v>3959</v>
-      </c>
-      <c r="C631" t="s">
-        <v>3960</v>
       </c>
       <c r="D631">
         <v>1875</v>
@@ -39865,18 +39865,18 @@
         <v>20</v>
       </c>
       <c r="H631" t="s">
+        <v>3960</v>
+      </c>
+      <c r="I631" t="s">
         <v>3961</v>
       </c>
-      <c r="I631" t="s">
+      <c r="J631" t="s">
         <v>3962</v>
-      </c>
-      <c r="J631" t="s">
-        <v>3963</v>
       </c>
     </row>
     <row r="632" spans="1:25" ht="15.75" customHeight="1">
       <c r="A632" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="C632" t="s">
         <v>925</v>
@@ -39888,13 +39888,13 @@
         <v>1933</v>
       </c>
       <c r="H632" t="s">
+        <v>3964</v>
+      </c>
+      <c r="I632" t="s">
         <v>3965</v>
       </c>
-      <c r="I632" t="s">
+      <c r="J632" t="s">
         <v>3966</v>
-      </c>
-      <c r="J632" t="s">
-        <v>3967</v>
       </c>
     </row>
     <row r="633" spans="1:25" ht="15.75" customHeight="1">
@@ -40099,7 +40099,7 @@
         <v>2383</v>
       </c>
       <c r="C638" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="D638">
         <v>1867</v>
@@ -40114,13 +40114,13 @@
         <v>304</v>
       </c>
       <c r="H638" t="s">
+        <v>3968</v>
+      </c>
+      <c r="I638" t="s">
         <v>3969</v>
       </c>
-      <c r="I638" t="s">
+      <c r="J638" t="s">
         <v>3970</v>
-      </c>
-      <c r="J638" t="s">
-        <v>3971</v>
       </c>
     </row>
     <row r="639" spans="1:25" ht="15.75" customHeight="1">
@@ -40137,13 +40137,13 @@
         <v>1917</v>
       </c>
       <c r="F639" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="G639" t="s">
         <v>20</v>
       </c>
       <c r="H639" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="I639" s="138" t="s">
         <v>2386</v>
@@ -40154,13 +40154,13 @@
     </row>
     <row r="640" spans="1:25" ht="15.75" customHeight="1">
       <c r="A640" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B640" t="s">
         <v>18</v>
       </c>
       <c r="C640" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="D640">
         <v>1873</v>
@@ -40175,10 +40175,10 @@
         <v>20</v>
       </c>
       <c r="H640" t="s">
+        <v>3975</v>
+      </c>
+      <c r="J640" t="s">
         <v>3976</v>
-      </c>
-      <c r="J640" t="s">
-        <v>3977</v>
       </c>
     </row>
     <row r="641" spans="1:25" ht="15.75" customHeight="1">
@@ -40277,7 +40277,7 @@
     </row>
     <row r="643" spans="1:25" ht="15.75" customHeight="1">
       <c r="A643" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="C643" t="s">
         <v>3605</v>
@@ -40295,13 +40295,13 @@
         <v>3180</v>
       </c>
       <c r="H643" t="s">
+        <v>3978</v>
+      </c>
+      <c r="I643" t="s">
         <v>3979</v>
       </c>
-      <c r="I643" t="s">
+      <c r="J643" t="s">
         <v>3980</v>
-      </c>
-      <c r="J643" t="s">
-        <v>3981</v>
       </c>
     </row>
     <row r="644" spans="1:25" ht="15.75" customHeight="1">
@@ -40398,7 +40398,7 @@
     </row>
     <row r="646" spans="1:25" ht="15.75" customHeight="1">
       <c r="A646" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="C646" t="s">
         <v>3412</v>
@@ -40410,19 +40410,19 @@
         <v>1956</v>
       </c>
       <c r="F646" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="G646" t="s">
         <v>2542</v>
       </c>
       <c r="H646" t="s">
+        <v>3983</v>
+      </c>
+      <c r="I646" t="s">
         <v>3984</v>
       </c>
-      <c r="I646" t="s">
+      <c r="J646" t="s">
         <v>3985</v>
-      </c>
-      <c r="J646" t="s">
-        <v>3986</v>
       </c>
     </row>
     <row r="647" spans="1:25" ht="15.75" customHeight="1">
@@ -40839,10 +40839,10 @@
     </row>
     <row r="658" spans="1:25" ht="15.75" customHeight="1">
       <c r="A658" t="s">
+        <v>3986</v>
+      </c>
+      <c r="C658" t="s">
         <v>3987</v>
-      </c>
-      <c r="C658" t="s">
-        <v>3988</v>
       </c>
       <c r="D658">
         <v>1874</v>
@@ -40857,24 +40857,24 @@
         <v>20</v>
       </c>
       <c r="H658" t="s">
+        <v>3988</v>
+      </c>
+      <c r="I658" s="138" t="s">
         <v>3989</v>
       </c>
-      <c r="I658" s="138" t="s">
+      <c r="J658" t="s">
         <v>3990</v>
-      </c>
-      <c r="J658" t="s">
-        <v>3991</v>
       </c>
     </row>
     <row r="659" spans="1:25" ht="15.75" customHeight="1">
       <c r="A659" t="s">
+        <v>3991</v>
+      </c>
+      <c r="H659" t="s">
         <v>3992</v>
       </c>
-      <c r="H659" t="s">
-        <v>3993</v>
-      </c>
       <c r="J659" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="660" spans="1:25" ht="15.75" customHeight="1">
@@ -41262,10 +41262,10 @@
     </row>
     <row r="669" spans="1:25" ht="15.75" customHeight="1">
       <c r="A669" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C669" t="s">
         <v>3994</v>
-      </c>
-      <c r="C669" t="s">
-        <v>3995</v>
       </c>
       <c r="D669">
         <v>1873</v>
@@ -41274,13 +41274,13 @@
         <v>1933</v>
       </c>
       <c r="F669" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
       </c>
       <c r="J669" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="670" spans="1:25" ht="15.75" customHeight="1">
@@ -41379,10 +41379,10 @@
     </row>
     <row r="672" spans="1:25" ht="15.75" customHeight="1">
       <c r="A672" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C672" t="s">
         <v>3998</v>
-      </c>
-      <c r="C672" t="s">
-        <v>3999</v>
       </c>
       <c r="D672">
         <v>1867</v>
@@ -41397,18 +41397,18 @@
         <v>3180</v>
       </c>
       <c r="H672" t="s">
+        <v>3999</v>
+      </c>
+      <c r="I672" t="s">
         <v>4000</v>
       </c>
-      <c r="I672" t="s">
+      <c r="J672" t="s">
         <v>4001</v>
-      </c>
-      <c r="J672" t="s">
-        <v>4002</v>
       </c>
     </row>
     <row r="673" spans="1:25" ht="15.75" customHeight="1">
       <c r="A673" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="C673" t="s">
         <v>3734</v>
@@ -41420,19 +41420,19 @@
         <v>1930</v>
       </c>
       <c r="F673" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="G673" t="s">
         <v>3180</v>
       </c>
       <c r="H673" t="s">
+        <v>4003</v>
+      </c>
+      <c r="I673" t="s">
         <v>4004</v>
       </c>
-      <c r="I673" t="s">
+      <c r="J673" t="s">
         <v>4005</v>
-      </c>
-      <c r="J673" t="s">
-        <v>4006</v>
       </c>
     </row>
     <row r="674" spans="1:25" ht="15.75" customHeight="1">
@@ -41746,7 +41746,7 @@
     </row>
     <row r="681" spans="1:25" ht="15.75" customHeight="1">
       <c r="A681" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="B681" t="s">
         <v>653</v>
@@ -41767,13 +41767,13 @@
         <v>20</v>
       </c>
       <c r="H681" t="s">
+        <v>4007</v>
+      </c>
+      <c r="I681" t="s">
         <v>4008</v>
       </c>
-      <c r="I681" t="s">
+      <c r="J681" t="s">
         <v>4009</v>
-      </c>
-      <c r="J681" t="s">
-        <v>4010</v>
       </c>
     </row>
     <row r="682" spans="1:25" ht="15.75" customHeight="1">
@@ -42191,13 +42191,13 @@
     </row>
     <row r="693" spans="1:25" ht="15.75" customHeight="1">
       <c r="A693" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="B693" t="s">
         <v>18</v>
       </c>
       <c r="C693" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="D693">
         <v>1857</v>
@@ -42206,19 +42206,19 @@
         <v>1926</v>
       </c>
       <c r="F693" t="s">
+        <v>4012</v>
+      </c>
+      <c r="G693" t="s">
         <v>4013</v>
       </c>
-      <c r="G693" t="s">
+      <c r="H693" t="s">
         <v>4014</v>
       </c>
-      <c r="H693" t="s">
+      <c r="I693" t="s">
         <v>4015</v>
       </c>
-      <c r="I693" t="s">
+      <c r="J693" t="s">
         <v>4016</v>
-      </c>
-      <c r="J693" t="s">
-        <v>4017</v>
       </c>
     </row>
     <row r="694" spans="1:25" ht="15.75" customHeight="1">
@@ -42653,7 +42653,7 @@
       <c r="H703" s="10" t="s">
         <v>3546</v>
       </c>
-      <c r="I703" s="11" t="s">
+      <c r="I703" s="256" t="s">
         <v>3547</v>
       </c>
       <c r="J703" s="10" t="s">
@@ -42767,7 +42767,7 @@
     </row>
     <row r="706" spans="1:25" ht="15.75" customHeight="1">
       <c r="A706" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B706" t="s">
         <v>479</v>
@@ -42785,13 +42785,13 @@
         <v>556</v>
       </c>
       <c r="H706" t="s">
+        <v>4018</v>
+      </c>
+      <c r="I706" t="s">
         <v>4019</v>
       </c>
-      <c r="I706" t="s">
+      <c r="J706" t="s">
         <v>4020</v>
-      </c>
-      <c r="J706" t="s">
-        <v>4021</v>
       </c>
     </row>
     <row r="707" spans="1:25" ht="15.75" customHeight="1">
@@ -42937,10 +42937,10 @@
     </row>
     <row r="710" spans="1:25" ht="15.75" customHeight="1">
       <c r="A710" t="s">
+        <v>4021</v>
+      </c>
+      <c r="C710" t="s">
         <v>4022</v>
-      </c>
-      <c r="C710" t="s">
-        <v>4023</v>
       </c>
       <c r="D710">
         <v>1864</v>
@@ -42952,16 +42952,16 @@
         <v>122</v>
       </c>
       <c r="G710" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H710" t="s">
         <v>4024</v>
       </c>
-      <c r="H710" t="s">
+      <c r="I710" t="s">
         <v>4025</v>
       </c>
-      <c r="I710" t="s">
+      <c r="J710" t="s">
         <v>4026</v>
-      </c>
-      <c r="J710" t="s">
-        <v>4027</v>
       </c>
     </row>
     <row r="711" spans="1:25" ht="15.75" customHeight="1">
@@ -43215,7 +43215,7 @@
     </row>
     <row r="717" spans="1:25" ht="15.75" customHeight="1">
       <c r="A717" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="C717" t="s">
         <v>3605</v>
@@ -43227,19 +43227,19 @@
         <v>1932</v>
       </c>
       <c r="F717" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="G717" t="s">
         <v>3180</v>
       </c>
       <c r="H717" t="s">
+        <v>4029</v>
+      </c>
+      <c r="I717" t="s">
         <v>4030</v>
       </c>
-      <c r="I717" t="s">
+      <c r="J717" t="s">
         <v>4031</v>
-      </c>
-      <c r="J717" t="s">
-        <v>4032</v>
       </c>
     </row>
     <row r="718" spans="1:25" ht="15.75" customHeight="1">
@@ -43369,10 +43369,10 @@
     </row>
     <row r="721" spans="1:25" ht="15.75" customHeight="1">
       <c r="A721" t="s">
+        <v>4032</v>
+      </c>
+      <c r="C721" t="s">
         <v>4033</v>
-      </c>
-      <c r="C721" t="s">
-        <v>4034</v>
       </c>
       <c r="D721">
         <v>1862</v>
@@ -43387,13 +43387,13 @@
         <v>3180</v>
       </c>
       <c r="H721" t="s">
+        <v>4034</v>
+      </c>
+      <c r="I721" t="s">
         <v>4035</v>
       </c>
-      <c r="I721" t="s">
+      <c r="J721" t="s">
         <v>4036</v>
-      </c>
-      <c r="J721" t="s">
-        <v>4037</v>
       </c>
     </row>
     <row r="722" spans="1:25" ht="15.75" customHeight="1">
@@ -43427,7 +43427,7 @@
     </row>
     <row r="723" spans="1:25" ht="15.75" customHeight="1">
       <c r="A723" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="B723" t="s">
         <v>1531</v>
@@ -43448,13 +43448,13 @@
         <v>715</v>
       </c>
       <c r="H723" t="s">
+        <v>4038</v>
+      </c>
+      <c r="I723" t="s">
         <v>4039</v>
       </c>
-      <c r="I723" t="s">
+      <c r="J723" t="s">
         <v>4040</v>
-      </c>
-      <c r="J723" t="s">
-        <v>4041</v>
       </c>
     </row>
     <row r="724" spans="1:25" ht="15.75" customHeight="1">
@@ -43488,7 +43488,7 @@
     </row>
     <row r="725" spans="1:25" ht="15.75" customHeight="1">
       <c r="A725" t="s">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C725" t="s">
         <v>3007</v>
@@ -43500,19 +43500,19 @@
         <v>1948</v>
       </c>
       <c r="F725" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="G725" t="s">
         <v>215</v>
       </c>
       <c r="H725" t="s">
+        <v>4043</v>
+      </c>
+      <c r="I725" t="s">
         <v>4044</v>
       </c>
-      <c r="I725" t="s">
+      <c r="J725" t="s">
         <v>4045</v>
-      </c>
-      <c r="J725" t="s">
-        <v>4046</v>
       </c>
     </row>
     <row r="726" spans="1:25" ht="15.75" customHeight="1">
@@ -43701,10 +43701,10 @@
     </row>
     <row r="730" spans="1:25" ht="15.75" customHeight="1">
       <c r="A730" t="s">
+        <v>4046</v>
+      </c>
+      <c r="C730" t="s">
         <v>4047</v>
-      </c>
-      <c r="C730" t="s">
-        <v>4048</v>
       </c>
       <c r="D730">
         <v>1852</v>
@@ -43716,47 +43716,47 @@
         <v>264</v>
       </c>
       <c r="G730" t="s">
+        <v>4048</v>
+      </c>
+      <c r="H730" t="s">
         <v>4049</v>
       </c>
-      <c r="H730" t="s">
+      <c r="I730" t="s">
         <v>4050</v>
       </c>
-      <c r="I730" t="s">
+      <c r="J730" t="s">
         <v>4051</v>
-      </c>
-      <c r="J730" t="s">
-        <v>4052</v>
       </c>
     </row>
     <row r="731" spans="1:25" ht="15.75" customHeight="1">
       <c r="A731" t="s">
+        <v>4052</v>
+      </c>
+      <c r="C731" t="s">
         <v>4053</v>
-      </c>
-      <c r="C731" t="s">
-        <v>4054</v>
       </c>
       <c r="D731">
         <v>1865</v>
       </c>
       <c r="H731" t="s">
+        <v>4054</v>
+      </c>
+      <c r="J731" t="s">
         <v>4055</v>
-      </c>
-      <c r="J731" t="s">
-        <v>4056</v>
       </c>
     </row>
     <row r="732" spans="1:25" ht="15.75" customHeight="1">
       <c r="A732" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="C732" t="s">
         <v>73</v>
       </c>
       <c r="H732" t="s">
+        <v>4057</v>
+      </c>
+      <c r="J732" t="s">
         <v>4058</v>
-      </c>
-      <c r="J732" t="s">
-        <v>4059</v>
       </c>
     </row>
     <row r="733" spans="1:25" ht="15.75" customHeight="1">
@@ -43851,21 +43851,21 @@
     </row>
     <row r="735" spans="1:25" ht="15.75" customHeight="1">
       <c r="A735" t="s">
+        <v>4059</v>
+      </c>
+      <c r="H735" t="s">
         <v>4060</v>
       </c>
-      <c r="H735" t="s">
+      <c r="J735" t="s">
         <v>4061</v>
-      </c>
-      <c r="J735" t="s">
-        <v>4062</v>
       </c>
     </row>
     <row r="736" spans="1:25" ht="15.75" customHeight="1">
       <c r="A736" t="s">
+        <v>4062</v>
+      </c>
+      <c r="C736" t="s">
         <v>4063</v>
-      </c>
-      <c r="C736" t="s">
-        <v>4064</v>
       </c>
       <c r="D736">
         <v>1864</v>
@@ -43874,19 +43874,19 @@
         <v>1936</v>
       </c>
       <c r="F736" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="G736" t="s">
         <v>298</v>
       </c>
       <c r="H736" t="s">
+        <v>4065</v>
+      </c>
+      <c r="I736" t="s">
         <v>4066</v>
       </c>
-      <c r="I736" t="s">
+      <c r="J736" t="s">
         <v>4067</v>
-      </c>
-      <c r="J736" t="s">
-        <v>4068</v>
       </c>
     </row>
     <row r="737" spans="1:25" ht="15.75" customHeight="1">
@@ -44135,13 +44135,13 @@
     </row>
     <row r="743" spans="1:25" ht="15.75" customHeight="1">
       <c r="A743" t="s">
+        <v>4068</v>
+      </c>
+      <c r="H743" t="s">
         <v>4069</v>
       </c>
-      <c r="H743" t="s">
+      <c r="J743" t="s">
         <v>4070</v>
-      </c>
-      <c r="J743" t="s">
-        <v>4071</v>
       </c>
     </row>
     <row r="744" spans="1:25" ht="15.75" customHeight="1">
@@ -44610,7 +44610,7 @@
     </row>
     <row r="755" spans="1:25" ht="15.75" customHeight="1">
       <c r="A755" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="C755" t="s">
         <v>161</v>
@@ -44628,13 +44628,13 @@
         <v>13</v>
       </c>
       <c r="H755" s="154" t="s">
+        <v>4072</v>
+      </c>
+      <c r="I755" t="s">
         <v>4073</v>
       </c>
-      <c r="I755" t="s">
+      <c r="J755" t="s">
         <v>4074</v>
-      </c>
-      <c r="J755" t="s">
-        <v>4075</v>
       </c>
     </row>
     <row r="756" spans="1:25" ht="15.75" customHeight="1">
@@ -44745,7 +44745,7 @@
     </row>
     <row r="759" spans="1:25" ht="15.75" customHeight="1">
       <c r="A759" t="s">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="C759" t="s">
         <v>11</v>
@@ -44763,13 +44763,13 @@
         <v>20</v>
       </c>
       <c r="H759" t="s">
+        <v>4076</v>
+      </c>
+      <c r="I759" t="s">
         <v>4077</v>
       </c>
-      <c r="I759" t="s">
+      <c r="J759" t="s">
         <v>4078</v>
-      </c>
-      <c r="J759" t="s">
-        <v>4079</v>
       </c>
     </row>
     <row r="760" spans="1:25" ht="15.75" customHeight="1">
@@ -45252,10 +45252,10 @@
     </row>
     <row r="771" spans="1:25" ht="15.75" customHeight="1">
       <c r="A771" t="s">
+        <v>4079</v>
+      </c>
+      <c r="C771" t="s">
         <v>4080</v>
-      </c>
-      <c r="C771" t="s">
-        <v>4081</v>
       </c>
       <c r="D771">
         <v>1868</v>
@@ -45270,13 +45270,13 @@
         <v>567</v>
       </c>
       <c r="H771" t="s">
+        <v>4081</v>
+      </c>
+      <c r="I771" s="138" t="s">
         <v>4082</v>
       </c>
-      <c r="I771" s="138" t="s">
+      <c r="J771" t="s">
         <v>4083</v>
-      </c>
-      <c r="J771" t="s">
-        <v>4084</v>
       </c>
     </row>
     <row r="772" spans="1:25" ht="15.75" customHeight="1">
@@ -45526,10 +45526,10 @@
     </row>
     <row r="778" spans="1:25" ht="15.75" customHeight="1">
       <c r="A778" t="s">
+        <v>4084</v>
+      </c>
+      <c r="C778" t="s">
         <v>4085</v>
-      </c>
-      <c r="C778" t="s">
-        <v>4086</v>
       </c>
       <c r="D778">
         <v>1852</v>
@@ -45544,21 +45544,21 @@
         <v>20</v>
       </c>
       <c r="H778" t="s">
+        <v>4086</v>
+      </c>
+      <c r="I778" t="s">
         <v>4087</v>
       </c>
-      <c r="I778" t="s">
+      <c r="J778" t="s">
         <v>4088</v>
-      </c>
-      <c r="J778" t="s">
-        <v>4089</v>
       </c>
     </row>
     <row r="779" spans="1:25" ht="15.75" customHeight="1">
       <c r="A779" t="s">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="C779" t="s">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="D779">
         <v>1847</v>
@@ -45567,19 +45567,19 @@
         <v>1927</v>
       </c>
       <c r="F779" t="s">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="G779" t="s">
         <v>20</v>
       </c>
       <c r="H779" t="s">
+        <v>4091</v>
+      </c>
+      <c r="I779" t="s">
         <v>4092</v>
       </c>
-      <c r="I779" t="s">
+      <c r="J779" t="s">
         <v>4093</v>
-      </c>
-      <c r="J779" t="s">
-        <v>4094</v>
       </c>
     </row>
     <row r="780" spans="1:25" ht="15.75" customHeight="1">
@@ -47004,7 +47004,7 @@
     <hyperlink ref="I761" r:id="rId306" xr:uid="{DC8DA59C-9728-B348-8CBF-E7C3590D3EBA}"/>
     <hyperlink ref="I768" r:id="rId307" xr:uid="{F45E902F-8511-E24D-AE19-4FB322067B27}"/>
     <hyperlink ref="I63" r:id="rId308" tooltip="https://d-nb.info/gnd/118137948" xr:uid="{8B780818-038B-1C41-BBC6-6D7B0A6D4217}"/>
-    <hyperlink ref="I64" r:id="rId309" tooltip="https://d-nb.info/gnd/123557372" xr:uid="{B1B306E3-1895-F547-A084-F4AB46C52D26}"/>
+    <hyperlink ref="I64" r:id="rId309" xr:uid="{B1B306E3-1895-F547-A084-F4AB46C52D26}"/>
     <hyperlink ref="I93" r:id="rId310" tooltip="https://d-nb.info/gnd/124541755" xr:uid="{9AFB9BDC-B838-F046-9A8D-B7CA012FBBA7}"/>
     <hyperlink ref="I94" r:id="rId311" tooltip="https://d-nb.info/gnd/143806769" xr:uid="{60113DA8-C120-FC40-B011-03EDEA47276C}"/>
     <hyperlink ref="I99" r:id="rId312" tooltip="https://d-nb.info/gnd/116463015" xr:uid="{47EBCDE7-1D80-9D4B-814C-1EF955EF8323}"/>
@@ -47074,11 +47074,13 @@
     <hyperlink ref="I771" r:id="rId376" tooltip="https://d-nb.info/gnd/1268159913" xr:uid="{225F9276-F953-9145-BE3F-CD079A103304}"/>
     <hyperlink ref="I107" r:id="rId377" tooltip="https://d-nb.info/gnd/138066736" xr:uid="{3F39F859-CDE5-F44C-AE26-F55F5599A0FD}"/>
     <hyperlink ref="I454" r:id="rId378" xr:uid="{F1200265-72D3-0A46-92DF-D711D50C61F1}"/>
+    <hyperlink ref="I121" r:id="rId379" xr:uid="{FD0A9C6F-5343-874B-8E05-4B8C06EDAC44}"/>
+    <hyperlink ref="I703" r:id="rId380" xr:uid="{DCED84D7-DAA6-D74C-A942-42BB2D5BFB9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId379"/>
+    <tablePart r:id="rId381"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F021BD20-23FF-AE4B-91B0-6230748FE255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA1E658-EC39-FB48-A03D-4609CCD21C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB03C03F-F11D-B549-945E-93F8A3BD7BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9F2731-E127-4548-B21E-AD01F4C6ADC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="4361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5909" uniqueCount="4363">
   <si>
     <t>Nachname</t>
   </si>
@@ -13277,6 +13277,12 @@
   </si>
   <si>
     <t>https://d-nb.info/gnd/116933062</t>
+  </si>
+  <si>
+    <t>geb. Schoeller</t>
+  </si>
+  <si>
+    <t>Hütten bei Königstein</t>
   </si>
 </sst>
 </file>
@@ -14104,7 +14110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -14816,17 +14822,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -16770,26 +16768,26 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="1:25" ht="16">
-      <c r="A41" s="336" t="s">
+      <c r="A41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="336"/>
-      <c r="C41" s="336" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="s">
         <v>4351</v>
       </c>
-      <c r="D41" s="336"/>
-      <c r="E41" s="336">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1">
         <v>1910</v>
       </c>
-      <c r="F41" s="336"/>
-      <c r="G41" s="336" t="s">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1" t="s">
         <v>4354</v>
       </c>
-      <c r="H41" s="336" t="s">
+      <c r="H41" s="1" t="s">
         <v>4352</v>
       </c>
-      <c r="I41" s="337"/>
-      <c r="J41" s="336" t="s">
+      <c r="I41" s="4"/>
+      <c r="J41" s="1" t="s">
         <v>4353</v>
       </c>
       <c r="K41" s="1"/>
@@ -22773,28 +22771,28 @@
       <c r="Y190" s="1"/>
     </row>
     <row r="191" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A191" s="333" t="s">
+      <c r="A191" s="2" t="s">
         <v>4336</v>
       </c>
-      <c r="B191" s="333" t="s">
+      <c r="B191" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="C191" s="333" t="s">
+      <c r="C191" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D191" s="333">
+      <c r="D191" s="2">
         <v>1855</v>
       </c>
-      <c r="E191" s="333">
+      <c r="E191" s="2">
         <v>1941</v>
       </c>
-      <c r="F191" s="333" t="s">
+      <c r="F191" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G191" s="333" t="s">
+      <c r="G191" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H191" s="333" t="s">
+      <c r="H191" s="2" t="s">
         <v>4337</v>
       </c>
       <c r="I191" s="180" t="s">
@@ -27970,6 +27968,9 @@
       <c r="E322">
         <v>1908</v>
       </c>
+      <c r="F322" s="15" t="s">
+        <v>4362</v>
+      </c>
       <c r="G322" s="15" t="s">
         <v>419</v>
       </c>
@@ -27984,6 +27985,9 @@
       <c r="A323" s="15" t="s">
         <v>4347</v>
       </c>
+      <c r="B323" s="15" t="s">
+        <v>4361</v>
+      </c>
       <c r="C323" t="s">
         <v>4348</v>
       </c>
@@ -27992,6 +27996,12 @@
       </c>
       <c r="E323">
         <v>1913</v>
+      </c>
+      <c r="F323" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G323" s="15" t="s">
+        <v>304</v>
       </c>
       <c r="H323" s="15" t="s">
         <v>4349</v>
@@ -31961,7 +31971,7 @@
       <c r="E421" s="156"/>
       <c r="F421" s="156"/>
       <c r="G421" s="156"/>
-      <c r="H421" s="335" t="s">
+      <c r="H421" s="333" t="s">
         <v>3203</v>
       </c>
       <c r="J421" s="156" t="s">
@@ -37933,20 +37943,20 @@
       <c r="Y574" s="10"/>
     </row>
     <row r="575" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A575" s="333" t="s">
+      <c r="A575" s="2" t="s">
         <v>2043</v>
       </c>
-      <c r="B575" s="333"/>
-      <c r="C575" s="333"/>
-      <c r="D575" s="333"/>
-      <c r="E575" s="333"/>
-      <c r="F575" s="333"/>
-      <c r="G575" s="333"/>
-      <c r="H575" s="333" t="s">
+      <c r="B575" s="2"/>
+      <c r="C575" s="2"/>
+      <c r="D575" s="2"/>
+      <c r="E575" s="2"/>
+      <c r="F575" s="2"/>
+      <c r="G575" s="2"/>
+      <c r="H575" s="2" t="s">
         <v>4327</v>
       </c>
-      <c r="I575" s="334"/>
-      <c r="J575" s="333" t="s">
+      <c r="I575" s="19"/>
+      <c r="J575" s="2" t="s">
         <v>4328</v>
       </c>
       <c r="K575" s="10"/>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9F2731-E127-4548-B21E-AD01F4C6ADC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212C8CEE-292B-D249-8FC8-6D12DA7E6D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212C8CEE-292B-D249-8FC8-6D12DA7E6D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564A4656-AD60-7143-9AFC-618BCA59599C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5909" uniqueCount="4363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="4363">
   <si>
     <t>Nachname</t>
   </si>
@@ -13003,9 +13003,6 @@
     <t>Scarpa</t>
   </si>
   <si>
-    <t>Generalagent des Öst. Lloyd in Bombay</t>
-  </si>
-  <si>
     <t>ScarpaEmil</t>
   </si>
   <si>
@@ -13283,6 +13280,9 @@
   </si>
   <si>
     <t>Hütten bei Königstein</t>
+  </si>
+  <si>
+    <t>Generalagent des Öst. Lloyd in Bombay, Rechtsanwalt und Verwaltungsrat</t>
   </si>
 </sst>
 </file>
@@ -14110,7 +14110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="334">
+  <cellXfs count="335">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -14825,6 +14825,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -15925,13 +15928,13 @@
         <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>4328</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>4330</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>4329</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>4331</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>4330</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="32">
@@ -16773,7 +16776,7 @@
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>4351</v>
+        <v>4350</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1">
@@ -16781,14 +16784,14 @@
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>4352</v>
+        <v>4351</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="1" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -22232,11 +22235,11 @@
       <c r="F176" s="25"/>
       <c r="G176" s="25"/>
       <c r="H176" s="26" t="s">
-        <v>4344</v>
+        <v>4343</v>
       </c>
       <c r="I176" s="184"/>
       <c r="J176" s="25" t="s">
-        <v>4345</v>
+        <v>4344</v>
       </c>
       <c r="K176" s="9"/>
       <c r="L176" s="9"/>
@@ -22267,11 +22270,11 @@
       <c r="F177" s="25"/>
       <c r="G177" s="25"/>
       <c r="H177" s="26" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
       <c r="I177" s="184"/>
       <c r="J177" s="25" t="s">
-        <v>4355</v>
+        <v>4354</v>
       </c>
       <c r="K177" s="9"/>
       <c r="L177" s="9"/>
@@ -22772,7 +22775,7 @@
     </row>
     <row r="191" spans="1:26" ht="15.75" customHeight="1">
       <c r="A191" s="2" t="s">
-        <v>4336</v>
+        <v>4335</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>731</v>
@@ -22793,13 +22796,13 @@
         <v>20</v>
       </c>
       <c r="H191" s="2" t="s">
+        <v>4336</v>
+      </c>
+      <c r="I191" s="180" t="s">
         <v>4337</v>
       </c>
-      <c r="I191" s="180" t="s">
+      <c r="J191" s="252" t="s">
         <v>4338</v>
-      </c>
-      <c r="J191" s="252" t="s">
-        <v>4339</v>
       </c>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
@@ -26059,13 +26062,13 @@
     </row>
     <row r="277" spans="1:26" ht="15.75" customHeight="1">
       <c r="A277" s="1" t="s">
-        <v>4340</v>
+        <v>4339</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>4222</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>4341</v>
+        <v>4340</v>
       </c>
       <c r="D277" s="1">
         <v>1886</v>
@@ -26080,11 +26083,11 @@
         <v>95</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>4342</v>
+        <v>4341</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="75" t="s">
-        <v>4343</v>
+        <v>4342</v>
       </c>
       <c r="K277" s="75"/>
       <c r="L277" s="75"/>
@@ -27957,7 +27960,7 @@
     </row>
     <row r="322" spans="1:25" ht="15.75" customHeight="1">
       <c r="A322" s="15" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="C322" s="15" t="s">
         <v>745</v>
@@ -27969,27 +27972,27 @@
         <v>1908</v>
       </c>
       <c r="F322" s="15" t="s">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="G322" s="15" t="s">
         <v>419</v>
       </c>
       <c r="H322" s="15" t="s">
-        <v>4357</v>
+        <v>4356</v>
       </c>
       <c r="J322" s="15" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="323" spans="1:25" ht="15.75" customHeight="1">
       <c r="A323" s="15" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B323" s="15" t="s">
+        <v>4360</v>
+      </c>
+      <c r="C323" t="s">
         <v>4347</v>
-      </c>
-      <c r="B323" s="15" t="s">
-        <v>4361</v>
-      </c>
-      <c r="C323" t="s">
-        <v>4348</v>
       </c>
       <c r="D323">
         <v>1857</v>
@@ -28004,15 +28007,15 @@
         <v>304</v>
       </c>
       <c r="H323" s="15" t="s">
+        <v>4348</v>
+      </c>
+      <c r="J323" s="15" t="s">
         <v>4349</v>
-      </c>
-      <c r="J323" s="15" t="s">
-        <v>4350</v>
       </c>
     </row>
     <row r="324" spans="1:25" ht="15.75" customHeight="1">
       <c r="A324" s="15" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="C324" s="15" t="s">
         <v>143</v>
@@ -28030,13 +28033,13 @@
         <v>3672</v>
       </c>
       <c r="H324" s="15" t="s">
+        <v>4357</v>
+      </c>
+      <c r="I324" t="s">
+        <v>4359</v>
+      </c>
+      <c r="J324" s="15" t="s">
         <v>4358</v>
-      </c>
-      <c r="I324" t="s">
-        <v>4360</v>
-      </c>
-      <c r="J324" s="15" t="s">
-        <v>4359</v>
       </c>
     </row>
     <row r="325" spans="1:25" ht="15.75" customHeight="1">
@@ -30798,19 +30801,19 @@
         <v>1910</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>4332</v>
+        <v>4331</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H394" s="1" t="s">
+        <v>4332</v>
+      </c>
+      <c r="I394" s="1" t="s">
         <v>4333</v>
       </c>
-      <c r="I394" s="1" t="s">
+      <c r="J394" s="1" t="s">
         <v>4334</v>
-      </c>
-      <c r="J394" s="1" t="s">
-        <v>4335</v>
       </c>
       <c r="K394" s="1"/>
       <c r="L394" s="1"/>
@@ -37953,11 +37956,11 @@
       <c r="F575" s="2"/>
       <c r="G575" s="2"/>
       <c r="H575" s="2" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="I575" s="19"/>
       <c r="J575" s="2" t="s">
-        <v>4328</v>
+        <v>4327</v>
       </c>
       <c r="K575" s="10"/>
       <c r="L575" s="10"/>
@@ -40402,11 +40405,17 @@
       <c r="C639" t="s">
         <v>1038</v>
       </c>
-      <c r="H639" s="137" t="s">
+      <c r="E639">
+        <v>1929</v>
+      </c>
+      <c r="G639" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="H639" s="334" t="s">
+        <v>4362</v>
+      </c>
+      <c r="J639" t="s">
         <v>4269</v>
-      </c>
-      <c r="J639" t="s">
-        <v>4270</v>
       </c>
     </row>
     <row r="640" spans="1:25" ht="15.75" customHeight="1">
@@ -41072,7 +41081,7 @@
     </row>
     <row r="656" spans="1:25" ht="15.75" customHeight="1">
       <c r="A656" t="s">
-        <v>4271</v>
+        <v>4270</v>
       </c>
       <c r="C656" t="s">
         <v>151</v>
@@ -41084,19 +41093,19 @@
         <v>1927</v>
       </c>
       <c r="F656" t="s">
+        <v>4271</v>
+      </c>
+      <c r="G656" t="s">
         <v>4272</v>
       </c>
-      <c r="G656" t="s">
+      <c r="H656" s="137" t="s">
         <v>4273</v>
       </c>
-      <c r="H656" s="137" t="s">
+      <c r="I656" t="s">
         <v>4274</v>
       </c>
-      <c r="I656" t="s">
+      <c r="J656" t="s">
         <v>4275</v>
-      </c>
-      <c r="J656" t="s">
-        <v>4276</v>
       </c>
     </row>
     <row r="657" spans="1:25" ht="15.75" customHeight="1">
@@ -41712,7 +41721,7 @@
     </row>
     <row r="672" spans="1:25" ht="15.75" customHeight="1">
       <c r="A672" t="s">
-        <v>4277</v>
+        <v>4276</v>
       </c>
       <c r="C672" t="s">
         <v>432</v>
@@ -41730,13 +41739,13 @@
         <v>3621</v>
       </c>
       <c r="H672" s="137" t="s">
+        <v>4277</v>
+      </c>
+      <c r="I672" t="s">
         <v>4278</v>
       </c>
-      <c r="I672" t="s">
+      <c r="J672" t="s">
         <v>4279</v>
-      </c>
-      <c r="J672" t="s">
-        <v>4280</v>
       </c>
     </row>
     <row r="673" spans="1:25" ht="15.75" customHeight="1">
@@ -42872,7 +42881,7 @@
     </row>
     <row r="702" spans="1:25" ht="15.75" customHeight="1">
       <c r="A702" t="s">
-        <v>4281</v>
+        <v>4280</v>
       </c>
       <c r="C702" t="s">
         <v>1914</v>
@@ -42890,13 +42899,13 @@
         <v>1966</v>
       </c>
       <c r="H702" s="137" t="s">
+        <v>4281</v>
+      </c>
+      <c r="I702" s="124" t="s">
         <v>4282</v>
       </c>
-      <c r="I702" s="124" t="s">
+      <c r="J702" t="s">
         <v>4283</v>
-      </c>
-      <c r="J702" t="s">
-        <v>4284</v>
       </c>
     </row>
     <row r="703" spans="1:25" ht="15.75" customHeight="1">
@@ -44788,7 +44797,7 @@
     </row>
     <row r="751" spans="1:25" ht="15.75" customHeight="1">
       <c r="A751" t="s">
-        <v>4285</v>
+        <v>4284</v>
       </c>
       <c r="C751" t="s">
         <v>1050</v>
@@ -44806,13 +44815,13 @@
         <v>20</v>
       </c>
       <c r="H751" s="137" t="s">
+        <v>4285</v>
+      </c>
+      <c r="I751" t="s">
         <v>4286</v>
       </c>
-      <c r="I751" t="s">
+      <c r="J751" t="s">
         <v>4287</v>
-      </c>
-      <c r="J751" t="s">
-        <v>4288</v>
       </c>
     </row>
     <row r="752" spans="1:25" ht="15.75" customHeight="1">
@@ -45106,7 +45115,7 @@
     </row>
     <row r="759" spans="1:25" ht="15.75" customHeight="1">
       <c r="A759" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
       <c r="C759" t="s">
         <v>473</v>
@@ -45121,16 +45130,16 @@
         <v>1508</v>
       </c>
       <c r="G759" t="s">
+        <v>4289</v>
+      </c>
+      <c r="H759" s="137" t="s">
         <v>4290</v>
       </c>
-      <c r="H759" s="137" t="s">
+      <c r="I759" t="s">
         <v>4291</v>
       </c>
-      <c r="I759" t="s">
+      <c r="J759" t="s">
         <v>4292</v>
-      </c>
-      <c r="J759" t="s">
-        <v>4293</v>
       </c>
     </row>
     <row r="760" spans="1:25" ht="15.75" customHeight="1">
@@ -45290,10 +45299,10 @@
     </row>
     <row r="764" spans="1:25" ht="15.75" customHeight="1">
       <c r="A764" t="s">
+        <v>4293</v>
+      </c>
+      <c r="C764" t="s">
         <v>4294</v>
-      </c>
-      <c r="C764" t="s">
-        <v>4295</v>
       </c>
       <c r="D764">
         <v>1843</v>
@@ -45302,16 +45311,16 @@
         <v>1906</v>
       </c>
       <c r="F764" t="s">
-        <v>4296</v>
+        <v>4295</v>
       </c>
       <c r="G764" t="s">
         <v>1508</v>
       </c>
       <c r="H764" s="137" t="s">
+        <v>4296</v>
+      </c>
+      <c r="J764" t="s">
         <v>4297</v>
-      </c>
-      <c r="J764" t="s">
-        <v>4298</v>
       </c>
     </row>
     <row r="765" spans="1:25" ht="15.75" customHeight="1">
@@ -46207,10 +46216,10 @@
     </row>
     <row r="790" spans="1:25" ht="15.75" customHeight="1">
       <c r="A790" t="s">
+        <v>4298</v>
+      </c>
+      <c r="C790" t="s">
         <v>4299</v>
-      </c>
-      <c r="C790" t="s">
-        <v>4300</v>
       </c>
       <c r="D790">
         <v>1827</v>
@@ -46225,13 +46234,13 @@
         <v>800</v>
       </c>
       <c r="H790" s="137" t="s">
+        <v>4300</v>
+      </c>
+      <c r="I790" t="s">
         <v>4301</v>
       </c>
-      <c r="I790" t="s">
+      <c r="J790" t="s">
         <v>4302</v>
-      </c>
-      <c r="J790" t="s">
-        <v>4303</v>
       </c>
     </row>
     <row r="791" spans="1:25" ht="15.75" customHeight="1">
@@ -46283,13 +46292,13 @@
     </row>
     <row r="792" spans="1:25" ht="15.75" customHeight="1">
       <c r="A792" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B792" t="s">
         <v>4304</v>
       </c>
-      <c r="B792" t="s">
+      <c r="C792" t="s">
         <v>4305</v>
-      </c>
-      <c r="C792" t="s">
-        <v>4306</v>
       </c>
       <c r="D792">
         <v>1877</v>
@@ -46298,19 +46307,19 @@
         <v>1953</v>
       </c>
       <c r="F792" t="s">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="G792" t="s">
         <v>1204</v>
       </c>
       <c r="H792" s="137" t="s">
+        <v>4307</v>
+      </c>
+      <c r="I792" s="124" t="s">
         <v>4308</v>
       </c>
-      <c r="I792" s="124" t="s">
+      <c r="J792" t="s">
         <v>4309</v>
-      </c>
-      <c r="J792" t="s">
-        <v>4310</v>
       </c>
     </row>
     <row r="793" spans="1:25" ht="15.75" customHeight="1">
@@ -46391,7 +46400,7 @@
     </row>
     <row r="795" spans="1:25" ht="15.75" customHeight="1">
       <c r="A795" t="s">
-        <v>4311</v>
+        <v>4310</v>
       </c>
       <c r="B795" t="s">
         <v>26</v>
@@ -46406,19 +46415,19 @@
         <v>1930</v>
       </c>
       <c r="F795" t="s">
+        <v>4311</v>
+      </c>
+      <c r="G795" t="s">
         <v>4312</v>
       </c>
-      <c r="G795" t="s">
+      <c r="H795" s="137" t="s">
         <v>4313</v>
       </c>
-      <c r="H795" s="137" t="s">
+      <c r="I795" t="s">
         <v>4314</v>
       </c>
-      <c r="I795" t="s">
+      <c r="J795" t="s">
         <v>4315</v>
-      </c>
-      <c r="J795" t="s">
-        <v>4316</v>
       </c>
     </row>
     <row r="796" spans="1:25" ht="15.75" customHeight="1">
@@ -47496,13 +47505,13 @@
     </row>
     <row r="823" spans="1:25" ht="15.75" customHeight="1">
       <c r="A823" t="s">
-        <v>4317</v>
+        <v>4316</v>
       </c>
       <c r="B823" t="s">
         <v>18</v>
       </c>
       <c r="C823" t="s">
-        <v>4318</v>
+        <v>4317</v>
       </c>
       <c r="D823">
         <v>1838</v>
@@ -47517,13 +47526,13 @@
         <v>122</v>
       </c>
       <c r="H823" s="137" t="s">
+        <v>4318</v>
+      </c>
+      <c r="I823" t="s">
         <v>4319</v>
       </c>
-      <c r="I823" t="s">
+      <c r="J823" t="s">
         <v>4320</v>
-      </c>
-      <c r="J823" t="s">
-        <v>4321</v>
       </c>
     </row>
     <row r="824" spans="1:25" ht="15.75" customHeight="1">
@@ -47677,10 +47686,10 @@
     </row>
     <row r="828" spans="1:25" ht="15.75" customHeight="1">
       <c r="A828" t="s">
+        <v>4321</v>
+      </c>
+      <c r="C828" t="s">
         <v>4322</v>
-      </c>
-      <c r="C828" t="s">
-        <v>4323</v>
       </c>
       <c r="D828">
         <v>1819</v>
@@ -47695,13 +47704,13 @@
         <v>420</v>
       </c>
       <c r="H828" s="137" t="s">
+        <v>4323</v>
+      </c>
+      <c r="I828" t="s">
         <v>4324</v>
       </c>
-      <c r="I828" t="s">
+      <c r="J828" t="s">
         <v>4325</v>
-      </c>
-      <c r="J828" t="s">
-        <v>4326</v>
       </c>
     </row>
     <row r="829" spans="1:25" ht="15.75" customHeight="1">

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564A4656-AD60-7143-9AFC-618BCA59599C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3134D66-6A96-C844-9C4D-71C29629935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="4363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5918" uniqueCount="4368">
   <si>
     <t>Nachname</t>
   </si>
@@ -13283,6 +13283,21 @@
   </si>
   <si>
     <t>Generalagent des Öst. Lloyd in Bombay, Rechtsanwalt und Verwaltungsrat</t>
+  </si>
+  <si>
+    <t>Sternberg</t>
+  </si>
+  <si>
+    <t>Pohořelice</t>
+  </si>
+  <si>
+    <t>zunächst gescheiterte militärische Karriere, 1907–1911 MöAH</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/117232416</t>
+  </si>
+  <si>
+    <t>SternbergAdalbert</t>
   </si>
 </sst>
 </file>
@@ -14110,7 +14125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="335">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -14785,7 +14800,6 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="80" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -14878,9 +14892,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A2:Y849" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y849">
-    <sortCondition ref="A849"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A2:Y850" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y850">
+    <sortCondition ref="A850"/>
   </sortState>
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -15116,7 +15130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1429"/>
+  <dimension ref="A1:Z1430"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -19272,7 +19286,7 @@
       <c r="I102" s="192" t="s">
         <v>462</v>
       </c>
-      <c r="J102" s="325" t="s">
+      <c r="J102" s="324" t="s">
         <v>463</v>
       </c>
       <c r="K102" s="13"/>
@@ -20686,7 +20700,7 @@
       <c r="I137" t="s">
         <v>3617</v>
       </c>
-      <c r="J137" s="330" t="s">
+      <c r="J137" s="329" t="s">
         <v>3618</v>
       </c>
       <c r="Z137" s="16"/>
@@ -21355,7 +21369,7 @@
       <c r="H153" s="61" t="s">
         <v>635</v>
       </c>
-      <c r="I153" s="321" t="s">
+      <c r="I153" s="320" t="s">
         <v>636</v>
       </c>
       <c r="J153" s="61" t="s">
@@ -22625,7 +22639,7 @@
       <c r="I186" s="154" t="s">
         <v>3519</v>
       </c>
-      <c r="J186" s="330" t="s">
+      <c r="J186" s="329" t="s">
         <v>3520</v>
       </c>
     </row>
@@ -22848,7 +22862,7 @@
       <c r="I192" s="308" t="s">
         <v>3514</v>
       </c>
-      <c r="J192" s="328" t="s">
+      <c r="J192" s="327" t="s">
         <v>774</v>
       </c>
       <c r="K192" s="1"/>
@@ -24027,7 +24041,7 @@
       <c r="I224" s="124" t="s">
         <v>3536</v>
       </c>
-      <c r="J224" s="327" t="s">
+      <c r="J224" s="326" t="s">
         <v>3537</v>
       </c>
       <c r="K224" s="9"/>
@@ -24074,7 +24088,7 @@
       <c r="I225" s="184" t="s">
         <v>866</v>
       </c>
-      <c r="J225" s="327" t="s">
+      <c r="J225" s="326" t="s">
         <v>867</v>
       </c>
       <c r="K225" s="9"/>
@@ -24147,7 +24161,7 @@
       <c r="H227" s="67" t="s">
         <v>872</v>
       </c>
-      <c r="I227" s="312" t="s">
+      <c r="I227" s="311" t="s">
         <v>873</v>
       </c>
       <c r="J227" s="68" t="s">
@@ -24489,7 +24503,7 @@
       <c r="H236" s="26" t="s">
         <v>907</v>
       </c>
-      <c r="I236" s="319" t="s">
+      <c r="I236" s="318" t="s">
         <v>908</v>
       </c>
       <c r="J236" s="25" t="s">
@@ -26383,7 +26397,7 @@
       <c r="H284" s="164" t="s">
         <v>1074</v>
       </c>
-      <c r="I284" s="320" t="s">
+      <c r="I284" s="319" t="s">
         <v>1075</v>
       </c>
       <c r="J284" s="217" t="s">
@@ -26430,7 +26444,7 @@
       <c r="H285" s="164" t="s">
         <v>1078</v>
       </c>
-      <c r="I285" s="310" t="s">
+      <c r="I285" s="185" t="s">
         <v>1079</v>
       </c>
       <c r="J285" s="217" t="s">
@@ -26524,7 +26538,7 @@
       <c r="H287" s="25" t="s">
         <v>1088</v>
       </c>
-      <c r="I287" s="314" t="s">
+      <c r="I287" s="313" t="s">
         <v>1089</v>
       </c>
       <c r="J287" s="26" t="s">
@@ -27277,8 +27291,8 @@
       <c r="H305" s="25" t="s">
         <v>1163</v>
       </c>
-      <c r="I305" s="319"/>
-      <c r="J305" s="332" t="s">
+      <c r="I305" s="318"/>
+      <c r="J305" s="331" t="s">
         <v>1164</v>
       </c>
       <c r="K305" s="9"/>
@@ -27325,7 +27339,7 @@
       <c r="I306" s="27" t="s">
         <v>1169</v>
       </c>
-      <c r="J306" s="329" t="s">
+      <c r="J306" s="328" t="s">
         <v>1170</v>
       </c>
       <c r="K306" s="9"/>
@@ -27402,7 +27416,7 @@
       <c r="I308" s="82" t="s">
         <v>1174</v>
       </c>
-      <c r="J308" s="329" t="s">
+      <c r="J308" s="328" t="s">
         <v>1175</v>
       </c>
       <c r="K308" s="9"/>
@@ -27481,7 +27495,7 @@
       <c r="I310" s="299" t="s">
         <v>1180</v>
       </c>
-      <c r="J310" s="324" t="s">
+      <c r="J310" s="323" t="s">
         <v>1181</v>
       </c>
       <c r="K310" s="9"/>
@@ -28996,7 +29010,7 @@
       <c r="H348" s="230" t="s">
         <v>1308</v>
       </c>
-      <c r="I348" s="311"/>
+      <c r="I348" s="310"/>
       <c r="J348" s="230" t="s">
         <v>1309</v>
       </c>
@@ -30335,7 +30349,7 @@
       <c r="I383" s="297" t="s">
         <v>2907</v>
       </c>
-      <c r="J383" s="323" t="s">
+      <c r="J383" s="322" t="s">
         <v>2908</v>
       </c>
       <c r="K383" s="25"/>
@@ -31243,7 +31257,7 @@
       <c r="H404" s="97" t="s">
         <v>1498</v>
       </c>
-      <c r="I404" s="318" t="s">
+      <c r="I404" s="317" t="s">
         <v>1499</v>
       </c>
       <c r="J404" s="155" t="s">
@@ -31630,7 +31644,7 @@
       <c r="H413" s="156" t="s">
         <v>3783</v>
       </c>
-      <c r="I413" s="316" t="s">
+      <c r="I413" s="315" t="s">
         <v>3784</v>
       </c>
       <c r="J413" s="156" t="s">
@@ -31974,7 +31988,7 @@
       <c r="E421" s="156"/>
       <c r="F421" s="156"/>
       <c r="G421" s="156"/>
-      <c r="H421" s="333" t="s">
+      <c r="H421" s="332" t="s">
         <v>3203</v>
       </c>
       <c r="J421" s="156" t="s">
@@ -33699,7 +33713,7 @@
       <c r="H462" s="59" t="s">
         <v>1723</v>
       </c>
-      <c r="I462" s="313" t="s">
+      <c r="I462" s="312" t="s">
         <v>1724</v>
       </c>
       <c r="J462" s="59" t="s">
@@ -34092,7 +34106,7 @@
         <v>2934</v>
       </c>
       <c r="I471" s="304"/>
-      <c r="J471" s="326" t="s">
+      <c r="J471" s="325" t="s">
         <v>3547</v>
       </c>
       <c r="K471" s="1"/>
@@ -34532,7 +34546,7 @@
       <c r="H481" s="67" t="s">
         <v>1804</v>
       </c>
-      <c r="I481" s="322" t="s">
+      <c r="I481" s="321" t="s">
         <v>2854</v>
       </c>
       <c r="J481" s="68" t="s">
@@ -36398,7 +36412,7 @@
       <c r="H531" s="100" t="s">
         <v>1949</v>
       </c>
-      <c r="I531" s="315"/>
+      <c r="I531" s="314"/>
       <c r="J531" s="212" t="s">
         <v>1950</v>
       </c>
@@ -37229,7 +37243,7 @@
       <c r="I555" t="s">
         <v>3316</v>
       </c>
-      <c r="J555" s="331" t="s">
+      <c r="J555" s="330" t="s">
         <v>3317</v>
       </c>
     </row>
@@ -37925,7 +37939,7 @@
       <c r="H574" s="100" t="s">
         <v>2044</v>
       </c>
-      <c r="I574" s="317"/>
+      <c r="I574" s="316"/>
       <c r="J574" s="212" t="s">
         <v>2045</v>
       </c>
@@ -40411,7 +40425,7 @@
       <c r="G639" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="H639" s="334" t="s">
+      <c r="H639" s="333" t="s">
         <v>4362</v>
       </c>
       <c r="J639" t="s">
@@ -43404,82 +43418,67 @@
       </c>
     </row>
     <row r="717" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A717" s="26" t="s">
+      <c r="A717" s="15" t="s">
+        <v>4363</v>
+      </c>
+      <c r="B717" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C717" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="D717">
+        <v>1868</v>
+      </c>
+      <c r="E717">
+        <v>1930</v>
+      </c>
+      <c r="F717" t="s">
+        <v>4364</v>
+      </c>
+      <c r="G717" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H717" s="15" t="s">
+        <v>4365</v>
+      </c>
+      <c r="I717" t="s">
+        <v>4366</v>
+      </c>
+      <c r="J717" s="15" t="s">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="718" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A718" s="26" t="s">
         <v>2486</v>
       </c>
-      <c r="B717" s="25" t="s">
+      <c r="B718" s="25" t="s">
         <v>479</v>
       </c>
-      <c r="C717" s="25" t="s">
+      <c r="C718" s="25" t="s">
         <v>2487</v>
       </c>
-      <c r="D717" s="25">
+      <c r="D718" s="25">
         <v>1829</v>
       </c>
-      <c r="E717" s="25">
+      <c r="E718" s="25">
         <v>1897</v>
       </c>
-      <c r="F717" s="25" t="s">
+      <c r="F718" s="25" t="s">
         <v>2481</v>
       </c>
-      <c r="G717" s="25" t="s">
+      <c r="G718" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H717" s="26" t="s">
+      <c r="H718" s="26" t="s">
         <v>2488</v>
       </c>
-      <c r="I717" s="123" t="s">
+      <c r="I718" s="123" t="s">
         <v>2489</v>
       </c>
-      <c r="J717" s="25" t="s">
+      <c r="J718" s="25" t="s">
         <v>2490</v>
-      </c>
-      <c r="K717" s="9"/>
-      <c r="L717" s="9"/>
-      <c r="M717" s="9"/>
-      <c r="N717" s="9"/>
-      <c r="O717" s="9"/>
-      <c r="P717" s="9"/>
-      <c r="Q717" s="9"/>
-      <c r="R717" s="9"/>
-      <c r="S717" s="9"/>
-      <c r="T717" s="9"/>
-      <c r="U717" s="9"/>
-      <c r="V717" s="9"/>
-      <c r="W717" s="9"/>
-      <c r="X717" s="9"/>
-      <c r="Y717" s="9"/>
-    </row>
-    <row r="718" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A718" s="25" t="s">
-        <v>2491</v>
-      </c>
-      <c r="B718" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="C718" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D718" s="25">
-        <v>1854</v>
-      </c>
-      <c r="E718" s="25">
-        <v>1930</v>
-      </c>
-      <c r="F718" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G718" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="H718" s="26" t="s">
-        <v>2492</v>
-      </c>
-      <c r="I718" s="25" t="s">
-        <v>2493</v>
-      </c>
-      <c r="J718" s="25" t="s">
-        <v>2494</v>
       </c>
       <c r="K718" s="9"/>
       <c r="L718" s="9"/>
@@ -43498,261 +43497,261 @@
       <c r="Y718" s="9"/>
     </row>
     <row r="719" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A719" t="s">
-        <v>3995</v>
-      </c>
-      <c r="C719" t="s">
-        <v>3996</v>
-      </c>
-      <c r="D719">
-        <v>1867</v>
-      </c>
-      <c r="E719">
-        <v>1921</v>
-      </c>
-      <c r="F719" t="s">
-        <v>3671</v>
-      </c>
-      <c r="G719" t="s">
-        <v>3178</v>
-      </c>
-      <c r="H719" t="s">
-        <v>3997</v>
-      </c>
-      <c r="I719" t="s">
-        <v>3998</v>
-      </c>
-      <c r="J719" t="s">
-        <v>3999</v>
-      </c>
+      <c r="A719" s="25" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B719" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C719" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D719" s="25">
+        <v>1854</v>
+      </c>
+      <c r="E719" s="25">
+        <v>1930</v>
+      </c>
+      <c r="F719" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G719" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="H719" s="26" t="s">
+        <v>2492</v>
+      </c>
+      <c r="I719" s="25" t="s">
+        <v>2493</v>
+      </c>
+      <c r="J719" s="25" t="s">
+        <v>2494</v>
+      </c>
+      <c r="K719" s="9"/>
+      <c r="L719" s="9"/>
+      <c r="M719" s="9"/>
+      <c r="N719" s="9"/>
+      <c r="O719" s="9"/>
+      <c r="P719" s="9"/>
+      <c r="Q719" s="9"/>
+      <c r="R719" s="9"/>
+      <c r="S719" s="9"/>
+      <c r="T719" s="9"/>
+      <c r="U719" s="9"/>
+      <c r="V719" s="9"/>
+      <c r="W719" s="9"/>
+      <c r="X719" s="9"/>
+      <c r="Y719" s="9"/>
     </row>
     <row r="720" spans="1:25" ht="15.75" customHeight="1">
       <c r="A720" t="s">
         <v>3995</v>
       </c>
       <c r="C720" t="s">
-        <v>3732</v>
+        <v>3996</v>
       </c>
       <c r="D720">
-        <v>1860</v>
+        <v>1867</v>
       </c>
       <c r="E720">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="F720" t="s">
-        <v>4000</v>
+        <v>3671</v>
       </c>
       <c r="G720" t="s">
         <v>3178</v>
       </c>
       <c r="H720" t="s">
-        <v>4001</v>
+        <v>3997</v>
       </c>
       <c r="I720" t="s">
-        <v>4002</v>
+        <v>3998</v>
       </c>
       <c r="J720" t="s">
-        <v>4003</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="721" spans="1:25" ht="15.75" customHeight="1">
       <c r="A721" t="s">
+        <v>3995</v>
+      </c>
+      <c r="C721" t="s">
+        <v>3732</v>
+      </c>
+      <c r="D721">
+        <v>1860</v>
+      </c>
+      <c r="E721">
+        <v>1930</v>
+      </c>
+      <c r="F721" t="s">
+        <v>4000</v>
+      </c>
+      <c r="G721" t="s">
+        <v>3178</v>
+      </c>
+      <c r="H721" t="s">
+        <v>4001</v>
+      </c>
+      <c r="I721" t="s">
+        <v>4002</v>
+      </c>
+      <c r="J721" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="722" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A722" t="s">
         <v>3428</v>
       </c>
-      <c r="C721" t="s">
+      <c r="C722" t="s">
         <v>161</v>
       </c>
-      <c r="D721">
+      <c r="D722">
         <v>1847</v>
       </c>
-      <c r="E721">
+      <c r="E722">
         <v>1912</v>
       </c>
-      <c r="F721" t="s">
+      <c r="F722" t="s">
         <v>3429</v>
       </c>
-      <c r="G721" t="s">
+      <c r="G722" t="s">
         <v>3430</v>
       </c>
-      <c r="H721" s="135" t="s">
+      <c r="H722" s="135" t="s">
         <v>3431</v>
       </c>
-      <c r="I721" s="124" t="s">
+      <c r="I722" s="124" t="s">
         <v>3432</v>
       </c>
-      <c r="J721" s="15" t="s">
+      <c r="J722" s="15" t="s">
         <v>3433</v>
       </c>
     </row>
-    <row r="722" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A722" s="22" t="s">
+    <row r="723" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A723" s="22" t="s">
         <v>2495</v>
       </c>
-      <c r="B722" s="22" t="s">
+      <c r="B723" s="22" t="s">
         <v>2496</v>
       </c>
-      <c r="C722" s="22" t="s">
+      <c r="C723" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D722" s="22">
+      <c r="D723" s="22">
         <v>1855</v>
       </c>
-      <c r="E722" s="22">
+      <c r="E723" s="22">
         <v>1931</v>
       </c>
-      <c r="F722" s="22" t="s">
+      <c r="F723" s="22" t="s">
         <v>2497</v>
       </c>
-      <c r="G722" s="22" t="s">
+      <c r="G723" s="22" t="s">
         <v>2498</v>
       </c>
-      <c r="H722" s="23" t="s">
+      <c r="H723" s="23" t="s">
         <v>2499</v>
       </c>
-      <c r="I722" s="108" t="s">
+      <c r="I723" s="108" t="s">
         <v>2500</v>
       </c>
-      <c r="J722" s="22" t="s">
+      <c r="J723" s="22" t="s">
         <v>2501</v>
       </c>
-      <c r="K722" s="9"/>
-      <c r="L722" s="9"/>
-      <c r="M722" s="9"/>
-      <c r="N722" s="9"/>
-      <c r="O722" s="9"/>
-      <c r="P722" s="9"/>
-      <c r="Q722" s="9"/>
-      <c r="R722" s="9"/>
-      <c r="S722" s="9"/>
-      <c r="T722" s="9"/>
-      <c r="U722" s="9"/>
-      <c r="V722" s="9"/>
-      <c r="W722" s="9"/>
-      <c r="X722" s="9"/>
-      <c r="Y722" s="9"/>
-    </row>
-    <row r="723" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A723" s="25" t="s">
+      <c r="K723" s="9"/>
+      <c r="L723" s="9"/>
+      <c r="M723" s="9"/>
+      <c r="N723" s="9"/>
+      <c r="O723" s="9"/>
+      <c r="P723" s="9"/>
+      <c r="Q723" s="9"/>
+      <c r="R723" s="9"/>
+      <c r="S723" s="9"/>
+      <c r="T723" s="9"/>
+      <c r="U723" s="9"/>
+      <c r="V723" s="9"/>
+      <c r="W723" s="9"/>
+      <c r="X723" s="9"/>
+      <c r="Y723" s="9"/>
+    </row>
+    <row r="724" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A724" s="25" t="s">
         <v>2502</v>
       </c>
-      <c r="B723" s="26" t="s">
+      <c r="B724" s="26" t="s">
         <v>2503</v>
       </c>
-      <c r="C723" s="25" t="s">
+      <c r="C724" s="25" t="s">
         <v>432</v>
       </c>
-      <c r="D723" s="25">
+      <c r="D724" s="25">
         <v>1823</v>
       </c>
-      <c r="E723" s="25">
+      <c r="E724" s="25">
         <v>1904</v>
       </c>
-      <c r="F723" s="48" t="s">
+      <c r="F724" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="G723" s="48" t="s">
+      <c r="G724" s="48" t="s">
         <v>1584</v>
       </c>
-      <c r="H723" s="26" t="s">
+      <c r="H724" s="26" t="s">
         <v>2504</v>
       </c>
-      <c r="I723" s="184" t="s">
+      <c r="I724" s="184" t="s">
         <v>2505</v>
       </c>
-      <c r="J723" s="25" t="s">
+      <c r="J724" s="25" t="s">
         <v>2506</v>
       </c>
-      <c r="K723" s="25"/>
-      <c r="L723" s="25"/>
-      <c r="M723" s="25"/>
-      <c r="N723" s="25"/>
-      <c r="O723" s="25"/>
-      <c r="P723" s="25"/>
-      <c r="Q723" s="25"/>
-      <c r="R723" s="25"/>
-      <c r="S723" s="25"/>
-      <c r="T723" s="25"/>
-      <c r="U723" s="25"/>
-      <c r="V723" s="25"/>
-      <c r="W723" s="25"/>
-      <c r="X723" s="25"/>
-      <c r="Y723" s="25"/>
-    </row>
-    <row r="724" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A724" s="13" t="s">
+      <c r="K724" s="25"/>
+      <c r="L724" s="25"/>
+      <c r="M724" s="25"/>
+      <c r="N724" s="25"/>
+      <c r="O724" s="25"/>
+      <c r="P724" s="25"/>
+      <c r="Q724" s="25"/>
+      <c r="R724" s="25"/>
+      <c r="S724" s="25"/>
+      <c r="T724" s="25"/>
+      <c r="U724" s="25"/>
+      <c r="V724" s="25"/>
+      <c r="W724" s="25"/>
+      <c r="X724" s="25"/>
+      <c r="Y724" s="25"/>
+    </row>
+    <row r="725" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A725" s="13" t="s">
         <v>2507</v>
       </c>
-      <c r="B724" s="1"/>
-      <c r="C724" s="1" t="s">
+      <c r="B725" s="1"/>
+      <c r="C725" s="1" t="s">
         <v>2508</v>
       </c>
-      <c r="D724" s="1">
+      <c r="D725" s="1">
         <v>1815</v>
       </c>
-      <c r="E724" s="1">
+      <c r="E725" s="1">
         <v>1905</v>
       </c>
-      <c r="F724" s="1" t="s">
+      <c r="F725" s="1" t="s">
         <v>2509</v>
       </c>
-      <c r="G724" s="1" t="s">
+      <c r="G725" s="1" t="s">
         <v>2510</v>
       </c>
-      <c r="H724" s="1" t="s">
+      <c r="H725" s="1" t="s">
         <v>2511</v>
       </c>
-      <c r="I724" s="15" t="s">
+      <c r="I725" s="15" t="s">
         <v>2512</v>
       </c>
-      <c r="J724" s="1" t="s">
+      <c r="J725" s="1" t="s">
         <v>2513</v>
-      </c>
-      <c r="K724" s="1"/>
-      <c r="L724" s="1"/>
-      <c r="M724" s="1"/>
-      <c r="N724" s="1"/>
-      <c r="O724" s="1"/>
-      <c r="P724" s="1"/>
-      <c r="Q724" s="1"/>
-      <c r="R724" s="1"/>
-      <c r="S724" s="1"/>
-      <c r="T724" s="1"/>
-      <c r="U724" s="1"/>
-      <c r="V724" s="1"/>
-      <c r="W724" s="1"/>
-      <c r="X724" s="1"/>
-      <c r="Y724" s="1"/>
-    </row>
-    <row r="725" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A725" s="10" t="s">
-        <v>2520</v>
-      </c>
-      <c r="B725" s="10" t="s">
-        <v>2521</v>
-      </c>
-      <c r="C725" s="10" t="s">
-        <v>2522</v>
-      </c>
-      <c r="D725" s="10">
-        <v>1630</v>
-      </c>
-      <c r="E725" s="10">
-        <v>1685</v>
-      </c>
-      <c r="F725" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="G725" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="H725" s="10" t="s">
-        <v>2523</v>
-      </c>
-      <c r="I725" s="31" t="s">
-        <v>2524</v>
-      </c>
-      <c r="J725" s="10" t="s">
-        <v>2525</v>
       </c>
       <c r="K725" s="1"/>
       <c r="L725" s="1"/>
@@ -43771,35 +43770,35 @@
       <c r="Y725" s="1"/>
     </row>
     <row r="726" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A726" s="1" t="s">
-        <v>2514</v>
-      </c>
-      <c r="B726" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C726" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D726" s="1">
-        <v>1859</v>
-      </c>
-      <c r="E726" s="1" t="s">
-        <v>2515</v>
-      </c>
-      <c r="F726" s="1" t="s">
-        <v>2516</v>
-      </c>
-      <c r="G726" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H726" s="1" t="s">
-        <v>2517</v>
-      </c>
-      <c r="I726" s="4" t="s">
-        <v>2518</v>
-      </c>
-      <c r="J726" s="1" t="s">
-        <v>2519</v>
+      <c r="A726" s="10" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B726" s="10" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C726" s="10" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D726" s="10">
+        <v>1630</v>
+      </c>
+      <c r="E726" s="10">
+        <v>1685</v>
+      </c>
+      <c r="F726" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="G726" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H726" s="10" t="s">
+        <v>2523</v>
+      </c>
+      <c r="I726" s="31" t="s">
+        <v>2524</v>
+      </c>
+      <c r="J726" s="10" t="s">
+        <v>2525</v>
       </c>
       <c r="K726" s="1"/>
       <c r="L726" s="1"/>
@@ -43818,35 +43817,35 @@
       <c r="Y726" s="1"/>
     </row>
     <row r="727" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A727" s="10" t="s">
-        <v>2526</v>
-      </c>
-      <c r="B727" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C727" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D727" s="10">
-        <v>1830</v>
-      </c>
-      <c r="E727" s="10">
-        <v>1909</v>
-      </c>
-      <c r="F727" s="10" t="s">
-        <v>2527</v>
-      </c>
-      <c r="G727" s="10" t="s">
-        <v>2528</v>
-      </c>
-      <c r="H727" s="10" t="s">
-        <v>2529</v>
-      </c>
-      <c r="I727" s="21" t="s">
-        <v>2530</v>
-      </c>
-      <c r="J727" s="10" t="s">
-        <v>2531</v>
+      <c r="A727" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C727" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D727" s="1">
+        <v>1859</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>2515</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>2516</v>
+      </c>
+      <c r="G727" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H727" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="I727" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="J727" s="1" t="s">
+        <v>2519</v>
       </c>
       <c r="K727" s="1"/>
       <c r="L727" s="1"/>
@@ -43865,433 +43864,435 @@
       <c r="Y727" s="1"/>
     </row>
     <row r="728" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A728" t="s">
+      <c r="A728" s="10" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B728" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C728" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D728" s="10">
+        <v>1830</v>
+      </c>
+      <c r="E728" s="10">
+        <v>1909</v>
+      </c>
+      <c r="F728" s="10" t="s">
+        <v>2527</v>
+      </c>
+      <c r="G728" s="10" t="s">
+        <v>2528</v>
+      </c>
+      <c r="H728" s="10" t="s">
+        <v>2529</v>
+      </c>
+      <c r="I728" s="21" t="s">
+        <v>2530</v>
+      </c>
+      <c r="J728" s="10" t="s">
+        <v>2531</v>
+      </c>
+      <c r="K728" s="1"/>
+      <c r="L728" s="1"/>
+      <c r="M728" s="1"/>
+      <c r="N728" s="1"/>
+      <c r="O728" s="1"/>
+      <c r="P728" s="1"/>
+      <c r="Q728" s="1"/>
+      <c r="R728" s="1"/>
+      <c r="S728" s="1"/>
+      <c r="T728" s="1"/>
+      <c r="U728" s="1"/>
+      <c r="V728" s="1"/>
+      <c r="W728" s="1"/>
+      <c r="X728" s="1"/>
+      <c r="Y728" s="1"/>
+    </row>
+    <row r="729" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A729" t="s">
         <v>4004</v>
       </c>
-      <c r="B728" t="s">
+      <c r="B729" t="s">
         <v>653</v>
       </c>
-      <c r="C728" t="s">
+      <c r="C729" t="s">
         <v>161</v>
       </c>
-      <c r="D728">
+      <c r="D729">
         <v>1831</v>
       </c>
-      <c r="E728">
+      <c r="E729">
         <v>1914</v>
       </c>
-      <c r="F728" t="s">
+      <c r="F729" t="s">
         <v>573</v>
       </c>
-      <c r="G728" t="s">
+      <c r="G729" t="s">
         <v>20</v>
       </c>
-      <c r="H728" t="s">
+      <c r="H729" t="s">
         <v>4005</v>
       </c>
-      <c r="I728" t="s">
+      <c r="I729" t="s">
         <v>4006</v>
       </c>
-      <c r="J728" t="s">
+      <c r="J729" t="s">
         <v>4007</v>
       </c>
     </row>
-    <row r="729" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A729" s="10" t="s">
+    <row r="730" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A730" s="10" t="s">
         <v>2532</v>
       </c>
-      <c r="B729" s="10" t="s">
+      <c r="B730" s="10" t="s">
         <v>2533</v>
       </c>
-      <c r="C729" s="10" t="s">
+      <c r="C730" s="10" t="s">
         <v>2534</v>
       </c>
-      <c r="D729" s="10">
+      <c r="D730" s="10">
         <v>1849</v>
       </c>
-      <c r="E729" s="10">
+      <c r="E730" s="10">
         <v>1935</v>
       </c>
-      <c r="F729" s="10" t="s">
+      <c r="F730" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G729" s="10" t="s">
+      <c r="G730" s="10" t="s">
         <v>2535</v>
       </c>
-      <c r="H729" s="109" t="s">
+      <c r="H730" s="109" t="s">
         <v>2536</v>
       </c>
-      <c r="I729" s="50" t="s">
+      <c r="I730" s="50" t="s">
         <v>2537</v>
       </c>
-      <c r="J729" s="10" t="s">
+      <c r="J730" s="10" t="s">
         <v>2538</v>
       </c>
-      <c r="K729" s="1"/>
-      <c r="L729" s="1"/>
-      <c r="M729" s="1"/>
-      <c r="N729" s="1"/>
-      <c r="O729" s="1"/>
-      <c r="P729" s="1"/>
-      <c r="Q729" s="1"/>
-      <c r="R729" s="1"/>
-      <c r="S729" s="1"/>
-      <c r="T729" s="1"/>
-      <c r="U729" s="1"/>
-      <c r="V729" s="1"/>
-      <c r="W729" s="1"/>
-      <c r="X729" s="1"/>
-      <c r="Y729" s="1"/>
-    </row>
-    <row r="730" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A730" t="s">
+      <c r="K730" s="1"/>
+      <c r="L730" s="1"/>
+      <c r="M730" s="1"/>
+      <c r="N730" s="1"/>
+      <c r="O730" s="1"/>
+      <c r="P730" s="1"/>
+      <c r="Q730" s="1"/>
+      <c r="R730" s="1"/>
+      <c r="S730" s="1"/>
+      <c r="T730" s="1"/>
+      <c r="U730" s="1"/>
+      <c r="V730" s="1"/>
+      <c r="W730" s="1"/>
+      <c r="X730" s="1"/>
+      <c r="Y730" s="1"/>
+    </row>
+    <row r="731" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A731" t="s">
         <v>3434</v>
       </c>
-      <c r="C730" t="s">
+      <c r="C731" t="s">
         <v>3435</v>
       </c>
-      <c r="D730">
+      <c r="D731">
         <v>1870</v>
       </c>
-      <c r="E730">
+      <c r="E731">
         <v>1917</v>
       </c>
-      <c r="F730" t="s">
+      <c r="F731" t="s">
         <v>3436</v>
       </c>
-      <c r="G730" t="s">
+      <c r="G731" t="s">
         <v>573</v>
       </c>
-      <c r="H730" s="135" t="s">
+      <c r="H731" s="135" t="s">
         <v>3437</v>
       </c>
-      <c r="I730" t="s">
+      <c r="I731" t="s">
         <v>3438</v>
       </c>
-      <c r="J730" t="s">
+      <c r="J731" t="s">
         <v>3439</v>
       </c>
     </row>
-    <row r="731" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A731" s="2" t="s">
+    <row r="732" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A732" s="2" t="s">
         <v>2539</v>
       </c>
-      <c r="B731" s="2" t="s">
+      <c r="B732" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C731" s="2" t="s">
+      <c r="C732" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D731" s="2">
+      <c r="D732" s="2">
         <v>1819</v>
       </c>
-      <c r="E731" s="2">
+      <c r="E732" s="2">
         <v>1895</v>
       </c>
-      <c r="F731" s="2" t="s">
+      <c r="F732" s="2" t="s">
         <v>2540</v>
       </c>
-      <c r="G731" s="2" t="s">
+      <c r="G732" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H731" s="2" t="s">
+      <c r="H732" s="2" t="s">
         <v>2541</v>
       </c>
-      <c r="I731" s="3" t="s">
+      <c r="I732" s="3" t="s">
         <v>2542</v>
       </c>
-      <c r="J731" s="2" t="s">
+      <c r="J732" s="2" t="s">
         <v>2543</v>
       </c>
-      <c r="K731" s="1"/>
-      <c r="L731" s="1"/>
-      <c r="M731" s="1"/>
-      <c r="N731" s="1"/>
-      <c r="O731" s="1"/>
-      <c r="P731" s="1"/>
-      <c r="Q731" s="1"/>
-      <c r="R731" s="1"/>
-      <c r="S731" s="1"/>
-      <c r="T731" s="1"/>
-      <c r="U731" s="1"/>
-      <c r="V731" s="1"/>
-      <c r="W731" s="1"/>
-      <c r="X731" s="1"/>
-      <c r="Y731" s="1"/>
-    </row>
-    <row r="732" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A732" t="s">
+      <c r="K732" s="1"/>
+      <c r="L732" s="1"/>
+      <c r="M732" s="1"/>
+      <c r="N732" s="1"/>
+      <c r="O732" s="1"/>
+      <c r="P732" s="1"/>
+      <c r="Q732" s="1"/>
+      <c r="R732" s="1"/>
+      <c r="S732" s="1"/>
+      <c r="T732" s="1"/>
+      <c r="U732" s="1"/>
+      <c r="V732" s="1"/>
+      <c r="W732" s="1"/>
+      <c r="X732" s="1"/>
+      <c r="Y732" s="1"/>
+    </row>
+    <row r="733" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A733" t="s">
         <v>3440</v>
       </c>
-      <c r="C732" t="s">
+      <c r="C733" t="s">
         <v>3441</v>
       </c>
-      <c r="D732">
+      <c r="D733">
         <v>1863</v>
       </c>
-      <c r="E732">
+      <c r="E733">
         <v>1925</v>
       </c>
-      <c r="F732" t="s">
+      <c r="F733" t="s">
         <v>3442</v>
       </c>
-      <c r="G732" t="s">
+      <c r="G733" t="s">
         <v>2089</v>
       </c>
-      <c r="H732" s="136" t="s">
+      <c r="H733" s="136" t="s">
         <v>3443</v>
       </c>
-      <c r="I732" t="s">
+      <c r="I733" t="s">
         <v>3444</v>
       </c>
-      <c r="J732" t="s">
+      <c r="J733" t="s">
         <v>3445</v>
       </c>
     </row>
-    <row r="733" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A733" s="10" t="s">
+    <row r="734" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A734" s="10" t="s">
         <v>2544</v>
       </c>
-      <c r="B733" s="10"/>
-      <c r="C733" s="10" t="s">
+      <c r="B734" s="10"/>
+      <c r="C734" s="10" t="s">
         <v>2545</v>
       </c>
-      <c r="D733" s="10">
+      <c r="D734" s="10">
         <v>1730</v>
       </c>
-      <c r="E733" s="10">
+      <c r="E734" s="10">
         <v>1800</v>
       </c>
-      <c r="F733" s="10" t="s">
+      <c r="F734" s="10" t="s">
         <v>2546</v>
       </c>
-      <c r="G733" s="10" t="s">
+      <c r="G734" s="10" t="s">
         <v>2547</v>
       </c>
-      <c r="H733" s="10" t="s">
+      <c r="H734" s="10" t="s">
         <v>2548</v>
       </c>
-      <c r="I733" s="47" t="s">
+      <c r="I734" s="47" t="s">
         <v>2549</v>
       </c>
-      <c r="J733" s="10" t="s">
+      <c r="J734" s="10" t="s">
         <v>2550</v>
       </c>
-      <c r="K733" s="1"/>
-      <c r="L733" s="1"/>
-      <c r="M733" s="1"/>
-      <c r="N733" s="1"/>
-      <c r="O733" s="1"/>
-      <c r="P733" s="1"/>
-      <c r="Q733" s="1"/>
-      <c r="R733" s="1"/>
-      <c r="S733" s="1"/>
-      <c r="T733" s="1"/>
-      <c r="U733" s="1"/>
-      <c r="V733" s="1"/>
-      <c r="W733" s="1"/>
-      <c r="X733" s="1"/>
-      <c r="Y733" s="1"/>
-    </row>
-    <row r="734" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A734" t="s">
+      <c r="K734" s="1"/>
+      <c r="L734" s="1"/>
+      <c r="M734" s="1"/>
+      <c r="N734" s="1"/>
+      <c r="O734" s="1"/>
+      <c r="P734" s="1"/>
+      <c r="Q734" s="1"/>
+      <c r="R734" s="1"/>
+      <c r="S734" s="1"/>
+      <c r="T734" s="1"/>
+      <c r="U734" s="1"/>
+      <c r="V734" s="1"/>
+      <c r="W734" s="1"/>
+      <c r="X734" s="1"/>
+      <c r="Y734" s="1"/>
+    </row>
+    <row r="735" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A735" t="s">
         <v>3446</v>
       </c>
-      <c r="C734" t="s">
+      <c r="C735" t="s">
         <v>3447</v>
       </c>
-      <c r="D734">
+      <c r="D735">
         <v>1873</v>
       </c>
-      <c r="E734">
+      <c r="E735">
         <v>1933</v>
       </c>
-      <c r="F734" t="s">
+      <c r="F735" t="s">
         <v>52</v>
       </c>
-      <c r="G734" t="s">
+      <c r="G735" t="s">
         <v>52</v>
       </c>
-      <c r="H734" s="135" t="s">
+      <c r="H735" s="135" t="s">
         <v>3448</v>
       </c>
-      <c r="I734" t="s">
+      <c r="I735" t="s">
         <v>3449</v>
       </c>
-      <c r="J734" t="s">
+      <c r="J735" t="s">
         <v>3450</v>
       </c>
     </row>
-    <row r="735" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A735" s="2" t="s">
+    <row r="736" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A736" s="2" t="s">
         <v>2551</v>
       </c>
-      <c r="B735" s="2" t="s">
+      <c r="B736" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C735" s="2" t="s">
+      <c r="C736" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D735" s="2"/>
-      <c r="E735" s="2"/>
-      <c r="F735" s="2"/>
-      <c r="G735" s="2"/>
-      <c r="H735" s="2" t="s">
+      <c r="D736" s="2"/>
+      <c r="E736" s="2"/>
+      <c r="F736" s="2"/>
+      <c r="G736" s="2"/>
+      <c r="H736" s="2" t="s">
         <v>2552</v>
       </c>
-      <c r="I735" s="18"/>
-      <c r="J735" s="2" t="s">
+      <c r="I736" s="18"/>
+      <c r="J736" s="2" t="s">
         <v>2553</v>
       </c>
-      <c r="K735" s="1"/>
-      <c r="L735" s="1"/>
-      <c r="M735" s="1"/>
-      <c r="N735" s="1"/>
-      <c r="O735" s="1"/>
-      <c r="P735" s="1"/>
-      <c r="Q735" s="1"/>
-      <c r="R735" s="1"/>
-      <c r="S735" s="1"/>
-      <c r="T735" s="1"/>
-      <c r="U735" s="1"/>
-      <c r="V735" s="1"/>
-      <c r="W735" s="1"/>
-      <c r="X735" s="1"/>
-      <c r="Y735" s="1"/>
-    </row>
-    <row r="736" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A736" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C736" t="s">
-        <v>432</v>
-      </c>
-      <c r="D736">
-        <v>1857</v>
-      </c>
-      <c r="E736">
-        <v>1942</v>
-      </c>
-      <c r="G736" t="s">
-        <v>122</v>
-      </c>
-      <c r="H736" s="135" t="s">
-        <v>3451</v>
-      </c>
-      <c r="I736" t="s">
-        <v>3452</v>
-      </c>
-      <c r="J736" s="15" t="s">
-        <v>3453</v>
-      </c>
+      <c r="K736" s="1"/>
+      <c r="L736" s="1"/>
+      <c r="M736" s="1"/>
+      <c r="N736" s="1"/>
+      <c r="O736" s="1"/>
+      <c r="P736" s="1"/>
+      <c r="Q736" s="1"/>
+      <c r="R736" s="1"/>
+      <c r="S736" s="1"/>
+      <c r="T736" s="1"/>
+      <c r="U736" s="1"/>
+      <c r="V736" s="1"/>
+      <c r="W736" s="1"/>
+      <c r="X736" s="1"/>
+      <c r="Y736" s="1"/>
     </row>
     <row r="737" spans="1:25" ht="15.75" customHeight="1">
       <c r="A737" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C737" t="s">
+        <v>432</v>
+      </c>
+      <c r="D737">
+        <v>1857</v>
+      </c>
+      <c r="E737">
+        <v>1942</v>
+      </c>
+      <c r="G737" t="s">
+        <v>122</v>
+      </c>
+      <c r="H737" s="135" t="s">
+        <v>3451</v>
+      </c>
+      <c r="I737" t="s">
+        <v>3452</v>
+      </c>
+      <c r="J737" s="15" t="s">
+        <v>3453</v>
+      </c>
+    </row>
+    <row r="738" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A738" t="s">
         <v>3454</v>
       </c>
-      <c r="B737" t="s">
+      <c r="B738" t="s">
         <v>50</v>
       </c>
-      <c r="C737" t="s">
+      <c r="C738" t="s">
         <v>661</v>
       </c>
-      <c r="D737">
+      <c r="D738">
         <v>1854</v>
       </c>
-      <c r="E737">
+      <c r="E738">
         <v>1944</v>
       </c>
-      <c r="F737" t="s">
+      <c r="F738" t="s">
         <v>20</v>
       </c>
-      <c r="G737" t="s">
+      <c r="G738" t="s">
         <v>3455</v>
       </c>
-      <c r="H737" s="136" t="s">
+      <c r="H738" s="136" t="s">
         <v>3456</v>
       </c>
-      <c r="I737" t="s">
+      <c r="I738" t="s">
         <v>3457</v>
       </c>
-      <c r="J737" s="15" t="s">
+      <c r="J738" s="15" t="s">
         <v>3458</v>
       </c>
-    </row>
-    <row r="738" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A738" s="2" t="s">
-        <v>2554</v>
-      </c>
-      <c r="B738" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C738" s="2" t="s">
-        <v>2555</v>
-      </c>
-      <c r="D738" s="2">
-        <v>1832</v>
-      </c>
-      <c r="E738" s="2">
-        <v>1905</v>
-      </c>
-      <c r="F738" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G738" s="2" t="s">
-        <v>2556</v>
-      </c>
-      <c r="H738" s="2" t="s">
-        <v>2557</v>
-      </c>
-      <c r="I738" s="54" t="s">
-        <v>2558</v>
-      </c>
-      <c r="J738" s="2" t="s">
-        <v>2559</v>
-      </c>
-      <c r="K738" s="1"/>
-      <c r="L738" s="1"/>
-      <c r="M738" s="1"/>
-      <c r="N738" s="1"/>
-      <c r="O738" s="1"/>
-      <c r="P738" s="1"/>
-      <c r="Q738" s="1"/>
-      <c r="R738" s="1"/>
-      <c r="S738" s="1"/>
-      <c r="T738" s="1"/>
-      <c r="U738" s="1"/>
-      <c r="V738" s="1"/>
-      <c r="W738" s="1"/>
-      <c r="X738" s="1"/>
-      <c r="Y738" s="1"/>
     </row>
     <row r="739" spans="1:25" ht="15.75" customHeight="1">
       <c r="A739" s="2" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
       <c r="D739" s="2">
-        <v>1858</v>
+        <v>1832</v>
       </c>
       <c r="E739" s="2">
-        <v>1926</v>
+        <v>1905</v>
       </c>
       <c r="F739" s="2" t="s">
-        <v>2562</v>
+        <v>144</v>
       </c>
       <c r="G739" s="2" t="s">
-        <v>2563</v>
+        <v>2556</v>
       </c>
       <c r="H739" s="2" t="s">
-        <v>2564</v>
-      </c>
-      <c r="I739" s="110"/>
+        <v>2557</v>
+      </c>
+      <c r="I739" s="54" t="s">
+        <v>2558</v>
+      </c>
       <c r="J739" s="2" t="s">
-        <v>2565</v>
+        <v>2559</v>
       </c>
       <c r="K739" s="1"/>
       <c r="L739" s="1"/>
@@ -44310,110 +44311,110 @@
       <c r="Y739" s="1"/>
     </row>
     <row r="740" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A740" t="s">
+      <c r="A740" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D740" s="2">
+        <v>1858</v>
+      </c>
+      <c r="E740" s="2">
+        <v>1926</v>
+      </c>
+      <c r="F740" s="2" t="s">
+        <v>2562</v>
+      </c>
+      <c r="G740" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="H740" s="2" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I740" s="110"/>
+      <c r="J740" s="2" t="s">
+        <v>2565</v>
+      </c>
+      <c r="K740" s="1"/>
+      <c r="L740" s="1"/>
+      <c r="M740" s="1"/>
+      <c r="N740" s="1"/>
+      <c r="O740" s="1"/>
+      <c r="P740" s="1"/>
+      <c r="Q740" s="1"/>
+      <c r="R740" s="1"/>
+      <c r="S740" s="1"/>
+      <c r="T740" s="1"/>
+      <c r="U740" s="1"/>
+      <c r="V740" s="1"/>
+      <c r="W740" s="1"/>
+      <c r="X740" s="1"/>
+      <c r="Y740" s="1"/>
+    </row>
+    <row r="741" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A741" t="s">
         <v>4008</v>
       </c>
-      <c r="B740" t="s">
+      <c r="B741" t="s">
         <v>18</v>
       </c>
-      <c r="C740" t="s">
+      <c r="C741" t="s">
         <v>4009</v>
       </c>
-      <c r="D740">
+      <c r="D741">
         <v>1857</v>
       </c>
-      <c r="E740">
+      <c r="E741">
         <v>1926</v>
       </c>
-      <c r="F740" t="s">
+      <c r="F741" t="s">
         <v>4010</v>
       </c>
-      <c r="G740" t="s">
+      <c r="G741" t="s">
         <v>4011</v>
       </c>
-      <c r="H740" t="s">
+      <c r="H741" t="s">
         <v>4012</v>
       </c>
-      <c r="I740" t="s">
+      <c r="I741" t="s">
         <v>4013</v>
       </c>
-      <c r="J740" t="s">
+      <c r="J741" t="s">
         <v>4014</v>
       </c>
-    </row>
-    <row r="741" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A741" s="1" t="s">
-        <v>2566</v>
-      </c>
-      <c r="B741" s="1"/>
-      <c r="C741" s="1" t="s">
-        <v>2567</v>
-      </c>
-      <c r="D741" s="1">
-        <v>1843</v>
-      </c>
-      <c r="E741" s="1">
-        <v>1915</v>
-      </c>
-      <c r="F741" s="1" t="s">
-        <v>2568</v>
-      </c>
-      <c r="G741" s="1" t="s">
-        <v>2569</v>
-      </c>
-      <c r="H741" s="1" t="s">
-        <v>2570</v>
-      </c>
-      <c r="I741" s="17" t="s">
-        <v>2571</v>
-      </c>
-      <c r="J741" s="1" t="s">
-        <v>2572</v>
-      </c>
-      <c r="K741" s="1"/>
-      <c r="L741" s="1"/>
-      <c r="M741" s="1"/>
-      <c r="N741" s="1"/>
-      <c r="O741" s="1"/>
-      <c r="P741" s="1"/>
-      <c r="Q741" s="1"/>
-      <c r="R741" s="1"/>
-      <c r="S741" s="1"/>
-      <c r="T741" s="1"/>
-      <c r="U741" s="1"/>
-      <c r="V741" s="1"/>
-      <c r="W741" s="1"/>
-      <c r="X741" s="1"/>
-      <c r="Y741" s="1"/>
     </row>
     <row r="742" spans="1:25" ht="15.75" customHeight="1">
       <c r="A742" s="1" t="s">
-        <v>2573</v>
-      </c>
-      <c r="B742" s="1" t="s">
-        <v>50</v>
-      </c>
+        <v>2566</v>
+      </c>
+      <c r="B742" s="1"/>
       <c r="C742" s="1" t="s">
-        <v>2574</v>
-      </c>
-      <c r="D742" s="168">
-        <v>1865</v>
-      </c>
-      <c r="E742" s="168">
-        <v>1933</v>
-      </c>
-      <c r="F742" s="168" t="s">
-        <v>2575</v>
-      </c>
-      <c r="G742" s="168" t="s">
-        <v>82</v>
+        <v>2567</v>
+      </c>
+      <c r="D742" s="1">
+        <v>1843</v>
+      </c>
+      <c r="E742" s="1">
+        <v>1915</v>
+      </c>
+      <c r="F742" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="G742" s="1" t="s">
+        <v>2569</v>
       </c>
       <c r="H742" s="1" t="s">
-        <v>2576</v>
-      </c>
-      <c r="I742" s="1"/>
+        <v>2570</v>
+      </c>
+      <c r="I742" s="17" t="s">
+        <v>2571</v>
+      </c>
       <c r="J742" s="1" t="s">
-        <v>2577</v>
+        <v>2572</v>
       </c>
       <c r="K742" s="1"/>
       <c r="L742" s="1"/>
@@ -44432,33 +44433,33 @@
       <c r="Y742" s="1"/>
     </row>
     <row r="743" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A743" s="2" t="s">
-        <v>2578</v>
-      </c>
-      <c r="B743" s="2"/>
-      <c r="C743" s="2" t="s">
-        <v>2579</v>
-      </c>
-      <c r="D743" s="26">
-        <v>1818</v>
-      </c>
-      <c r="E743" s="26">
-        <v>1900</v>
-      </c>
-      <c r="F743" s="26" t="s">
-        <v>2580</v>
-      </c>
-      <c r="G743" s="26" t="s">
-        <v>2581</v>
-      </c>
-      <c r="H743" s="2" t="s">
-        <v>2582</v>
-      </c>
-      <c r="I743" s="98" t="s">
-        <v>2583</v>
-      </c>
-      <c r="J743" s="2" t="s">
-        <v>2584</v>
+      <c r="A743" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D743" s="168">
+        <v>1865</v>
+      </c>
+      <c r="E743" s="168">
+        <v>1933</v>
+      </c>
+      <c r="F743" s="168" t="s">
+        <v>2575</v>
+      </c>
+      <c r="G743" s="168" t="s">
+        <v>82</v>
+      </c>
+      <c r="H743" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="I743" s="1"/>
+      <c r="J743" s="1" t="s">
+        <v>2577</v>
       </c>
       <c r="K743" s="1"/>
       <c r="L743" s="1"/>
@@ -44477,35 +44478,33 @@
       <c r="Y743" s="1"/>
     </row>
     <row r="744" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A744" s="10" t="s">
-        <v>2585</v>
-      </c>
-      <c r="B744" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C744" s="10" t="s">
-        <v>2586</v>
-      </c>
-      <c r="D744" s="23">
-        <v>1841</v>
-      </c>
-      <c r="E744" s="23">
-        <v>1916</v>
-      </c>
-      <c r="F744" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G744" s="23" t="s">
-        <v>2587</v>
-      </c>
-      <c r="H744" s="10" t="s">
-        <v>2588</v>
-      </c>
-      <c r="I744" s="112" t="s">
-        <v>2589</v>
-      </c>
-      <c r="J744" s="10" t="s">
-        <v>2590</v>
+      <c r="A744" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B744" s="2"/>
+      <c r="C744" s="2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="D744" s="26">
+        <v>1818</v>
+      </c>
+      <c r="E744" s="26">
+        <v>1900</v>
+      </c>
+      <c r="F744" s="26" t="s">
+        <v>2580</v>
+      </c>
+      <c r="G744" s="26" t="s">
+        <v>2581</v>
+      </c>
+      <c r="H744" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="I744" s="98" t="s">
+        <v>2583</v>
+      </c>
+      <c r="J744" s="2" t="s">
+        <v>2584</v>
       </c>
       <c r="K744" s="1"/>
       <c r="L744" s="1"/>
@@ -44524,35 +44523,35 @@
       <c r="Y744" s="1"/>
     </row>
     <row r="745" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A745" s="1" t="s">
-        <v>2591</v>
-      </c>
-      <c r="B745" s="1" t="s">
-        <v>2592</v>
-      </c>
-      <c r="C745" s="1" t="s">
-        <v>2593</v>
-      </c>
-      <c r="D745" s="1">
-        <v>1861</v>
-      </c>
-      <c r="E745" s="1">
-        <v>1941</v>
-      </c>
-      <c r="F745" s="1" t="s">
-        <v>2594</v>
-      </c>
-      <c r="G745" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H745" s="1" t="s">
-        <v>2595</v>
-      </c>
-      <c r="I745" s="15" t="s">
-        <v>2596</v>
-      </c>
-      <c r="J745" s="1" t="s">
-        <v>2597</v>
+      <c r="A745" s="10" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B745" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C745" s="10" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D745" s="23">
+        <v>1841</v>
+      </c>
+      <c r="E745" s="23">
+        <v>1916</v>
+      </c>
+      <c r="F745" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G745" s="23" t="s">
+        <v>2587</v>
+      </c>
+      <c r="H745" s="10" t="s">
+        <v>2588</v>
+      </c>
+      <c r="I745" s="112" t="s">
+        <v>2589</v>
+      </c>
+      <c r="J745" s="10" t="s">
+        <v>2590</v>
       </c>
       <c r="K745" s="1"/>
       <c r="L745" s="1"/>
@@ -44572,34 +44571,34 @@
     </row>
     <row r="746" spans="1:25" ht="15.75" customHeight="1">
       <c r="A746" s="1" t="s">
-        <v>2598</v>
+        <v>2591</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>18</v>
+        <v>2592</v>
       </c>
       <c r="C746" s="1" t="s">
-        <v>161</v>
+        <v>2593</v>
       </c>
       <c r="D746" s="1">
-        <v>1833</v>
+        <v>1861</v>
       </c>
       <c r="E746" s="1">
-        <v>1895</v>
+        <v>1941</v>
       </c>
       <c r="F746" s="1" t="s">
-        <v>20</v>
+        <v>2594</v>
       </c>
       <c r="G746" s="1" t="s">
-        <v>2599</v>
+        <v>82</v>
       </c>
       <c r="H746" s="1" t="s">
-        <v>2600</v>
-      </c>
-      <c r="I746" s="4" t="s">
-        <v>2601</v>
+        <v>2595</v>
+      </c>
+      <c r="I746" s="15" t="s">
+        <v>2596</v>
       </c>
       <c r="J746" s="1" t="s">
-        <v>2602</v>
+        <v>2597</v>
       </c>
       <c r="K746" s="1"/>
       <c r="L746" s="1"/>
@@ -44618,76 +44617,76 @@
       <c r="Y746" s="1"/>
     </row>
     <row r="747" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A747" s="113" t="s">
-        <v>2603</v>
-      </c>
-      <c r="B747" s="25"/>
-      <c r="C747" s="26" t="s">
-        <v>2604</v>
-      </c>
-      <c r="D747" s="25" t="s">
-        <v>2605</v>
-      </c>
-      <c r="E747" s="25" t="s">
-        <v>2606</v>
-      </c>
-      <c r="F747" s="25"/>
-      <c r="G747" s="25"/>
-      <c r="H747" s="26" t="s">
-        <v>2607</v>
-      </c>
-      <c r="I747" s="25" t="s">
-        <v>2608</v>
-      </c>
-      <c r="J747" s="26" t="s">
-        <v>2603</v>
-      </c>
-      <c r="K747" s="9"/>
-      <c r="L747" s="9"/>
-      <c r="M747" s="9"/>
-      <c r="N747" s="9"/>
-      <c r="O747" s="9"/>
-      <c r="P747" s="9"/>
-      <c r="Q747" s="9"/>
-      <c r="R747" s="9"/>
-      <c r="S747" s="9"/>
-      <c r="T747" s="9"/>
-      <c r="U747" s="9"/>
-      <c r="V747" s="9"/>
-      <c r="W747" s="9"/>
-      <c r="X747" s="9"/>
-      <c r="Y747" s="9"/>
+      <c r="A747" s="1" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C747" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D747" s="1">
+        <v>1833</v>
+      </c>
+      <c r="E747" s="1">
+        <v>1895</v>
+      </c>
+      <c r="F747" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G747" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="H747" s="1" t="s">
+        <v>2600</v>
+      </c>
+      <c r="I747" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="J747" s="1" t="s">
+        <v>2602</v>
+      </c>
+      <c r="K747" s="1"/>
+      <c r="L747" s="1"/>
+      <c r="M747" s="1"/>
+      <c r="N747" s="1"/>
+      <c r="O747" s="1"/>
+      <c r="P747" s="1"/>
+      <c r="Q747" s="1"/>
+      <c r="R747" s="1"/>
+      <c r="S747" s="1"/>
+      <c r="T747" s="1"/>
+      <c r="U747" s="1"/>
+      <c r="V747" s="1"/>
+      <c r="W747" s="1"/>
+      <c r="X747" s="1"/>
+      <c r="Y747" s="1"/>
     </row>
     <row r="748" spans="1:25" ht="15.75" customHeight="1">
       <c r="A748" s="113" t="s">
-        <v>2609</v>
-      </c>
-      <c r="B748" s="25" t="s">
-        <v>2145</v>
-      </c>
+        <v>2603</v>
+      </c>
+      <c r="B748" s="25"/>
       <c r="C748" s="26" t="s">
-        <v>2610</v>
-      </c>
-      <c r="D748" s="25">
-        <v>1754</v>
-      </c>
-      <c r="E748" s="25">
-        <v>1838</v>
-      </c>
-      <c r="F748" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="G748" s="25" t="s">
-        <v>298</v>
-      </c>
+        <v>2604</v>
+      </c>
+      <c r="D748" s="25" t="s">
+        <v>2605</v>
+      </c>
+      <c r="E748" s="25" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F748" s="25"/>
+      <c r="G748" s="25"/>
       <c r="H748" s="26" t="s">
-        <v>2611</v>
+        <v>2607</v>
       </c>
       <c r="I748" s="25" t="s">
-        <v>2612</v>
+        <v>2608</v>
       </c>
       <c r="J748" s="26" t="s">
-        <v>2613</v>
+        <v>2603</v>
       </c>
       <c r="K748" s="9"/>
       <c r="L748" s="9"/>
@@ -44706,78 +44705,80 @@
       <c r="Y748" s="9"/>
     </row>
     <row r="749" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A749" s="10" t="s">
-        <v>2614</v>
-      </c>
-      <c r="B749" s="10"/>
-      <c r="C749" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="D749" s="10">
-        <v>1857</v>
-      </c>
-      <c r="E749" s="10">
-        <v>1939</v>
-      </c>
-      <c r="F749" s="10" t="s">
-        <v>2615</v>
-      </c>
-      <c r="G749" s="10" t="s">
-        <v>2615</v>
-      </c>
-      <c r="H749" s="10" t="s">
-        <v>2616</v>
-      </c>
-      <c r="I749" s="11" t="s">
-        <v>2617</v>
-      </c>
-      <c r="J749" s="10" t="s">
-        <v>2618</v>
-      </c>
-      <c r="K749" s="1"/>
-      <c r="L749" s="1"/>
-      <c r="M749" s="1"/>
-      <c r="N749" s="1"/>
-      <c r="O749" s="1"/>
-      <c r="P749" s="1"/>
-      <c r="Q749" s="1"/>
-      <c r="R749" s="1"/>
-      <c r="S749" s="1"/>
-      <c r="T749" s="1"/>
-      <c r="U749" s="1"/>
-      <c r="V749" s="1"/>
-      <c r="W749" s="1"/>
-      <c r="X749" s="1"/>
-      <c r="Y749" s="1"/>
+      <c r="A749" s="113" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B749" s="25" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C749" s="26" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D749" s="25">
+        <v>1754</v>
+      </c>
+      <c r="E749" s="25">
+        <v>1838</v>
+      </c>
+      <c r="F749" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="G749" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="H749" s="26" t="s">
+        <v>2611</v>
+      </c>
+      <c r="I749" s="25" t="s">
+        <v>2612</v>
+      </c>
+      <c r="J749" s="26" t="s">
+        <v>2613</v>
+      </c>
+      <c r="K749" s="9"/>
+      <c r="L749" s="9"/>
+      <c r="M749" s="9"/>
+      <c r="N749" s="9"/>
+      <c r="O749" s="9"/>
+      <c r="P749" s="9"/>
+      <c r="Q749" s="9"/>
+      <c r="R749" s="9"/>
+      <c r="S749" s="9"/>
+      <c r="T749" s="9"/>
+      <c r="U749" s="9"/>
+      <c r="V749" s="9"/>
+      <c r="W749" s="9"/>
+      <c r="X749" s="9"/>
+      <c r="Y749" s="9"/>
     </row>
     <row r="750" spans="1:25" ht="15.75" customHeight="1">
       <c r="A750" s="10" t="s">
-        <v>3542</v>
-      </c>
-      <c r="B750" s="10" t="s">
-        <v>2271</v>
-      </c>
+        <v>2614</v>
+      </c>
+      <c r="B750" s="10"/>
       <c r="C750" s="10" t="s">
-        <v>3543</v>
+        <v>551</v>
       </c>
       <c r="D750" s="10">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="E750" s="10">
-        <v>1934</v>
-      </c>
-      <c r="F750" s="10"/>
+        <v>1939</v>
+      </c>
+      <c r="F750" s="10" t="s">
+        <v>2615</v>
+      </c>
       <c r="G750" s="10" t="s">
-        <v>2273</v>
+        <v>2615</v>
       </c>
       <c r="H750" s="10" t="s">
-        <v>3544</v>
-      </c>
-      <c r="I750" s="218" t="s">
-        <v>3545</v>
+        <v>2616</v>
+      </c>
+      <c r="I750" s="11" t="s">
+        <v>2617</v>
       </c>
       <c r="J750" s="10" t="s">
-        <v>3546</v>
+        <v>2618</v>
       </c>
       <c r="K750" s="1"/>
       <c r="L750" s="1"/>
@@ -44796,107 +44797,105 @@
       <c r="Y750" s="1"/>
     </row>
     <row r="751" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A751" t="s">
+      <c r="A751" s="10" t="s">
+        <v>3542</v>
+      </c>
+      <c r="B751" s="10" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C751" s="10" t="s">
+        <v>3543</v>
+      </c>
+      <c r="D751" s="10">
+        <v>1856</v>
+      </c>
+      <c r="E751" s="10">
+        <v>1934</v>
+      </c>
+      <c r="F751" s="10"/>
+      <c r="G751" s="10" t="s">
+        <v>2273</v>
+      </c>
+      <c r="H751" s="10" t="s">
+        <v>3544</v>
+      </c>
+      <c r="I751" s="218" t="s">
+        <v>3545</v>
+      </c>
+      <c r="J751" s="10" t="s">
+        <v>3546</v>
+      </c>
+      <c r="K751" s="1"/>
+      <c r="L751" s="1"/>
+      <c r="M751" s="1"/>
+      <c r="N751" s="1"/>
+      <c r="O751" s="1"/>
+      <c r="P751" s="1"/>
+      <c r="Q751" s="1"/>
+      <c r="R751" s="1"/>
+      <c r="S751" s="1"/>
+      <c r="T751" s="1"/>
+      <c r="U751" s="1"/>
+      <c r="V751" s="1"/>
+      <c r="W751" s="1"/>
+      <c r="X751" s="1"/>
+      <c r="Y751" s="1"/>
+    </row>
+    <row r="752" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A752" t="s">
         <v>4284</v>
       </c>
-      <c r="C751" t="s">
+      <c r="C752" t="s">
         <v>1050</v>
       </c>
-      <c r="D751">
+      <c r="D752">
         <v>1849</v>
       </c>
-      <c r="E751">
+      <c r="E752">
         <v>1909</v>
       </c>
-      <c r="F751" t="s">
+      <c r="F752" t="s">
         <v>52</v>
       </c>
-      <c r="G751" t="s">
+      <c r="G752" t="s">
         <v>20</v>
       </c>
-      <c r="H751" s="137" t="s">
+      <c r="H752" s="137" t="s">
         <v>4285</v>
       </c>
-      <c r="I751" t="s">
+      <c r="I752" t="s">
         <v>4286</v>
       </c>
-      <c r="J751" t="s">
+      <c r="J752" t="s">
         <v>4287</v>
       </c>
-    </row>
-    <row r="752" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A752" s="1" t="s">
-        <v>3558</v>
-      </c>
-      <c r="B752" s="1"/>
-      <c r="C752" s="1"/>
-      <c r="D752" s="1">
-        <v>1336</v>
-      </c>
-      <c r="E752" s="1">
-        <v>1405</v>
-      </c>
-      <c r="F752" s="1" t="s">
-        <v>3559</v>
-      </c>
-      <c r="G752" s="1" t="s">
-        <v>3560</v>
-      </c>
-      <c r="H752" s="1" t="s">
-        <v>3561</v>
-      </c>
-      <c r="I752" s="4" t="s">
-        <v>3562</v>
-      </c>
-      <c r="J752" s="1" t="s">
-        <v>3563</v>
-      </c>
-      <c r="K752" s="1"/>
-      <c r="L752" s="1"/>
-      <c r="M752" s="1"/>
-      <c r="N752" s="1"/>
-      <c r="O752" s="1"/>
-      <c r="P752" s="1"/>
-      <c r="Q752" s="1"/>
-      <c r="R752" s="1"/>
-      <c r="S752" s="1"/>
-      <c r="T752" s="1"/>
-      <c r="U752" s="1"/>
-      <c r="V752" s="1"/>
-      <c r="W752" s="1"/>
-      <c r="X752" s="1"/>
-      <c r="Y752" s="1"/>
     </row>
     <row r="753" spans="1:25" ht="15.75" customHeight="1">
       <c r="A753" s="1" t="s">
-        <v>2619</v>
-      </c>
-      <c r="B753" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C753" s="1" t="s">
-        <v>157</v>
-      </c>
+        <v>3558</v>
+      </c>
+      <c r="B753" s="1"/>
+      <c r="C753" s="1"/>
       <c r="D753" s="1">
-        <v>1842</v>
+        <v>1336</v>
       </c>
       <c r="E753" s="1">
-        <v>1927</v>
+        <v>1405</v>
       </c>
       <c r="F753" s="1" t="s">
-        <v>2619</v>
+        <v>3559</v>
       </c>
       <c r="G753" s="1" t="s">
-        <v>2619</v>
+        <v>3560</v>
       </c>
       <c r="H753" s="1" t="s">
-        <v>2620</v>
+        <v>3561</v>
       </c>
       <c r="I753" s="4" t="s">
-        <v>2621</v>
+        <v>3562</v>
       </c>
       <c r="J753" s="1" t="s">
-        <v>2622</v>
+        <v>3563</v>
       </c>
       <c r="K753" s="1"/>
       <c r="L753" s="1"/>
@@ -44915,111 +44914,111 @@
       <c r="Y753" s="1"/>
     </row>
     <row r="754" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A754" t="s">
+      <c r="A754" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C754" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D754" s="1">
+        <v>1842</v>
+      </c>
+      <c r="E754" s="1">
+        <v>1927</v>
+      </c>
+      <c r="F754" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="G754" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="H754" s="1" t="s">
+        <v>2620</v>
+      </c>
+      <c r="I754" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="J754" s="1" t="s">
+        <v>2622</v>
+      </c>
+      <c r="K754" s="1"/>
+      <c r="L754" s="1"/>
+      <c r="M754" s="1"/>
+      <c r="N754" s="1"/>
+      <c r="O754" s="1"/>
+      <c r="P754" s="1"/>
+      <c r="Q754" s="1"/>
+      <c r="R754" s="1"/>
+      <c r="S754" s="1"/>
+      <c r="T754" s="1"/>
+      <c r="U754" s="1"/>
+      <c r="V754" s="1"/>
+      <c r="W754" s="1"/>
+      <c r="X754" s="1"/>
+      <c r="Y754" s="1"/>
+    </row>
+    <row r="755" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A755" t="s">
         <v>4015</v>
       </c>
-      <c r="B754" t="s">
+      <c r="B755" t="s">
         <v>479</v>
       </c>
-      <c r="C754" t="s">
+      <c r="C755" t="s">
         <v>311</v>
       </c>
-      <c r="D754">
+      <c r="D755">
         <v>1929</v>
       </c>
-      <c r="E754">
+      <c r="E755">
         <v>1902</v>
       </c>
-      <c r="G754" t="s">
+      <c r="G755" t="s">
         <v>556</v>
       </c>
-      <c r="H754" t="s">
+      <c r="H755" t="s">
         <v>4016</v>
       </c>
-      <c r="I754" t="s">
+      <c r="I755" t="s">
         <v>4017</v>
       </c>
-      <c r="J754" t="s">
+      <c r="J755" t="s">
         <v>4018</v>
       </c>
     </row>
-    <row r="755" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A755" s="1" t="s">
+    <row r="756" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A756" s="1" t="s">
         <v>2623</v>
       </c>
-      <c r="B755" s="1" t="s">
+      <c r="B756" s="1" t="s">
         <v>2624</v>
       </c>
-      <c r="C755" s="1" t="s">
+      <c r="C756" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D755" s="1">
+      <c r="D756" s="1">
         <v>1847</v>
       </c>
-      <c r="E755" s="1">
+      <c r="E756" s="1">
         <v>1916</v>
       </c>
-      <c r="F755" s="1" t="s">
+      <c r="F756" s="1" t="s">
         <v>2625</v>
       </c>
-      <c r="G755" s="1" t="s">
+      <c r="G756" s="1" t="s">
         <v>2625</v>
       </c>
-      <c r="H755" s="1" t="s">
+      <c r="H756" s="1" t="s">
         <v>2626</v>
       </c>
-      <c r="I755" s="4" t="s">
+      <c r="I756" s="4" t="s">
         <v>2627</v>
       </c>
-      <c r="J755" s="1" t="s">
+      <c r="J756" s="1" t="s">
         <v>2628</v>
-      </c>
-      <c r="K755" s="1"/>
-      <c r="L755" s="1"/>
-      <c r="M755" s="1"/>
-      <c r="N755" s="1"/>
-      <c r="O755" s="1"/>
-      <c r="P755" s="1"/>
-      <c r="Q755" s="1"/>
-      <c r="R755" s="1"/>
-      <c r="S755" s="1"/>
-      <c r="T755" s="1"/>
-      <c r="U755" s="1"/>
-      <c r="V755" s="1"/>
-      <c r="W755" s="1"/>
-      <c r="X755" s="1"/>
-      <c r="Y755" s="1"/>
-    </row>
-    <row r="756" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A756" s="2" t="s">
-        <v>2623</v>
-      </c>
-      <c r="B756" s="2" t="s">
-        <v>2629</v>
-      </c>
-      <c r="C756" s="2" t="s">
-        <v>2630</v>
-      </c>
-      <c r="D756" s="2">
-        <v>1854</v>
-      </c>
-      <c r="E756" s="2">
-        <v>1898</v>
-      </c>
-      <c r="F756" s="2" t="s">
-        <v>2631</v>
-      </c>
-      <c r="G756" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H756" s="2" t="s">
-        <v>2632</v>
-      </c>
-      <c r="I756" s="3" t="s">
-        <v>2633</v>
-      </c>
-      <c r="J756" s="2" t="s">
-        <v>2634</v>
       </c>
       <c r="K756" s="1"/>
       <c r="L756" s="1"/>
@@ -45038,35 +45037,35 @@
       <c r="Y756" s="1"/>
     </row>
     <row r="757" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A757" s="1" t="s">
-        <v>2635</v>
-      </c>
-      <c r="B757" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C757" s="1" t="s">
-        <v>2636</v>
-      </c>
-      <c r="D757" s="1">
-        <v>1849</v>
-      </c>
-      <c r="E757" s="1">
-        <v>1913</v>
-      </c>
-      <c r="F757" s="1" t="s">
+      <c r="A757" s="2" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D757" s="2">
+        <v>1854</v>
+      </c>
+      <c r="E757" s="2">
+        <v>1898</v>
+      </c>
+      <c r="F757" s="2" t="s">
         <v>2631</v>
       </c>
-      <c r="G757" s="1" t="s">
+      <c r="G757" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H757" s="1" t="s">
-        <v>2637</v>
-      </c>
-      <c r="I757" s="4" t="s">
-        <v>2638</v>
-      </c>
-      <c r="J757" s="1" t="s">
-        <v>2639</v>
+      <c r="H757" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="I757" s="3" t="s">
+        <v>2633</v>
+      </c>
+      <c r="J757" s="2" t="s">
+        <v>2634</v>
       </c>
       <c r="K757" s="1"/>
       <c r="L757" s="1"/>
@@ -45085,124 +45084,124 @@
       <c r="Y757" s="1"/>
     </row>
     <row r="758" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A758" t="s">
-        <v>4019</v>
-      </c>
-      <c r="C758" t="s">
-        <v>4020</v>
-      </c>
-      <c r="D758">
-        <v>1864</v>
-      </c>
-      <c r="E758">
-        <v>1939</v>
-      </c>
-      <c r="F758" t="s">
-        <v>122</v>
-      </c>
-      <c r="G758" t="s">
-        <v>4021</v>
-      </c>
-      <c r="H758" t="s">
-        <v>4022</v>
-      </c>
-      <c r="I758" t="s">
-        <v>4023</v>
-      </c>
-      <c r="J758" t="s">
-        <v>4024</v>
-      </c>
+      <c r="A758" s="1" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D758" s="1">
+        <v>1849</v>
+      </c>
+      <c r="E758" s="1">
+        <v>1913</v>
+      </c>
+      <c r="F758" s="1" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G758" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H758" s="1" t="s">
+        <v>2637</v>
+      </c>
+      <c r="I758" s="4" t="s">
+        <v>2638</v>
+      </c>
+      <c r="J758" s="1" t="s">
+        <v>2639</v>
+      </c>
+      <c r="K758" s="1"/>
+      <c r="L758" s="1"/>
+      <c r="M758" s="1"/>
+      <c r="N758" s="1"/>
+      <c r="O758" s="1"/>
+      <c r="P758" s="1"/>
+      <c r="Q758" s="1"/>
+      <c r="R758" s="1"/>
+      <c r="S758" s="1"/>
+      <c r="T758" s="1"/>
+      <c r="U758" s="1"/>
+      <c r="V758" s="1"/>
+      <c r="W758" s="1"/>
+      <c r="X758" s="1"/>
+      <c r="Y758" s="1"/>
     </row>
     <row r="759" spans="1:25" ht="15.75" customHeight="1">
       <c r="A759" t="s">
+        <v>4019</v>
+      </c>
+      <c r="C759" t="s">
+        <v>4020</v>
+      </c>
+      <c r="D759">
+        <v>1864</v>
+      </c>
+      <c r="E759">
+        <v>1939</v>
+      </c>
+      <c r="F759" t="s">
+        <v>122</v>
+      </c>
+      <c r="G759" t="s">
+        <v>4021</v>
+      </c>
+      <c r="H759" t="s">
+        <v>4022</v>
+      </c>
+      <c r="I759" t="s">
+        <v>4023</v>
+      </c>
+      <c r="J759" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="760" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A760" t="s">
         <v>4288</v>
       </c>
-      <c r="C759" t="s">
+      <c r="C760" t="s">
         <v>473</v>
       </c>
-      <c r="D759">
+      <c r="D760">
         <v>1696</v>
       </c>
-      <c r="E759">
+      <c r="E760">
         <v>1770</v>
       </c>
-      <c r="F759" t="s">
+      <c r="F760" t="s">
         <v>1508</v>
       </c>
-      <c r="G759" t="s">
+      <c r="G760" t="s">
         <v>4289</v>
       </c>
-      <c r="H759" s="137" t="s">
+      <c r="H760" s="137" t="s">
         <v>4290</v>
       </c>
-      <c r="I759" t="s">
+      <c r="I760" t="s">
         <v>4291</v>
       </c>
-      <c r="J759" t="s">
+      <c r="J760" t="s">
         <v>4292</v>
       </c>
     </row>
-    <row r="760" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A760" s="26" t="s">
+    <row r="761" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A761" s="26" t="s">
         <v>2640</v>
       </c>
-      <c r="B760" s="26"/>
-      <c r="C760" s="26"/>
-      <c r="D760" s="26"/>
-      <c r="E760" s="26"/>
-      <c r="F760" s="26"/>
-      <c r="G760" s="26"/>
-      <c r="H760" s="26"/>
-      <c r="I760" s="110"/>
-      <c r="J760" s="2" t="s">
+      <c r="B761" s="26"/>
+      <c r="C761" s="26"/>
+      <c r="D761" s="26"/>
+      <c r="E761" s="26"/>
+      <c r="F761" s="26"/>
+      <c r="G761" s="26"/>
+      <c r="H761" s="26"/>
+      <c r="I761" s="110"/>
+      <c r="J761" s="2" t="s">
         <v>2640</v>
-      </c>
-      <c r="K760" s="1"/>
-      <c r="L760" s="1"/>
-      <c r="M760" s="1"/>
-      <c r="N760" s="1"/>
-      <c r="O760" s="1"/>
-      <c r="P760" s="1"/>
-      <c r="Q760" s="1"/>
-      <c r="R760" s="1"/>
-      <c r="S760" s="1"/>
-      <c r="T760" s="1"/>
-      <c r="U760" s="1"/>
-      <c r="V760" s="1"/>
-      <c r="W760" s="1"/>
-      <c r="X760" s="1"/>
-      <c r="Y760" s="1"/>
-    </row>
-    <row r="761" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A761" s="1" t="s">
-        <v>2640</v>
-      </c>
-      <c r="B761" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C761" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D761" s="1">
-        <v>1861</v>
-      </c>
-      <c r="E761" s="1" t="s">
-        <v>2647</v>
-      </c>
-      <c r="F761" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G761" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H761" s="1" t="s">
-        <v>2648</v>
-      </c>
-      <c r="I761" s="15" t="s">
-        <v>2649</v>
-      </c>
-      <c r="J761" s="1" t="s">
-        <v>2650</v>
       </c>
       <c r="K761" s="1"/>
       <c r="L761" s="1"/>
@@ -45221,33 +45220,35 @@
       <c r="Y761" s="1"/>
     </row>
     <row r="762" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A762" s="26" t="s">
-        <v>2641</v>
-      </c>
-      <c r="B762" s="26"/>
-      <c r="C762" s="26" t="s">
-        <v>2642</v>
-      </c>
-      <c r="D762" s="26">
-        <v>1830</v>
-      </c>
-      <c r="E762" s="26">
-        <v>1902</v>
-      </c>
-      <c r="F762" s="26" t="s">
-        <v>2643</v>
-      </c>
-      <c r="G762" s="26" t="s">
+      <c r="A762" s="1" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D762" s="1">
+        <v>1861</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>2647</v>
+      </c>
+      <c r="F762" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H762" s="26" t="s">
-        <v>2644</v>
-      </c>
-      <c r="I762" s="110" t="s">
-        <v>2645</v>
-      </c>
-      <c r="J762" s="2" t="s">
-        <v>2646</v>
+      <c r="G762" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H762" s="1" t="s">
+        <v>2648</v>
+      </c>
+      <c r="I762" s="15" t="s">
+        <v>2649</v>
+      </c>
+      <c r="J762" s="1" t="s">
+        <v>2650</v>
       </c>
       <c r="K762" s="1"/>
       <c r="L762" s="1"/>
@@ -45266,140 +45267,138 @@
       <c r="Y762" s="1"/>
     </row>
     <row r="763" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A763" t="s">
-        <v>3459</v>
-      </c>
-      <c r="B763" t="s">
-        <v>50</v>
-      </c>
-      <c r="C763" t="s">
-        <v>3460</v>
-      </c>
-      <c r="D763">
-        <v>1863</v>
-      </c>
-      <c r="E763">
-        <v>1923</v>
-      </c>
-      <c r="F763" t="s">
-        <v>3461</v>
-      </c>
-      <c r="G763" t="s">
-        <v>2082</v>
-      </c>
-      <c r="H763" s="135" t="s">
-        <v>3462</v>
-      </c>
-      <c r="I763" s="124" t="s">
-        <v>3463</v>
-      </c>
-      <c r="J763" t="s">
-        <v>3464</v>
-      </c>
+      <c r="A763" s="26" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B763" s="26"/>
+      <c r="C763" s="26" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D763" s="26">
+        <v>1830</v>
+      </c>
+      <c r="E763" s="26">
+        <v>1902</v>
+      </c>
+      <c r="F763" s="26" t="s">
+        <v>2643</v>
+      </c>
+      <c r="G763" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H763" s="26" t="s">
+        <v>2644</v>
+      </c>
+      <c r="I763" s="110" t="s">
+        <v>2645</v>
+      </c>
+      <c r="J763" s="2" t="s">
+        <v>2646</v>
+      </c>
+      <c r="K763" s="1"/>
+      <c r="L763" s="1"/>
+      <c r="M763" s="1"/>
+      <c r="N763" s="1"/>
+      <c r="O763" s="1"/>
+      <c r="P763" s="1"/>
+      <c r="Q763" s="1"/>
+      <c r="R763" s="1"/>
+      <c r="S763" s="1"/>
+      <c r="T763" s="1"/>
+      <c r="U763" s="1"/>
+      <c r="V763" s="1"/>
+      <c r="W763" s="1"/>
+      <c r="X763" s="1"/>
+      <c r="Y763" s="1"/>
     </row>
     <row r="764" spans="1:25" ht="15.75" customHeight="1">
       <c r="A764" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B764" t="s">
+        <v>50</v>
+      </c>
+      <c r="C764" t="s">
+        <v>3460</v>
+      </c>
+      <c r="D764">
+        <v>1863</v>
+      </c>
+      <c r="E764">
+        <v>1923</v>
+      </c>
+      <c r="F764" t="s">
+        <v>3461</v>
+      </c>
+      <c r="G764" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H764" s="135" t="s">
+        <v>3462</v>
+      </c>
+      <c r="I764" s="124" t="s">
+        <v>3463</v>
+      </c>
+      <c r="J764" t="s">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="765" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A765" t="s">
         <v>4293</v>
       </c>
-      <c r="C764" t="s">
+      <c r="C765" t="s">
         <v>4294</v>
       </c>
-      <c r="D764">
+      <c r="D765">
         <v>1843</v>
       </c>
-      <c r="E764">
+      <c r="E765">
         <v>1906</v>
       </c>
-      <c r="F764" t="s">
+      <c r="F765" t="s">
         <v>4295</v>
       </c>
-      <c r="G764" t="s">
+      <c r="G765" t="s">
         <v>1508</v>
       </c>
-      <c r="H764" s="137" t="s">
+      <c r="H765" s="137" t="s">
         <v>4296</v>
       </c>
-      <c r="J764" t="s">
+      <c r="J765" t="s">
         <v>4297</v>
       </c>
     </row>
-    <row r="765" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A765" s="1" t="s">
+    <row r="766" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A766" s="1" t="s">
         <v>2651</v>
       </c>
-      <c r="B765" s="1" t="s">
+      <c r="B766" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C765" s="1" t="s">
+      <c r="C766" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D765" s="1">
+      <c r="D766" s="1">
         <v>1847</v>
       </c>
-      <c r="E765" s="1">
+      <c r="E766" s="1">
         <v>1926</v>
       </c>
-      <c r="F765" s="1" t="s">
+      <c r="F766" s="1" t="s">
         <v>2652</v>
       </c>
-      <c r="G765" s="1" t="s">
+      <c r="G766" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="H765" s="1" t="s">
+      <c r="H766" s="1" t="s">
         <v>2653</v>
       </c>
-      <c r="I765" s="15" t="s">
+      <c r="I766" s="15" t="s">
         <v>2654</v>
       </c>
-      <c r="J765" s="1" t="s">
+      <c r="J766" s="1" t="s">
         <v>2655</v>
-      </c>
-      <c r="K765" s="1"/>
-      <c r="L765" s="1"/>
-      <c r="M765" s="1"/>
-      <c r="N765" s="1"/>
-      <c r="O765" s="1"/>
-      <c r="P765" s="1"/>
-      <c r="Q765" s="1"/>
-      <c r="R765" s="1"/>
-      <c r="S765" s="1"/>
-      <c r="T765" s="1"/>
-      <c r="U765" s="1"/>
-      <c r="V765" s="1"/>
-      <c r="W765" s="1"/>
-      <c r="X765" s="1"/>
-      <c r="Y765" s="1"/>
-    </row>
-    <row r="766" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A766" s="10" t="s">
-        <v>2656</v>
-      </c>
-      <c r="B766" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C766" s="10" t="s">
-        <v>2657</v>
-      </c>
-      <c r="D766" s="10">
-        <v>1840</v>
-      </c>
-      <c r="E766" s="10">
-        <v>1889</v>
-      </c>
-      <c r="F766" s="10" t="s">
-        <v>2658</v>
-      </c>
-      <c r="G766" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H766" s="10" t="s">
-        <v>2659</v>
-      </c>
-      <c r="I766" s="21" t="s">
-        <v>2660</v>
-      </c>
-      <c r="J766" s="10" t="s">
-        <v>2661</v>
       </c>
       <c r="K766" s="1"/>
       <c r="L766" s="1"/>
@@ -45418,99 +45417,101 @@
       <c r="Y766" s="1"/>
     </row>
     <row r="767" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A767" t="s">
+      <c r="A767" s="10" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B767" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C767" s="10" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D767" s="10">
+        <v>1840</v>
+      </c>
+      <c r="E767" s="10">
+        <v>1889</v>
+      </c>
+      <c r="F767" s="10" t="s">
+        <v>2658</v>
+      </c>
+      <c r="G767" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H767" s="10" t="s">
+        <v>2659</v>
+      </c>
+      <c r="I767" s="21" t="s">
+        <v>2660</v>
+      </c>
+      <c r="J767" s="10" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K767" s="1"/>
+      <c r="L767" s="1"/>
+      <c r="M767" s="1"/>
+      <c r="N767" s="1"/>
+      <c r="O767" s="1"/>
+      <c r="P767" s="1"/>
+      <c r="Q767" s="1"/>
+      <c r="R767" s="1"/>
+      <c r="S767" s="1"/>
+      <c r="T767" s="1"/>
+      <c r="U767" s="1"/>
+      <c r="V767" s="1"/>
+      <c r="W767" s="1"/>
+      <c r="X767" s="1"/>
+      <c r="Y767" s="1"/>
+    </row>
+    <row r="768" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A768" t="s">
         <v>4025</v>
       </c>
-      <c r="C767" t="s">
+      <c r="C768" t="s">
         <v>3603</v>
       </c>
-      <c r="D767">
+      <c r="D768">
         <v>1869</v>
       </c>
-      <c r="E767">
+      <c r="E768">
         <v>1932</v>
       </c>
-      <c r="F767" t="s">
+      <c r="F768" t="s">
         <v>4026</v>
       </c>
-      <c r="G767" t="s">
+      <c r="G768" t="s">
         <v>3178</v>
       </c>
-      <c r="H767" t="s">
+      <c r="H768" t="s">
         <v>4027</v>
       </c>
-      <c r="I767" t="s">
+      <c r="I768" t="s">
         <v>4028</v>
       </c>
-      <c r="J767" t="s">
+      <c r="J768" t="s">
         <v>4029</v>
       </c>
     </row>
-    <row r="768" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A768" s="2" t="s">
+    <row r="769" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A769" s="2" t="s">
         <v>2662</v>
       </c>
-      <c r="B768" s="2" t="s">
+      <c r="B769" s="2" t="s">
         <v>2663</v>
       </c>
-      <c r="C768" s="2" t="s">
+      <c r="C769" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="D768" s="2"/>
-      <c r="E768" s="2"/>
-      <c r="F768" s="2"/>
-      <c r="G768" s="2"/>
-      <c r="H768" s="2" t="s">
+      <c r="D769" s="2"/>
+      <c r="E769" s="2"/>
+      <c r="F769" s="2"/>
+      <c r="G769" s="2"/>
+      <c r="H769" s="2" t="s">
         <v>2664</v>
       </c>
-      <c r="I768" s="2"/>
-      <c r="J768" s="2" t="s">
+      <c r="I769" s="2"/>
+      <c r="J769" s="2" t="s">
         <v>2665</v>
-      </c>
-      <c r="K768" s="1"/>
-      <c r="L768" s="1"/>
-      <c r="M768" s="1"/>
-      <c r="N768" s="1"/>
-      <c r="O768" s="1"/>
-      <c r="P768" s="1"/>
-      <c r="Q768" s="1"/>
-      <c r="R768" s="1"/>
-      <c r="S768" s="1"/>
-      <c r="T768" s="1"/>
-      <c r="U768" s="1"/>
-      <c r="V768" s="1"/>
-      <c r="W768" s="1"/>
-      <c r="X768" s="1"/>
-      <c r="Y768" s="1"/>
-    </row>
-    <row r="769" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A769" s="1" t="s">
-        <v>2666</v>
-      </c>
-      <c r="B769" s="1" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C769" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D769" s="1">
-        <v>1845</v>
-      </c>
-      <c r="E769" s="1">
-        <v>1921</v>
-      </c>
-      <c r="F769" s="1" t="s">
-        <v>2668</v>
-      </c>
-      <c r="G769" s="1" t="s">
-        <v>2669</v>
-      </c>
-      <c r="H769" s="1" t="s">
-        <v>2670</v>
-      </c>
-      <c r="I769" s="1"/>
-      <c r="J769" s="1" t="s">
-        <v>2671</v>
       </c>
       <c r="K769" s="1"/>
       <c r="L769" s="1"/>
@@ -45529,273 +45530,271 @@
       <c r="Y769" s="1"/>
     </row>
     <row r="770" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A770" s="85" t="s">
+      <c r="A770" s="1" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D770" s="1">
+        <v>1845</v>
+      </c>
+      <c r="E770" s="1">
+        <v>1921</v>
+      </c>
+      <c r="F770" s="1" t="s">
+        <v>2668</v>
+      </c>
+      <c r="G770" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H770" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="I770" s="1"/>
+      <c r="J770" s="1" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K770" s="1"/>
+      <c r="L770" s="1"/>
+      <c r="M770" s="1"/>
+      <c r="N770" s="1"/>
+      <c r="O770" s="1"/>
+      <c r="P770" s="1"/>
+      <c r="Q770" s="1"/>
+      <c r="R770" s="1"/>
+      <c r="S770" s="1"/>
+      <c r="T770" s="1"/>
+      <c r="U770" s="1"/>
+      <c r="V770" s="1"/>
+      <c r="W770" s="1"/>
+      <c r="X770" s="1"/>
+      <c r="Y770" s="1"/>
+    </row>
+    <row r="771" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A771" s="85" t="s">
         <v>2672</v>
       </c>
-      <c r="B770" s="85"/>
-      <c r="C770" s="85" t="s">
+      <c r="B771" s="85"/>
+      <c r="C771" s="85" t="s">
         <v>2673</v>
       </c>
-      <c r="D770" s="85">
+      <c r="D771" s="85">
         <v>1827</v>
       </c>
-      <c r="E770" s="85">
+      <c r="E771" s="85">
         <v>1902</v>
       </c>
-      <c r="F770" s="85" t="s">
+      <c r="F771" s="85" t="s">
         <v>2674</v>
       </c>
-      <c r="G770" s="85" t="s">
+      <c r="G771" s="85" t="s">
         <v>2674</v>
       </c>
-      <c r="H770" s="85" t="s">
+      <c r="H771" s="85" t="s">
         <v>2675</v>
       </c>
-      <c r="I770" s="114"/>
-      <c r="J770" s="84" t="s">
+      <c r="I771" s="114"/>
+      <c r="J771" s="84" t="s">
         <v>2676</v>
       </c>
-      <c r="K770" s="115"/>
-      <c r="L770" s="115"/>
-      <c r="M770" s="115"/>
-      <c r="N770" s="115"/>
-      <c r="O770" s="115"/>
-      <c r="P770" s="115"/>
-      <c r="Q770" s="115"/>
-      <c r="R770" s="115"/>
-      <c r="S770" s="115"/>
-      <c r="T770" s="115"/>
-      <c r="U770" s="115"/>
-      <c r="V770" s="115"/>
-      <c r="W770" s="115"/>
-      <c r="X770" s="115"/>
-      <c r="Y770" s="115"/>
-    </row>
-    <row r="771" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A771" t="s">
-        <v>4030</v>
-      </c>
-      <c r="C771" t="s">
-        <v>4031</v>
-      </c>
-      <c r="D771">
-        <v>1862</v>
-      </c>
-      <c r="E771">
-        <v>1935</v>
-      </c>
-      <c r="F771" t="s">
-        <v>3857</v>
-      </c>
-      <c r="G771" t="s">
-        <v>3178</v>
-      </c>
-      <c r="H771" t="s">
-        <v>4032</v>
-      </c>
-      <c r="I771" t="s">
-        <v>4033</v>
-      </c>
-      <c r="J771" t="s">
-        <v>4034</v>
-      </c>
+      <c r="K771" s="115"/>
+      <c r="L771" s="115"/>
+      <c r="M771" s="115"/>
+      <c r="N771" s="115"/>
+      <c r="O771" s="115"/>
+      <c r="P771" s="115"/>
+      <c r="Q771" s="115"/>
+      <c r="R771" s="115"/>
+      <c r="S771" s="115"/>
+      <c r="T771" s="115"/>
+      <c r="U771" s="115"/>
+      <c r="V771" s="115"/>
+      <c r="W771" s="115"/>
+      <c r="X771" s="115"/>
+      <c r="Y771" s="115"/>
     </row>
     <row r="772" spans="1:25" ht="15.75" customHeight="1">
       <c r="A772" t="s">
-        <v>3465</v>
+        <v>4030</v>
       </c>
       <c r="C772" t="s">
-        <v>11</v>
+        <v>4031</v>
       </c>
       <c r="D772">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="E772">
-        <v>1916</v>
+        <v>1935</v>
       </c>
       <c r="F772" t="s">
-        <v>304</v>
+        <v>3857</v>
       </c>
       <c r="G772" t="s">
-        <v>20</v>
-      </c>
-      <c r="H772" s="135" t="s">
-        <v>3466</v>
+        <v>3178</v>
+      </c>
+      <c r="H772" t="s">
+        <v>4032</v>
       </c>
       <c r="I772" t="s">
-        <v>3467</v>
-      </c>
-      <c r="J772" s="15" t="s">
-        <v>3468</v>
+        <v>4033</v>
+      </c>
+      <c r="J772" t="s">
+        <v>4034</v>
       </c>
     </row>
     <row r="773" spans="1:25" ht="15.75" customHeight="1">
       <c r="A773" t="s">
-        <v>4035</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1531</v>
+        <v>3465</v>
       </c>
       <c r="C773" t="s">
         <v>11</v>
       </c>
       <c r="D773">
-        <v>1853</v>
+        <v>1858</v>
       </c>
       <c r="E773">
-        <v>1925</v>
+        <v>1916</v>
       </c>
       <c r="F773" t="s">
-        <v>715</v>
+        <v>304</v>
       </c>
       <c r="G773" t="s">
-        <v>715</v>
-      </c>
-      <c r="H773" t="s">
-        <v>4036</v>
+        <v>20</v>
+      </c>
+      <c r="H773" s="135" t="s">
+        <v>3466</v>
       </c>
       <c r="I773" t="s">
-        <v>4037</v>
-      </c>
-      <c r="J773" t="s">
-        <v>4038</v>
+        <v>3467</v>
+      </c>
+      <c r="J773" s="15" t="s">
+        <v>3468</v>
       </c>
     </row>
     <row r="774" spans="1:25" ht="15.75" customHeight="1">
       <c r="A774" t="s">
-        <v>3469</v>
+        <v>4035</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1531</v>
       </c>
       <c r="C774" t="s">
-        <v>3099</v>
+        <v>11</v>
       </c>
       <c r="D774">
-        <v>1866</v>
+        <v>1853</v>
       </c>
       <c r="E774">
-        <v>1938</v>
+        <v>1925</v>
       </c>
       <c r="F774" t="s">
-        <v>3470</v>
+        <v>715</v>
       </c>
       <c r="G774" t="s">
-        <v>3471</v>
-      </c>
-      <c r="H774" s="135" t="s">
-        <v>3472</v>
+        <v>715</v>
+      </c>
+      <c r="H774" t="s">
+        <v>4036</v>
       </c>
       <c r="I774" t="s">
-        <v>3473</v>
-      </c>
-      <c r="J774" s="15" t="s">
-        <v>3474</v>
+        <v>4037</v>
+      </c>
+      <c r="J774" t="s">
+        <v>4038</v>
       </c>
     </row>
     <row r="775" spans="1:25" ht="15.75" customHeight="1">
       <c r="A775" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C775" t="s">
+        <v>3099</v>
+      </c>
+      <c r="D775">
+        <v>1866</v>
+      </c>
+      <c r="E775">
+        <v>1938</v>
+      </c>
+      <c r="F775" t="s">
+        <v>3470</v>
+      </c>
+      <c r="G775" t="s">
+        <v>3471</v>
+      </c>
+      <c r="H775" s="135" t="s">
+        <v>3472</v>
+      </c>
+      <c r="I775" t="s">
+        <v>3473</v>
+      </c>
+      <c r="J775" s="15" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="776" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A776" t="s">
         <v>4039</v>
       </c>
-      <c r="C775" t="s">
+      <c r="C776" t="s">
         <v>3005</v>
       </c>
-      <c r="D775">
+      <c r="D776">
         <v>1862</v>
       </c>
-      <c r="E775">
+      <c r="E776">
         <v>1948</v>
       </c>
-      <c r="F775" t="s">
+      <c r="F776" t="s">
         <v>4040</v>
       </c>
-      <c r="G775" t="s">
+      <c r="G776" t="s">
         <v>215</v>
       </c>
-      <c r="H775" t="s">
+      <c r="H776" t="s">
         <v>4041</v>
       </c>
-      <c r="I775" t="s">
+      <c r="I776" t="s">
         <v>4042</v>
       </c>
-      <c r="J775" t="s">
+      <c r="J776" t="s">
         <v>4043</v>
       </c>
     </row>
-    <row r="776" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A776" s="85" t="s">
+    <row r="777" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A777" s="85" t="s">
         <v>2677</v>
       </c>
-      <c r="B776" s="85" t="s">
+      <c r="B777" s="85" t="s">
         <v>198</v>
       </c>
-      <c r="C776" s="85" t="s">
+      <c r="C777" s="85" t="s">
         <v>2678</v>
       </c>
-      <c r="D776" s="85">
+      <c r="D777" s="85">
         <v>1843</v>
       </c>
-      <c r="E776" s="85">
+      <c r="E777" s="85">
         <v>1910</v>
       </c>
-      <c r="F776" s="85" t="s">
+      <c r="F777" s="85" t="s">
         <v>1297</v>
       </c>
-      <c r="G776" s="85" t="s">
+      <c r="G777" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="H776" s="85" t="s">
+      <c r="H777" s="85" t="s">
         <v>2679</v>
       </c>
-      <c r="I776" s="114" t="s">
+      <c r="I777" s="114" t="s">
         <v>2680</v>
       </c>
-      <c r="J776" s="84" t="s">
+      <c r="J777" s="84" t="s">
         <v>2681</v>
-      </c>
-      <c r="K776" s="115"/>
-      <c r="L776" s="115"/>
-      <c r="M776" s="115"/>
-      <c r="N776" s="115"/>
-      <c r="O776" s="115"/>
-      <c r="P776" s="115"/>
-      <c r="Q776" s="115"/>
-      <c r="R776" s="115"/>
-      <c r="S776" s="115"/>
-      <c r="T776" s="115"/>
-      <c r="U776" s="115"/>
-      <c r="V776" s="115"/>
-      <c r="W776" s="115"/>
-      <c r="X776" s="115"/>
-      <c r="Y776" s="115"/>
-    </row>
-    <row r="777" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A777" s="117" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B777" s="117" t="s">
-        <v>2683</v>
-      </c>
-      <c r="C777" s="117" t="s">
-        <v>551</v>
-      </c>
-      <c r="D777" s="117">
-        <v>1828</v>
-      </c>
-      <c r="E777" s="117">
-        <v>1913</v>
-      </c>
-      <c r="F777" s="117" t="s">
-        <v>20</v>
-      </c>
-      <c r="G777" s="117" t="s">
-        <v>20</v>
-      </c>
-      <c r="H777" s="117" t="s">
-        <v>2684</v>
-      </c>
-      <c r="I777" s="21" t="s">
-        <v>2685</v>
-      </c>
-      <c r="J777" s="115" t="s">
-        <v>2686</v>
       </c>
       <c r="K777" s="115"/>
       <c r="L777" s="115"/>
@@ -45814,78 +45813,78 @@
       <c r="Y777" s="115"/>
     </row>
     <row r="778" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A778" s="85" t="s">
+      <c r="A778" s="117" t="s">
         <v>2682</v>
       </c>
-      <c r="B778" s="85" t="s">
+      <c r="B778" s="117" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C778" s="117" t="s">
+        <v>551</v>
+      </c>
+      <c r="D778" s="117">
+        <v>1828</v>
+      </c>
+      <c r="E778" s="117">
+        <v>1913</v>
+      </c>
+      <c r="F778" s="117" t="s">
+        <v>20</v>
+      </c>
+      <c r="G778" s="117" t="s">
+        <v>20</v>
+      </c>
+      <c r="H778" s="117" t="s">
+        <v>2684</v>
+      </c>
+      <c r="I778" s="21" t="s">
+        <v>2685</v>
+      </c>
+      <c r="J778" s="115" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K778" s="115"/>
+      <c r="L778" s="115"/>
+      <c r="M778" s="115"/>
+      <c r="N778" s="115"/>
+      <c r="O778" s="115"/>
+      <c r="P778" s="115"/>
+      <c r="Q778" s="115"/>
+      <c r="R778" s="115"/>
+      <c r="S778" s="115"/>
+      <c r="T778" s="115"/>
+      <c r="U778" s="115"/>
+      <c r="V778" s="115"/>
+      <c r="W778" s="115"/>
+      <c r="X778" s="115"/>
+      <c r="Y778" s="115"/>
+    </row>
+    <row r="779" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A779" s="85" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B779" s="85" t="s">
         <v>2687</v>
       </c>
-      <c r="C778" s="85" t="s">
+      <c r="C779" s="85" t="s">
         <v>2688</v>
       </c>
-      <c r="D778" s="85">
+      <c r="D779" s="85">
         <v>1840</v>
       </c>
-      <c r="E778" s="85">
+      <c r="E779" s="85">
         <v>1913</v>
       </c>
-      <c r="F778" s="85"/>
-      <c r="G778" s="85"/>
-      <c r="H778" s="85" t="s">
+      <c r="F779" s="85"/>
+      <c r="G779" s="85"/>
+      <c r="H779" s="85" t="s">
         <v>2689</v>
       </c>
-      <c r="I778" s="3" t="s">
+      <c r="I779" s="3" t="s">
         <v>2690</v>
       </c>
-      <c r="J778" s="84" t="s">
+      <c r="J779" s="84" t="s">
         <v>2691</v>
-      </c>
-      <c r="K778" s="116"/>
-      <c r="L778" s="116"/>
-      <c r="M778" s="116"/>
-      <c r="N778" s="116"/>
-      <c r="O778" s="116"/>
-      <c r="P778" s="116"/>
-      <c r="Q778" s="116"/>
-      <c r="R778" s="116"/>
-      <c r="S778" s="116"/>
-      <c r="T778" s="116"/>
-      <c r="U778" s="116"/>
-      <c r="V778" s="116"/>
-      <c r="W778" s="116"/>
-      <c r="X778" s="116"/>
-      <c r="Y778" s="116"/>
-    </row>
-    <row r="779" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A779" s="144" t="s">
-        <v>2692</v>
-      </c>
-      <c r="B779" s="144" t="s">
-        <v>50</v>
-      </c>
-      <c r="C779" s="144" t="s">
-        <v>432</v>
-      </c>
-      <c r="D779" s="144">
-        <v>1855</v>
-      </c>
-      <c r="E779" s="144">
-        <v>1940</v>
-      </c>
-      <c r="F779" s="144" t="s">
-        <v>52</v>
-      </c>
-      <c r="G779" s="144" t="s">
-        <v>52</v>
-      </c>
-      <c r="H779" s="144" t="s">
-        <v>2693</v>
-      </c>
-      <c r="I779" s="17" t="s">
-        <v>2694</v>
-      </c>
-      <c r="J779" s="116" t="s">
-        <v>2695</v>
       </c>
       <c r="K779" s="116"/>
       <c r="L779" s="116"/>
@@ -45904,138 +45903,140 @@
       <c r="Y779" s="116"/>
     </row>
     <row r="780" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A780" t="s">
-        <v>4044</v>
-      </c>
-      <c r="C780" t="s">
-        <v>4045</v>
-      </c>
-      <c r="D780">
-        <v>1852</v>
-      </c>
-      <c r="E780">
-        <v>1942</v>
-      </c>
-      <c r="F780" t="s">
-        <v>264</v>
-      </c>
-      <c r="G780" t="s">
-        <v>4046</v>
-      </c>
-      <c r="H780" t="s">
-        <v>4047</v>
-      </c>
-      <c r="I780" t="s">
-        <v>4048</v>
-      </c>
-      <c r="J780" t="s">
-        <v>4049</v>
-      </c>
+      <c r="A780" s="144" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B780" s="144" t="s">
+        <v>50</v>
+      </c>
+      <c r="C780" s="144" t="s">
+        <v>432</v>
+      </c>
+      <c r="D780" s="144">
+        <v>1855</v>
+      </c>
+      <c r="E780" s="144">
+        <v>1940</v>
+      </c>
+      <c r="F780" s="144" t="s">
+        <v>52</v>
+      </c>
+      <c r="G780" s="144" t="s">
+        <v>52</v>
+      </c>
+      <c r="H780" s="144" t="s">
+        <v>2693</v>
+      </c>
+      <c r="I780" s="17" t="s">
+        <v>2694</v>
+      </c>
+      <c r="J780" s="116" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K780" s="116"/>
+      <c r="L780" s="116"/>
+      <c r="M780" s="116"/>
+      <c r="N780" s="116"/>
+      <c r="O780" s="116"/>
+      <c r="P780" s="116"/>
+      <c r="Q780" s="116"/>
+      <c r="R780" s="116"/>
+      <c r="S780" s="116"/>
+      <c r="T780" s="116"/>
+      <c r="U780" s="116"/>
+      <c r="V780" s="116"/>
+      <c r="W780" s="116"/>
+      <c r="X780" s="116"/>
+      <c r="Y780" s="116"/>
     </row>
     <row r="781" spans="1:25" ht="15.75" customHeight="1">
       <c r="A781" t="s">
-        <v>4050</v>
+        <v>4044</v>
       </c>
       <c r="C781" t="s">
-        <v>4051</v>
+        <v>4045</v>
       </c>
       <c r="D781">
-        <v>1865</v>
+        <v>1852</v>
+      </c>
+      <c r="E781">
+        <v>1942</v>
+      </c>
+      <c r="F781" t="s">
+        <v>264</v>
+      </c>
+      <c r="G781" t="s">
+        <v>4046</v>
       </c>
       <c r="H781" t="s">
-        <v>4052</v>
+        <v>4047</v>
+      </c>
+      <c r="I781" t="s">
+        <v>4048</v>
       </c>
       <c r="J781" t="s">
-        <v>4053</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="782" spans="1:25" ht="15.75" customHeight="1">
       <c r="A782" t="s">
+        <v>4050</v>
+      </c>
+      <c r="C782" t="s">
+        <v>4051</v>
+      </c>
+      <c r="D782">
+        <v>1865</v>
+      </c>
+      <c r="H782" t="s">
+        <v>4052</v>
+      </c>
+      <c r="J782" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="783" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A783" t="s">
         <v>4054</v>
       </c>
-      <c r="C782" t="s">
+      <c r="C783" t="s">
         <v>73</v>
       </c>
-      <c r="H782" t="s">
+      <c r="H783" t="s">
         <v>4055</v>
       </c>
-      <c r="J782" t="s">
+      <c r="J783" t="s">
         <v>4056</v>
       </c>
     </row>
-    <row r="783" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A783" s="115" t="s">
+    <row r="784" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A784" s="115" t="s">
         <v>2696</v>
       </c>
-      <c r="B783" s="117"/>
-      <c r="C783" s="117" t="s">
+      <c r="B784" s="117"/>
+      <c r="C784" s="117" t="s">
         <v>2697</v>
       </c>
-      <c r="D783" s="117">
+      <c r="D784" s="117">
         <v>1490</v>
       </c>
-      <c r="E783" s="117">
+      <c r="E784" s="117">
         <v>1576</v>
       </c>
-      <c r="F783" s="117" t="s">
+      <c r="F784" s="117" t="s">
         <v>2698</v>
       </c>
-      <c r="G783" s="117" t="s">
+      <c r="G784" s="117" t="s">
         <v>1508</v>
       </c>
-      <c r="H783" s="117" t="s">
+      <c r="H784" s="117" t="s">
         <v>2699</v>
       </c>
-      <c r="I783" s="47" t="s">
+      <c r="I784" s="47" t="s">
         <v>2700</v>
       </c>
-      <c r="J783" s="115" t="s">
+      <c r="J784" s="115" t="s">
         <v>3531</v>
-      </c>
-      <c r="K783" s="116"/>
-      <c r="L783" s="116"/>
-      <c r="M783" s="116"/>
-      <c r="N783" s="116"/>
-      <c r="O783" s="116"/>
-      <c r="P783" s="116"/>
-      <c r="Q783" s="116"/>
-      <c r="R783" s="116"/>
-      <c r="S783" s="116"/>
-      <c r="T783" s="116"/>
-      <c r="U783" s="116"/>
-      <c r="V783" s="116"/>
-      <c r="W783" s="116"/>
-      <c r="X783" s="116"/>
-      <c r="Y783" s="116"/>
-    </row>
-    <row r="784" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A784" s="116" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B784" s="144"/>
-      <c r="C784" s="144" t="s">
-        <v>466</v>
-      </c>
-      <c r="D784" s="144">
-        <v>1846</v>
-      </c>
-      <c r="E784" s="144">
-        <v>1907</v>
-      </c>
-      <c r="F784" s="144" t="s">
-        <v>2702</v>
-      </c>
-      <c r="G784" s="144" t="s">
-        <v>82</v>
-      </c>
-      <c r="H784" s="144" t="s">
-        <v>2703</v>
-      </c>
-      <c r="I784" s="15" t="s">
-        <v>2704</v>
-      </c>
-      <c r="J784" s="116" t="s">
-        <v>2705</v>
       </c>
       <c r="K784" s="116"/>
       <c r="L784" s="116"/>
@@ -46054,149 +46055,147 @@
       <c r="Y784" s="116"/>
     </row>
     <row r="785" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A785" t="s">
-        <v>4057</v>
-      </c>
-      <c r="H785" t="s">
-        <v>4058</v>
-      </c>
-      <c r="J785" t="s">
-        <v>4059</v>
-      </c>
+      <c r="A785" s="116" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B785" s="144"/>
+      <c r="C785" s="144" t="s">
+        <v>466</v>
+      </c>
+      <c r="D785" s="144">
+        <v>1846</v>
+      </c>
+      <c r="E785" s="144">
+        <v>1907</v>
+      </c>
+      <c r="F785" s="144" t="s">
+        <v>2702</v>
+      </c>
+      <c r="G785" s="144" t="s">
+        <v>82</v>
+      </c>
+      <c r="H785" s="144" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I785" s="15" t="s">
+        <v>2704</v>
+      </c>
+      <c r="J785" s="116" t="s">
+        <v>2705</v>
+      </c>
+      <c r="K785" s="116"/>
+      <c r="L785" s="116"/>
+      <c r="M785" s="116"/>
+      <c r="N785" s="116"/>
+      <c r="O785" s="116"/>
+      <c r="P785" s="116"/>
+      <c r="Q785" s="116"/>
+      <c r="R785" s="116"/>
+      <c r="S785" s="116"/>
+      <c r="T785" s="116"/>
+      <c r="U785" s="116"/>
+      <c r="V785" s="116"/>
+      <c r="W785" s="116"/>
+      <c r="X785" s="116"/>
+      <c r="Y785" s="116"/>
     </row>
     <row r="786" spans="1:25" ht="15.75" customHeight="1">
       <c r="A786" t="s">
-        <v>4060</v>
-      </c>
-      <c r="C786" t="s">
-        <v>4061</v>
-      </c>
-      <c r="D786">
-        <v>1864</v>
-      </c>
-      <c r="E786">
-        <v>1936</v>
-      </c>
-      <c r="F786" t="s">
-        <v>4062</v>
-      </c>
-      <c r="G786" t="s">
-        <v>298</v>
+        <v>4057</v>
       </c>
       <c r="H786" t="s">
-        <v>4063</v>
-      </c>
-      <c r="I786" t="s">
-        <v>4064</v>
+        <v>4058</v>
       </c>
       <c r="J786" t="s">
-        <v>4065</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="787" spans="1:25" ht="15.75" customHeight="1">
       <c r="A787" t="s">
+        <v>4060</v>
+      </c>
+      <c r="C787" t="s">
+        <v>4061</v>
+      </c>
+      <c r="D787">
+        <v>1864</v>
+      </c>
+      <c r="E787">
+        <v>1936</v>
+      </c>
+      <c r="F787" t="s">
+        <v>4062</v>
+      </c>
+      <c r="G787" t="s">
+        <v>298</v>
+      </c>
+      <c r="H787" t="s">
+        <v>4063</v>
+      </c>
+      <c r="I787" t="s">
+        <v>4064</v>
+      </c>
+      <c r="J787" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="788" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A788" t="s">
         <v>3475</v>
       </c>
-      <c r="C787" t="s">
+      <c r="C788" t="s">
         <v>199</v>
       </c>
-      <c r="D787">
+      <c r="D788">
         <v>1848</v>
       </c>
-      <c r="E787">
+      <c r="E788">
         <v>1915</v>
       </c>
-      <c r="F787" t="s">
+      <c r="F788" t="s">
         <v>3476</v>
       </c>
-      <c r="G787" t="s">
+      <c r="G788" t="s">
         <v>831</v>
       </c>
-      <c r="H787" s="135" t="s">
+      <c r="H788" s="135" t="s">
         <v>3477</v>
       </c>
-      <c r="I787" t="s">
+      <c r="I788" t="s">
         <v>3478</v>
       </c>
-      <c r="J787" t="s">
+      <c r="J788" t="s">
         <v>3479</v>
       </c>
-    </row>
-    <row r="788" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A788" s="144" t="s">
-        <v>2706</v>
-      </c>
-      <c r="B788" s="144"/>
-      <c r="C788" s="144" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D788" s="144">
-        <v>1858</v>
-      </c>
-      <c r="E788" s="144">
-        <v>1940</v>
-      </c>
-      <c r="F788" s="144" t="s">
-        <v>2575</v>
-      </c>
-      <c r="G788" s="144" t="s">
-        <v>82</v>
-      </c>
-      <c r="H788" s="144" t="s">
-        <v>2707</v>
-      </c>
-      <c r="I788" s="15" t="s">
-        <v>2708</v>
-      </c>
-      <c r="J788" s="116" t="s">
-        <v>2709</v>
-      </c>
-      <c r="K788" s="116"/>
-      <c r="L788" s="116"/>
-      <c r="M788" s="116"/>
-      <c r="N788" s="116"/>
-      <c r="O788" s="116"/>
-      <c r="P788" s="116"/>
-      <c r="Q788" s="116"/>
-      <c r="R788" s="116"/>
-      <c r="S788" s="116"/>
-      <c r="T788" s="116"/>
-      <c r="U788" s="116"/>
-      <c r="V788" s="116"/>
-      <c r="W788" s="116"/>
-      <c r="X788" s="116"/>
-      <c r="Y788" s="116"/>
     </row>
     <row r="789" spans="1:25" ht="15.75" customHeight="1">
       <c r="A789" s="144" t="s">
-        <v>2710</v>
-      </c>
-      <c r="B789" s="144" t="s">
-        <v>2711</v>
-      </c>
+        <v>2706</v>
+      </c>
+      <c r="B789" s="144"/>
       <c r="C789" s="144" t="s">
-        <v>2712</v>
+        <v>1578</v>
       </c>
       <c r="D789" s="144">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="E789" s="144">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="F789" s="144" t="s">
-        <v>176</v>
+        <v>2575</v>
       </c>
       <c r="G789" s="144" t="s">
-        <v>2713</v>
+        <v>82</v>
       </c>
       <c r="H789" s="144" t="s">
-        <v>2714</v>
+        <v>2707</v>
       </c>
       <c r="I789" s="15" t="s">
-        <v>2715</v>
+        <v>2708</v>
       </c>
       <c r="J789" s="116" t="s">
-        <v>2716</v>
+        <v>2709</v>
       </c>
       <c r="K789" s="116"/>
       <c r="L789" s="116"/>
@@ -46215,421 +46214,425 @@
       <c r="Y789" s="116"/>
     </row>
     <row r="790" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A790" t="s">
+      <c r="A790" s="144" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B790" s="144" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C790" s="144" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D790" s="144">
+        <v>1856</v>
+      </c>
+      <c r="E790" s="144">
+        <v>1945</v>
+      </c>
+      <c r="F790" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="G790" s="144" t="s">
+        <v>2713</v>
+      </c>
+      <c r="H790" s="144" t="s">
+        <v>2714</v>
+      </c>
+      <c r="I790" s="15" t="s">
+        <v>2715</v>
+      </c>
+      <c r="J790" s="116" t="s">
+        <v>2716</v>
+      </c>
+      <c r="K790" s="116"/>
+      <c r="L790" s="116"/>
+      <c r="M790" s="116"/>
+      <c r="N790" s="116"/>
+      <c r="O790" s="116"/>
+      <c r="P790" s="116"/>
+      <c r="Q790" s="116"/>
+      <c r="R790" s="116"/>
+      <c r="S790" s="116"/>
+      <c r="T790" s="116"/>
+      <c r="U790" s="116"/>
+      <c r="V790" s="116"/>
+      <c r="W790" s="116"/>
+      <c r="X790" s="116"/>
+      <c r="Y790" s="116"/>
+    </row>
+    <row r="791" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A791" t="s">
         <v>4298</v>
       </c>
-      <c r="C790" t="s">
+      <c r="C791" t="s">
         <v>4299</v>
       </c>
-      <c r="D790">
+      <c r="D791">
         <v>1827</v>
       </c>
-      <c r="E790">
+      <c r="E791">
         <v>1917</v>
       </c>
-      <c r="F790" t="s">
+      <c r="F791" t="s">
         <v>419</v>
       </c>
-      <c r="G790" t="s">
+      <c r="G791" t="s">
         <v>800</v>
       </c>
-      <c r="H790" s="137" t="s">
+      <c r="H791" s="137" t="s">
         <v>4300</v>
       </c>
-      <c r="I790" t="s">
+      <c r="I791" t="s">
         <v>4301</v>
       </c>
-      <c r="J790" t="s">
+      <c r="J791" t="s">
         <v>4302</v>
       </c>
     </row>
-    <row r="791" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A791" s="117" t="s">
+    <row r="792" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A792" s="117" t="s">
         <v>2717</v>
       </c>
-      <c r="B791" s="117" t="s">
+      <c r="B792" s="117" t="s">
         <v>2718</v>
       </c>
-      <c r="C791" s="117" t="s">
+      <c r="C792" s="117" t="s">
         <v>2719</v>
       </c>
-      <c r="D791" s="117">
+      <c r="D792" s="117">
         <v>1628</v>
       </c>
-      <c r="E791" s="117">
+      <c r="E792" s="117">
         <v>1687</v>
       </c>
-      <c r="F791" s="117" t="s">
+      <c r="F792" s="117" t="s">
         <v>573</v>
       </c>
-      <c r="G791" s="117" t="s">
+      <c r="G792" s="117" t="s">
         <v>2720</v>
       </c>
-      <c r="H791" s="117" t="s">
+      <c r="H792" s="117" t="s">
         <v>2721</v>
       </c>
-      <c r="I791" s="47" t="s">
+      <c r="I792" s="47" t="s">
         <v>2722</v>
       </c>
-      <c r="J791" s="115" t="s">
+      <c r="J792" s="115" t="s">
         <v>2723</v>
       </c>
-      <c r="K791" s="116"/>
-      <c r="L791" s="116"/>
-      <c r="M791" s="116"/>
-      <c r="N791" s="116"/>
-      <c r="O791" s="116"/>
-      <c r="P791" s="116"/>
-      <c r="Q791" s="116"/>
-      <c r="R791" s="116"/>
-      <c r="S791" s="116"/>
-      <c r="T791" s="116"/>
-      <c r="U791" s="116"/>
-      <c r="V791" s="116"/>
-      <c r="W791" s="116"/>
-      <c r="X791" s="116"/>
-      <c r="Y791" s="116"/>
-    </row>
-    <row r="792" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A792" t="s">
-        <v>4303</v>
-      </c>
-      <c r="B792" t="s">
-        <v>4304</v>
-      </c>
-      <c r="C792" t="s">
-        <v>4305</v>
-      </c>
-      <c r="D792">
-        <v>1877</v>
-      </c>
-      <c r="E792">
-        <v>1953</v>
-      </c>
-      <c r="F792" t="s">
-        <v>4306</v>
-      </c>
-      <c r="G792" t="s">
-        <v>1204</v>
-      </c>
-      <c r="H792" s="137" t="s">
-        <v>4307</v>
-      </c>
-      <c r="I792" s="124" t="s">
-        <v>4308</v>
-      </c>
-      <c r="J792" t="s">
-        <v>4309</v>
-      </c>
+      <c r="K792" s="116"/>
+      <c r="L792" s="116"/>
+      <c r="M792" s="116"/>
+      <c r="N792" s="116"/>
+      <c r="O792" s="116"/>
+      <c r="P792" s="116"/>
+      <c r="Q792" s="116"/>
+      <c r="R792" s="116"/>
+      <c r="S792" s="116"/>
+      <c r="T792" s="116"/>
+      <c r="U792" s="116"/>
+      <c r="V792" s="116"/>
+      <c r="W792" s="116"/>
+      <c r="X792" s="116"/>
+      <c r="Y792" s="116"/>
     </row>
     <row r="793" spans="1:25" ht="15.75" customHeight="1">
       <c r="A793" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B793" t="s">
+        <v>4304</v>
+      </c>
+      <c r="C793" t="s">
+        <v>4305</v>
+      </c>
+      <c r="D793">
+        <v>1877</v>
+      </c>
+      <c r="E793">
+        <v>1953</v>
+      </c>
+      <c r="F793" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G793" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H793" s="137" t="s">
+        <v>4307</v>
+      </c>
+      <c r="I793" s="124" t="s">
+        <v>4308</v>
+      </c>
+      <c r="J793" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="794" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A794" t="s">
         <v>3480</v>
       </c>
-      <c r="C793" t="s">
+      <c r="C794" t="s">
         <v>432</v>
       </c>
-      <c r="D793">
+      <c r="D794">
         <v>1868</v>
       </c>
-      <c r="E793">
+      <c r="E794">
         <v>1932</v>
       </c>
-      <c r="F793" t="s">
+      <c r="F794" t="s">
         <v>3481</v>
       </c>
-      <c r="G793" t="s">
+      <c r="G794" t="s">
         <v>52</v>
       </c>
-      <c r="H793" s="135" t="s">
+      <c r="H794" s="135" t="s">
         <v>3482</v>
       </c>
-      <c r="I793" s="124" t="s">
+      <c r="I794" s="124" t="s">
         <v>3483</v>
       </c>
-      <c r="J793" s="15" t="s">
+      <c r="J794" s="15" t="s">
         <v>3484</v>
       </c>
     </row>
-    <row r="794" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A794" s="144" t="s">
+    <row r="795" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A795" s="144" t="s">
         <v>2724</v>
       </c>
-      <c r="B794" s="144" t="s">
+      <c r="B795" s="144" t="s">
         <v>2725</v>
       </c>
-      <c r="C794" s="116" t="s">
+      <c r="C795" s="116" t="s">
         <v>1777</v>
       </c>
-      <c r="D794" s="116">
+      <c r="D795" s="116">
         <v>1849</v>
       </c>
-      <c r="E794" s="116">
+      <c r="E795" s="116">
         <v>1925</v>
       </c>
-      <c r="F794" s="144" t="s">
+      <c r="F795" s="144" t="s">
         <v>2726</v>
       </c>
-      <c r="G794" s="116" t="s">
+      <c r="G795" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="H794" s="116" t="s">
+      <c r="H795" s="116" t="s">
         <v>2727</v>
       </c>
-      <c r="I794" s="15" t="s">
+      <c r="I795" s="15" t="s">
         <v>2728</v>
       </c>
-      <c r="J794" s="116" t="s">
+      <c r="J795" s="116" t="s">
         <v>2729</v>
       </c>
-      <c r="K794" s="116"/>
-      <c r="L794" s="116"/>
-      <c r="M794" s="116"/>
-      <c r="N794" s="116"/>
-      <c r="O794" s="116"/>
-      <c r="P794" s="116"/>
-      <c r="Q794" s="116"/>
-      <c r="R794" s="116"/>
-      <c r="S794" s="116"/>
-      <c r="T794" s="116"/>
-      <c r="U794" s="116"/>
-      <c r="V794" s="116"/>
-      <c r="W794" s="116"/>
-      <c r="X794" s="116"/>
-      <c r="Y794" s="116"/>
-    </row>
-    <row r="795" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A795" t="s">
-        <v>4310</v>
-      </c>
-      <c r="B795" t="s">
-        <v>26</v>
-      </c>
-      <c r="C795" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D795">
-        <v>1850</v>
-      </c>
-      <c r="E795">
-        <v>1930</v>
-      </c>
-      <c r="F795" t="s">
-        <v>4311</v>
-      </c>
-      <c r="G795" t="s">
-        <v>4312</v>
-      </c>
-      <c r="H795" s="137" t="s">
-        <v>4313</v>
-      </c>
-      <c r="I795" t="s">
-        <v>4314</v>
-      </c>
-      <c r="J795" t="s">
-        <v>4315</v>
-      </c>
+      <c r="K795" s="116"/>
+      <c r="L795" s="116"/>
+      <c r="M795" s="116"/>
+      <c r="N795" s="116"/>
+      <c r="O795" s="116"/>
+      <c r="P795" s="116"/>
+      <c r="Q795" s="116"/>
+      <c r="R795" s="116"/>
+      <c r="S795" s="116"/>
+      <c r="T795" s="116"/>
+      <c r="U795" s="116"/>
+      <c r="V795" s="116"/>
+      <c r="W795" s="116"/>
+      <c r="X795" s="116"/>
+      <c r="Y795" s="116"/>
     </row>
     <row r="796" spans="1:25" ht="15.75" customHeight="1">
       <c r="A796" t="s">
+        <v>4310</v>
+      </c>
+      <c r="B796" t="s">
+        <v>26</v>
+      </c>
+      <c r="C796" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D796">
+        <v>1850</v>
+      </c>
+      <c r="E796">
+        <v>1930</v>
+      </c>
+      <c r="F796" t="s">
+        <v>4311</v>
+      </c>
+      <c r="G796" t="s">
+        <v>4312</v>
+      </c>
+      <c r="H796" s="137" t="s">
+        <v>4313</v>
+      </c>
+      <c r="I796" t="s">
+        <v>4314</v>
+      </c>
+      <c r="J796" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="797" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A797" t="s">
         <v>4066</v>
       </c>
-      <c r="H796" t="s">
+      <c r="H797" t="s">
         <v>4067</v>
       </c>
-      <c r="J796" t="s">
+      <c r="J797" t="s">
         <v>4068</v>
       </c>
     </row>
-    <row r="797" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A797" s="117" t="s">
+    <row r="798" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A798" s="117" t="s">
         <v>2730</v>
       </c>
-      <c r="B797" s="117"/>
-      <c r="C797" s="115" t="s">
+      <c r="B798" s="117"/>
+      <c r="C798" s="115" t="s">
         <v>2731</v>
       </c>
-      <c r="D797" s="115">
+      <c r="D798" s="115">
         <v>1813</v>
       </c>
-      <c r="E797" s="115">
+      <c r="E798" s="115">
         <v>1883</v>
       </c>
-      <c r="F797" s="117" t="s">
+      <c r="F798" s="117" t="s">
         <v>1966</v>
       </c>
-      <c r="G797" s="115" t="s">
+      <c r="G798" s="115" t="s">
         <v>1508</v>
       </c>
-      <c r="H797" s="115" t="s">
+      <c r="H798" s="115" t="s">
         <v>2732</v>
       </c>
-      <c r="I797" s="47" t="s">
+      <c r="I798" s="47" t="s">
         <v>2733</v>
       </c>
-      <c r="J797" s="115" t="s">
+      <c r="J798" s="115" t="s">
         <v>2734</v>
       </c>
-      <c r="K797" s="116"/>
-      <c r="L797" s="116"/>
-      <c r="M797" s="116"/>
-      <c r="N797" s="116"/>
-      <c r="O797" s="116"/>
-      <c r="P797" s="116"/>
-      <c r="Q797" s="116"/>
-      <c r="R797" s="116"/>
-      <c r="S797" s="116"/>
-      <c r="T797" s="116"/>
-      <c r="U797" s="116"/>
-      <c r="V797" s="116"/>
-      <c r="W797" s="116"/>
-      <c r="X797" s="116"/>
-      <c r="Y797" s="116"/>
-    </row>
-    <row r="798" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A798" t="s">
+      <c r="K798" s="116"/>
+      <c r="L798" s="116"/>
+      <c r="M798" s="116"/>
+      <c r="N798" s="116"/>
+      <c r="O798" s="116"/>
+      <c r="P798" s="116"/>
+      <c r="Q798" s="116"/>
+      <c r="R798" s="116"/>
+      <c r="S798" s="116"/>
+      <c r="T798" s="116"/>
+      <c r="U798" s="116"/>
+      <c r="V798" s="116"/>
+      <c r="W798" s="116"/>
+      <c r="X798" s="116"/>
+      <c r="Y798" s="116"/>
+    </row>
+    <row r="799" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A799" t="s">
         <v>2730</v>
       </c>
-      <c r="C798" t="s">
+      <c r="C799" t="s">
         <v>3485</v>
       </c>
-      <c r="D798">
+      <c r="D799">
         <v>1880</v>
       </c>
-      <c r="E798">
+      <c r="E799">
         <v>1915</v>
       </c>
-      <c r="G798" t="s">
+      <c r="G799" t="s">
         <v>3486</v>
       </c>
-      <c r="H798" s="135" t="s">
+      <c r="H799" s="135" t="s">
         <v>3487</v>
       </c>
-      <c r="I798" t="s">
+      <c r="I799" t="s">
         <v>3488</v>
       </c>
-      <c r="J798" s="15" t="s">
+      <c r="J799" s="15" t="s">
         <v>3489</v>
       </c>
     </row>
-    <row r="799" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A799" s="117" t="s">
+    <row r="800" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A800" s="117" t="s">
         <v>2964</v>
       </c>
-      <c r="B799" s="117"/>
-      <c r="C799" s="115" t="s">
+      <c r="B800" s="117"/>
+      <c r="C800" s="115" t="s">
         <v>199</v>
       </c>
-      <c r="D799" s="115">
+      <c r="D800" s="115">
         <v>1837</v>
       </c>
-      <c r="E799" s="115">
+      <c r="E800" s="115">
         <v>1900</v>
       </c>
-      <c r="F799" s="117" t="s">
+      <c r="F800" s="117" t="s">
         <v>2965</v>
       </c>
-      <c r="G799" s="115" t="s">
+      <c r="G800" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="H799" s="115" t="s">
+      <c r="H800" s="115" t="s">
         <v>2966</v>
       </c>
-      <c r="I799" s="129" t="s">
+      <c r="I800" s="129" t="s">
         <v>2967</v>
       </c>
-      <c r="J799" s="115" t="s">
+      <c r="J800" s="115" t="s">
         <v>2968</v>
       </c>
-      <c r="K799" s="116"/>
-      <c r="L799" s="116"/>
-      <c r="M799" s="116"/>
-      <c r="N799" s="116"/>
-      <c r="O799" s="116"/>
-      <c r="P799" s="116"/>
-      <c r="Q799" s="116"/>
-      <c r="R799" s="116"/>
-      <c r="S799" s="116"/>
-      <c r="T799" s="116"/>
-      <c r="U799" s="116"/>
-      <c r="V799" s="116"/>
-      <c r="W799" s="116"/>
-      <c r="X799" s="116"/>
-      <c r="Y799" s="116"/>
-    </row>
-    <row r="800" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A800" s="25" t="s">
+      <c r="K800" s="116"/>
+      <c r="L800" s="116"/>
+      <c r="M800" s="116"/>
+      <c r="N800" s="116"/>
+      <c r="O800" s="116"/>
+      <c r="P800" s="116"/>
+      <c r="Q800" s="116"/>
+      <c r="R800" s="116"/>
+      <c r="S800" s="116"/>
+      <c r="T800" s="116"/>
+      <c r="U800" s="116"/>
+      <c r="V800" s="116"/>
+      <c r="W800" s="116"/>
+      <c r="X800" s="116"/>
+      <c r="Y800" s="116"/>
+    </row>
+    <row r="801" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A801" s="25" t="s">
         <v>2735</v>
       </c>
-      <c r="B800" s="26" t="s">
+      <c r="B801" s="26" t="s">
         <v>2736</v>
       </c>
-      <c r="C800" s="26" t="s">
+      <c r="C801" s="26" t="s">
         <v>2737</v>
       </c>
-      <c r="D800" s="118">
+      <c r="D801" s="118">
         <v>1583</v>
       </c>
-      <c r="E800" s="118">
+      <c r="E801" s="118">
         <v>1634</v>
       </c>
-      <c r="F800" s="25" t="s">
+      <c r="F801" s="25" t="s">
         <v>2738</v>
       </c>
-      <c r="G800" s="25" t="s">
+      <c r="G801" s="25" t="s">
         <v>2739</v>
       </c>
-      <c r="H800" s="26" t="s">
+      <c r="H801" s="26" t="s">
         <v>2740</v>
       </c>
-      <c r="I800" s="106" t="s">
+      <c r="I801" s="106" t="s">
         <v>2741</v>
       </c>
-      <c r="J800" s="25" t="s">
+      <c r="J801" s="25" t="s">
         <v>2742</v>
-      </c>
-      <c r="K800" s="9"/>
-      <c r="L800" s="9"/>
-      <c r="M800" s="9"/>
-      <c r="N800" s="9"/>
-      <c r="O800" s="9"/>
-      <c r="P800" s="9"/>
-      <c r="Q800" s="9"/>
-      <c r="R800" s="9"/>
-      <c r="S800" s="9"/>
-      <c r="T800" s="9"/>
-      <c r="U800" s="9"/>
-      <c r="V800" s="9"/>
-      <c r="W800" s="9"/>
-      <c r="X800" s="9"/>
-      <c r="Y800" s="9"/>
-    </row>
-    <row r="801" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A801" s="12" t="s">
-        <v>2969</v>
-      </c>
-      <c r="B801" s="23"/>
-      <c r="C801" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D801" s="119">
-        <v>1838</v>
-      </c>
-      <c r="E801" s="119">
-        <v>1917</v>
-      </c>
-      <c r="F801" s="22" t="s">
-        <v>2743</v>
-      </c>
-      <c r="G801" s="22" t="s">
-        <v>2744</v>
-      </c>
-      <c r="H801" s="23" t="s">
-        <v>2745</v>
-      </c>
-      <c r="I801" s="74"/>
-      <c r="J801" s="22" t="s">
-        <v>2857</v>
       </c>
       <c r="K801" s="9"/>
       <c r="L801" s="9"/>
@@ -46648,35 +46651,31 @@
       <c r="Y801" s="9"/>
     </row>
     <row r="802" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A802" s="25" t="s">
-        <v>2746</v>
-      </c>
-      <c r="B802" s="26" t="s">
-        <v>2747</v>
-      </c>
-      <c r="C802" s="25" t="s">
-        <v>551</v>
-      </c>
-      <c r="D802" s="118">
-        <v>1811</v>
-      </c>
-      <c r="E802" s="118">
-        <v>1899</v>
-      </c>
-      <c r="F802" s="25" t="s">
-        <v>2748</v>
-      </c>
-      <c r="G802" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="H802" s="26" t="s">
-        <v>2749</v>
-      </c>
-      <c r="I802" s="198" t="s">
-        <v>2750</v>
-      </c>
-      <c r="J802" s="25" t="s">
-        <v>2751</v>
+      <c r="A802" s="12" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B802" s="23"/>
+      <c r="C802" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D802" s="119">
+        <v>1838</v>
+      </c>
+      <c r="E802" s="119">
+        <v>1917</v>
+      </c>
+      <c r="F802" s="22" t="s">
+        <v>2743</v>
+      </c>
+      <c r="G802" s="22" t="s">
+        <v>2744</v>
+      </c>
+      <c r="H802" s="23" t="s">
+        <v>2745</v>
+      </c>
+      <c r="I802" s="74"/>
+      <c r="J802" s="22" t="s">
+        <v>2857</v>
       </c>
       <c r="K802" s="9"/>
       <c r="L802" s="9"/>
@@ -46695,31 +46694,35 @@
       <c r="Y802" s="9"/>
     </row>
     <row r="803" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A803" s="48" t="s">
-        <v>2752</v>
-      </c>
-      <c r="B803" s="48" t="s">
-        <v>479</v>
-      </c>
-      <c r="C803" s="48" t="s">
-        <v>585</v>
+      <c r="A803" s="25" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B803" s="26" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C803" s="25" t="s">
+        <v>551</v>
       </c>
       <c r="D803" s="118">
-        <v>1885</v>
+        <v>1811</v>
       </c>
       <c r="E803" s="118">
         <v>1899</v>
       </c>
-      <c r="F803" s="48"/>
-      <c r="G803" s="48"/>
-      <c r="H803" s="177" t="s">
-        <v>2753</v>
-      </c>
-      <c r="I803" s="27" t="s">
-        <v>2754</v>
-      </c>
-      <c r="J803" s="48" t="s">
-        <v>2755</v>
+      <c r="F803" s="25" t="s">
+        <v>2748</v>
+      </c>
+      <c r="G803" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H803" s="26" t="s">
+        <v>2749</v>
+      </c>
+      <c r="I803" s="198" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J803" s="25" t="s">
+        <v>2751</v>
       </c>
       <c r="K803" s="9"/>
       <c r="L803" s="9"/>
@@ -46738,320 +46741,330 @@
       <c r="Y803" s="9"/>
     </row>
     <row r="804" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A804" t="s">
-        <v>3490</v>
-      </c>
-      <c r="C804" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D804">
-        <v>1861</v>
-      </c>
-      <c r="E804">
-        <v>1926</v>
-      </c>
-      <c r="F804" t="s">
-        <v>20</v>
-      </c>
-      <c r="G804" t="s">
-        <v>20</v>
-      </c>
-      <c r="H804" s="135" t="s">
-        <v>3491</v>
-      </c>
-      <c r="I804" t="s">
-        <v>3492</v>
-      </c>
-      <c r="J804" t="s">
-        <v>3493</v>
-      </c>
+      <c r="A804" s="48" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B804" s="48" t="s">
+        <v>479</v>
+      </c>
+      <c r="C804" s="48" t="s">
+        <v>585</v>
+      </c>
+      <c r="D804" s="118">
+        <v>1885</v>
+      </c>
+      <c r="E804" s="118">
+        <v>1899</v>
+      </c>
+      <c r="F804" s="48"/>
+      <c r="G804" s="48"/>
+      <c r="H804" s="177" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I804" s="27" t="s">
+        <v>2754</v>
+      </c>
+      <c r="J804" s="48" t="s">
+        <v>2755</v>
+      </c>
+      <c r="K804" s="9"/>
+      <c r="L804" s="9"/>
+      <c r="M804" s="9"/>
+      <c r="N804" s="9"/>
+      <c r="O804" s="9"/>
+      <c r="P804" s="9"/>
+      <c r="Q804" s="9"/>
+      <c r="R804" s="9"/>
+      <c r="S804" s="9"/>
+      <c r="T804" s="9"/>
+      <c r="U804" s="9"/>
+      <c r="V804" s="9"/>
+      <c r="W804" s="9"/>
+      <c r="X804" s="9"/>
+      <c r="Y804" s="9"/>
     </row>
     <row r="805" spans="1:25" ht="15.75" customHeight="1">
       <c r="A805" t="s">
         <v>3490</v>
       </c>
-      <c r="B805" t="s">
+      <c r="C805" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D805">
+        <v>1861</v>
+      </c>
+      <c r="E805">
+        <v>1926</v>
+      </c>
+      <c r="F805" t="s">
+        <v>20</v>
+      </c>
+      <c r="G805" t="s">
+        <v>20</v>
+      </c>
+      <c r="H805" s="135" t="s">
+        <v>3491</v>
+      </c>
+      <c r="I805" t="s">
+        <v>3492</v>
+      </c>
+      <c r="J805" t="s">
+        <v>3493</v>
+      </c>
+    </row>
+    <row r="806" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A806" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B806" t="s">
         <v>4262</v>
       </c>
-      <c r="C805" t="s">
+      <c r="C806" t="s">
         <v>4263</v>
       </c>
-      <c r="D805">
+      <c r="D806">
         <v>1865</v>
       </c>
-      <c r="E805">
+      <c r="E806">
         <v>1934</v>
       </c>
-      <c r="G805" t="s">
+      <c r="G806" t="s">
         <v>4264</v>
       </c>
-      <c r="H805" s="137" t="s">
+      <c r="H806" s="137" t="s">
         <v>4265</v>
       </c>
-      <c r="I805" t="s">
+      <c r="I806" t="s">
         <v>4266</v>
       </c>
-      <c r="J805" t="s">
+      <c r="J806" t="s">
         <v>4267</v>
       </c>
     </row>
-    <row r="806" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A806" s="1" t="s">
+    <row r="807" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A807" s="1" t="s">
         <v>2756</v>
       </c>
-      <c r="B806" s="1"/>
-      <c r="C806" s="1" t="s">
+      <c r="B807" s="1"/>
+      <c r="C807" s="1" t="s">
         <v>2757</v>
       </c>
-      <c r="D806" s="1">
+      <c r="D807" s="1">
         <v>1848</v>
       </c>
-      <c r="E806" s="1">
+      <c r="E807" s="1">
         <v>1921</v>
       </c>
-      <c r="F806" s="1" t="s">
+      <c r="F807" s="1" t="s">
         <v>2758</v>
       </c>
-      <c r="G806" s="1" t="s">
+      <c r="G807" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H806" s="1" t="s">
+      <c r="H807" s="1" t="s">
         <v>2759</v>
       </c>
-      <c r="I806" s="15" t="s">
+      <c r="I807" s="15" t="s">
         <v>2760</v>
       </c>
-      <c r="J806" s="1" t="s">
+      <c r="J807" s="1" t="s">
         <v>2761</v>
       </c>
-      <c r="K806" s="1"/>
-      <c r="L806" s="1"/>
-      <c r="M806" s="1"/>
-      <c r="N806" s="1"/>
-      <c r="O806" s="1"/>
-      <c r="P806" s="1"/>
-      <c r="Q806" s="1"/>
-      <c r="R806" s="1"/>
-      <c r="S806" s="1"/>
-      <c r="T806" s="1"/>
-      <c r="U806" s="1"/>
-      <c r="V806" s="1"/>
-      <c r="W806" s="1"/>
-      <c r="X806" s="1"/>
-      <c r="Y806" s="1"/>
-    </row>
-    <row r="807" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A807" s="25" t="s">
+      <c r="K807" s="1"/>
+      <c r="L807" s="1"/>
+      <c r="M807" s="1"/>
+      <c r="N807" s="1"/>
+      <c r="O807" s="1"/>
+      <c r="P807" s="1"/>
+      <c r="Q807" s="1"/>
+      <c r="R807" s="1"/>
+      <c r="S807" s="1"/>
+      <c r="T807" s="1"/>
+      <c r="U807" s="1"/>
+      <c r="V807" s="1"/>
+      <c r="W807" s="1"/>
+      <c r="X807" s="1"/>
+      <c r="Y807" s="1"/>
+    </row>
+    <row r="808" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A808" s="25" t="s">
         <v>2762</v>
       </c>
-      <c r="B807" s="26" t="s">
+      <c r="B808" s="26" t="s">
         <v>2763</v>
       </c>
-      <c r="C807" s="25" t="s">
+      <c r="C808" s="25" t="s">
         <v>2764</v>
       </c>
-      <c r="D807" s="25">
+      <c r="D808" s="25">
         <v>1835</v>
       </c>
-      <c r="E807" s="25">
+      <c r="E808" s="25">
         <v>1921</v>
       </c>
-      <c r="F807" s="25" t="s">
+      <c r="F808" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="G807" s="25" t="s">
+      <c r="G808" s="25" t="s">
         <v>2765</v>
       </c>
-      <c r="H807" s="26" t="s">
+      <c r="H808" s="26" t="s">
         <v>2766</v>
       </c>
-      <c r="I807" s="186" t="s">
+      <c r="I808" s="186" t="s">
         <v>2767</v>
       </c>
-      <c r="J807" s="25" t="s">
+      <c r="J808" s="25" t="s">
         <v>2768</v>
       </c>
-      <c r="K807" s="25"/>
-      <c r="L807" s="25"/>
-      <c r="M807" s="25"/>
-      <c r="N807" s="25"/>
-      <c r="O807" s="25"/>
-      <c r="P807" s="25"/>
-      <c r="Q807" s="25"/>
-      <c r="R807" s="25"/>
-      <c r="S807" s="25"/>
-      <c r="T807" s="25"/>
-      <c r="U807" s="25"/>
-      <c r="V807" s="25"/>
-      <c r="W807" s="25"/>
-      <c r="X807" s="25"/>
-      <c r="Y807" s="25"/>
-    </row>
-    <row r="808" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A808" s="2" t="s">
+      <c r="K808" s="25"/>
+      <c r="L808" s="25"/>
+      <c r="M808" s="25"/>
+      <c r="N808" s="25"/>
+      <c r="O808" s="25"/>
+      <c r="P808" s="25"/>
+      <c r="Q808" s="25"/>
+      <c r="R808" s="25"/>
+      <c r="S808" s="25"/>
+      <c r="T808" s="25"/>
+      <c r="U808" s="25"/>
+      <c r="V808" s="25"/>
+      <c r="W808" s="25"/>
+      <c r="X808" s="25"/>
+      <c r="Y808" s="25"/>
+    </row>
+    <row r="809" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A809" s="2" t="s">
         <v>2769</v>
       </c>
-      <c r="B808" s="2" t="s">
+      <c r="B809" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="C808" s="2" t="s">
+      <c r="C809" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D808" s="2">
+      <c r="D809" s="2">
         <v>1811</v>
       </c>
-      <c r="E808" s="2">
+      <c r="E809" s="2">
         <v>1879</v>
       </c>
-      <c r="F808" s="2" t="s">
+      <c r="F809" s="2" t="s">
         <v>2770</v>
       </c>
-      <c r="G808" s="2" t="s">
+      <c r="G809" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H808" s="2" t="s">
+      <c r="H809" s="2" t="s">
         <v>2771</v>
       </c>
-      <c r="I808" s="53" t="s">
+      <c r="I809" s="53" t="s">
         <v>2772</v>
       </c>
-      <c r="J808" s="2" t="s">
+      <c r="J809" s="2" t="s">
         <v>2773</v>
       </c>
-      <c r="K808" s="1"/>
-      <c r="L808" s="1"/>
-      <c r="M808" s="1"/>
-      <c r="N808" s="1"/>
-      <c r="O808" s="1"/>
-      <c r="P808" s="1"/>
-      <c r="Q808" s="1"/>
-      <c r="R808" s="1"/>
-      <c r="S808" s="1"/>
-      <c r="T808" s="1"/>
-      <c r="U808" s="1"/>
-      <c r="V808" s="1"/>
-      <c r="W808" s="1"/>
-      <c r="X808" s="1"/>
-      <c r="Y808" s="1"/>
-    </row>
-    <row r="809" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A809" t="s">
-        <v>4069</v>
-      </c>
-      <c r="C809" t="s">
-        <v>161</v>
-      </c>
-      <c r="D809">
-        <v>1848</v>
-      </c>
-      <c r="E809">
-        <v>1930</v>
-      </c>
-      <c r="F809" t="s">
-        <v>82</v>
-      </c>
-      <c r="G809" t="s">
-        <v>13</v>
-      </c>
-      <c r="H809" s="137" t="s">
-        <v>4070</v>
-      </c>
-      <c r="I809" t="s">
-        <v>4071</v>
-      </c>
-      <c r="J809" t="s">
-        <v>4072</v>
-      </c>
+      <c r="K809" s="1"/>
+      <c r="L809" s="1"/>
+      <c r="M809" s="1"/>
+      <c r="N809" s="1"/>
+      <c r="O809" s="1"/>
+      <c r="P809" s="1"/>
+      <c r="Q809" s="1"/>
+      <c r="R809" s="1"/>
+      <c r="S809" s="1"/>
+      <c r="T809" s="1"/>
+      <c r="U809" s="1"/>
+      <c r="V809" s="1"/>
+      <c r="W809" s="1"/>
+      <c r="X809" s="1"/>
+      <c r="Y809" s="1"/>
     </row>
     <row r="810" spans="1:25" ht="15.75" customHeight="1">
       <c r="A810" t="s">
-        <v>3494</v>
+        <v>4069</v>
       </c>
       <c r="C810" t="s">
-        <v>3495</v>
+        <v>161</v>
       </c>
       <c r="D810">
-        <v>1841</v>
+        <v>1848</v>
       </c>
       <c r="E810">
         <v>1930</v>
       </c>
       <c r="F810" t="s">
+        <v>82</v>
+      </c>
+      <c r="G810" t="s">
+        <v>13</v>
+      </c>
+      <c r="H810" s="137" t="s">
+        <v>4070</v>
+      </c>
+      <c r="I810" t="s">
+        <v>4071</v>
+      </c>
+      <c r="J810" t="s">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="811" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A811" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C811" t="s">
+        <v>3495</v>
+      </c>
+      <c r="D811">
+        <v>1841</v>
+      </c>
+      <c r="E811">
+        <v>1930</v>
+      </c>
+      <c r="F811" t="s">
         <v>2547</v>
       </c>
-      <c r="H810" s="135" t="s">
+      <c r="H811" s="135" t="s">
         <v>3496</v>
       </c>
-      <c r="I810" t="s">
+      <c r="I811" t="s">
         <v>3497</v>
       </c>
-      <c r="J810" s="15" t="s">
+      <c r="J811" s="15" t="s">
         <v>3498</v>
       </c>
-    </row>
-    <row r="811" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A811" s="10" t="s">
-        <v>2774</v>
-      </c>
-      <c r="B811" s="10" t="s">
-        <v>2775</v>
-      </c>
-      <c r="C811" s="10" t="s">
-        <v>925</v>
-      </c>
-      <c r="D811" s="10">
-        <v>1868</v>
-      </c>
-      <c r="E811" s="10">
-        <v>1945</v>
-      </c>
-      <c r="F811" s="10" t="s">
-        <v>2776</v>
-      </c>
-      <c r="G811" s="10" t="s">
-        <v>2776</v>
-      </c>
-      <c r="H811" s="10" t="s">
-        <v>2777</v>
-      </c>
-      <c r="I811" s="47" t="s">
-        <v>2778</v>
-      </c>
-      <c r="J811" s="10" t="s">
-        <v>2779</v>
-      </c>
-      <c r="K811" s="1"/>
-      <c r="L811" s="1"/>
-      <c r="M811" s="1"/>
-      <c r="N811" s="1"/>
-      <c r="O811" s="1"/>
-      <c r="P811" s="1"/>
-      <c r="Q811" s="1"/>
-      <c r="R811" s="1"/>
-      <c r="S811" s="1"/>
-      <c r="T811" s="1"/>
-      <c r="U811" s="1"/>
-      <c r="V811" s="1"/>
-      <c r="W811" s="1"/>
-      <c r="X811" s="1"/>
-      <c r="Y811" s="1"/>
     </row>
     <row r="812" spans="1:25" ht="15.75" customHeight="1">
       <c r="A812" s="10" t="s">
-        <v>2780</v>
-      </c>
-      <c r="B812" s="10"/>
-      <c r="C812" s="10"/>
-      <c r="D812" s="10"/>
-      <c r="E812" s="10"/>
-      <c r="F812" s="10"/>
-      <c r="G812" s="10"/>
+        <v>2774</v>
+      </c>
+      <c r="B812" s="10" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C812" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="D812" s="10">
+        <v>1868</v>
+      </c>
+      <c r="E812" s="10">
+        <v>1945</v>
+      </c>
+      <c r="F812" s="10" t="s">
+        <v>2776</v>
+      </c>
+      <c r="G812" s="10" t="s">
+        <v>2776</v>
+      </c>
       <c r="H812" s="10" t="s">
-        <v>2781</v>
-      </c>
-      <c r="I812" s="16"/>
+        <v>2777</v>
+      </c>
+      <c r="I812" s="47" t="s">
+        <v>2778</v>
+      </c>
       <c r="J812" s="10" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="K812" s="1"/>
       <c r="L812" s="1"/>
@@ -47070,109 +47083,97 @@
       <c r="Y812" s="1"/>
     </row>
     <row r="813" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A813" t="s">
+      <c r="A813" s="10" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B813" s="10"/>
+      <c r="C813" s="10"/>
+      <c r="D813" s="10"/>
+      <c r="E813" s="10"/>
+      <c r="F813" s="10"/>
+      <c r="G813" s="10"/>
+      <c r="H813" s="10" t="s">
+        <v>2781</v>
+      </c>
+      <c r="I813" s="16"/>
+      <c r="J813" s="10" t="s">
+        <v>2780</v>
+      </c>
+      <c r="K813" s="1"/>
+      <c r="L813" s="1"/>
+      <c r="M813" s="1"/>
+      <c r="N813" s="1"/>
+      <c r="O813" s="1"/>
+      <c r="P813" s="1"/>
+      <c r="Q813" s="1"/>
+      <c r="R813" s="1"/>
+      <c r="S813" s="1"/>
+      <c r="T813" s="1"/>
+      <c r="U813" s="1"/>
+      <c r="V813" s="1"/>
+      <c r="W813" s="1"/>
+      <c r="X813" s="1"/>
+      <c r="Y813" s="1"/>
+    </row>
+    <row r="814" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A814" t="s">
         <v>4073</v>
       </c>
-      <c r="C813" t="s">
+      <c r="C814" t="s">
         <v>11</v>
       </c>
-      <c r="D813">
+      <c r="D814">
         <v>1879</v>
       </c>
-      <c r="E813">
+      <c r="E814">
         <v>1957</v>
       </c>
-      <c r="F813" t="s">
+      <c r="F814" t="s">
         <v>534</v>
       </c>
-      <c r="G813" t="s">
+      <c r="G814" t="s">
         <v>20</v>
       </c>
-      <c r="H813" t="s">
+      <c r="H814" t="s">
         <v>4074</v>
       </c>
-      <c r="I813" t="s">
+      <c r="I814" t="s">
         <v>4075</v>
       </c>
-      <c r="J813" t="s">
+      <c r="J814" t="s">
         <v>4076</v>
       </c>
     </row>
-    <row r="814" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A814" s="1" t="s">
+    <row r="815" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A815" s="1" t="s">
         <v>2782</v>
       </c>
-      <c r="B814" s="1" t="s">
+      <c r="B815" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="C814" s="1" t="s">
+      <c r="C815" s="1" t="s">
         <v>2783</v>
       </c>
-      <c r="D814" s="1">
+      <c r="D815" s="1">
         <v>1851</v>
       </c>
-      <c r="E814" s="1">
+      <c r="E815" s="1">
         <v>1927</v>
       </c>
-      <c r="F814" s="1" t="s">
+      <c r="F815" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G814" s="1" t="s">
+      <c r="G815" s="1" t="s">
         <v>2784</v>
       </c>
-      <c r="H814" s="1" t="s">
+      <c r="H815" s="1" t="s">
         <v>2785</v>
       </c>
-      <c r="I814" s="4" t="s">
+      <c r="I815" s="4" t="s">
         <v>2786</v>
       </c>
-      <c r="J814" s="1" t="s">
+      <c r="J815" s="1" t="s">
         <v>2787</v>
-      </c>
-      <c r="K814" s="1"/>
-      <c r="L814" s="1"/>
-      <c r="M814" s="1"/>
-      <c r="N814" s="1"/>
-      <c r="O814" s="1"/>
-      <c r="P814" s="1"/>
-      <c r="Q814" s="1"/>
-      <c r="R814" s="1"/>
-      <c r="S814" s="1"/>
-      <c r="T814" s="1"/>
-      <c r="U814" s="1"/>
-      <c r="V814" s="1"/>
-      <c r="W814" s="1"/>
-      <c r="X814" s="1"/>
-      <c r="Y814" s="1"/>
-    </row>
-    <row r="815" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A815" s="132" t="s">
-        <v>2970</v>
-      </c>
-      <c r="B815" s="132"/>
-      <c r="C815" s="132" t="s">
-        <v>2971</v>
-      </c>
-      <c r="D815" s="132">
-        <v>1849</v>
-      </c>
-      <c r="E815" s="132">
-        <v>1945</v>
-      </c>
-      <c r="F815" s="132" t="s">
-        <v>2972</v>
-      </c>
-      <c r="G815" s="132" t="s">
-        <v>2547</v>
-      </c>
-      <c r="H815" s="132" t="s">
-        <v>2973</v>
-      </c>
-      <c r="I815" s="133" t="s">
-        <v>2974</v>
-      </c>
-      <c r="J815" s="132" t="s">
-        <v>2975</v>
       </c>
       <c r="K815" s="1"/>
       <c r="L815" s="1"/>
@@ -47191,82 +47192,80 @@
       <c r="Y815" s="1"/>
     </row>
     <row r="816" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A816" s="25" t="s">
-        <v>2788</v>
-      </c>
-      <c r="B816" s="26" t="s">
-        <v>2789</v>
-      </c>
-      <c r="C816" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D816" s="25">
-        <v>1844</v>
-      </c>
-      <c r="E816" s="25">
-        <v>1930</v>
-      </c>
-      <c r="F816" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G816" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="H816" s="26" t="s">
-        <v>2790</v>
-      </c>
-      <c r="I816" s="186" t="s">
-        <v>2791</v>
-      </c>
-      <c r="J816" s="25" t="s">
-        <v>2792</v>
-      </c>
-      <c r="K816" s="9"/>
-      <c r="L816" s="9"/>
-      <c r="M816" s="9"/>
-      <c r="N816" s="9"/>
-      <c r="O816" s="9"/>
-      <c r="P816" s="9"/>
-      <c r="Q816" s="9"/>
-      <c r="R816" s="9"/>
-      <c r="S816" s="9"/>
-      <c r="T816" s="9"/>
-      <c r="U816" s="9"/>
-      <c r="V816" s="9"/>
-      <c r="W816" s="9"/>
-      <c r="X816" s="9"/>
-      <c r="Y816" s="9"/>
+      <c r="A816" s="132" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B816" s="132"/>
+      <c r="C816" s="132" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D816" s="132">
+        <v>1849</v>
+      </c>
+      <c r="E816" s="132">
+        <v>1945</v>
+      </c>
+      <c r="F816" s="132" t="s">
+        <v>2972</v>
+      </c>
+      <c r="G816" s="132" t="s">
+        <v>2547</v>
+      </c>
+      <c r="H816" s="132" t="s">
+        <v>2973</v>
+      </c>
+      <c r="I816" s="133" t="s">
+        <v>2974</v>
+      </c>
+      <c r="J816" s="132" t="s">
+        <v>2975</v>
+      </c>
+      <c r="K816" s="1"/>
+      <c r="L816" s="1"/>
+      <c r="M816" s="1"/>
+      <c r="N816" s="1"/>
+      <c r="O816" s="1"/>
+      <c r="P816" s="1"/>
+      <c r="Q816" s="1"/>
+      <c r="R816" s="1"/>
+      <c r="S816" s="1"/>
+      <c r="T816" s="1"/>
+      <c r="U816" s="1"/>
+      <c r="V816" s="1"/>
+      <c r="W816" s="1"/>
+      <c r="X816" s="1"/>
+      <c r="Y816" s="1"/>
     </row>
     <row r="817" spans="1:25" ht="15.75" customHeight="1">
       <c r="A817" s="25" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
       <c r="B817" s="26" t="s">
-        <v>2794</v>
+        <v>2789</v>
       </c>
       <c r="C817" s="25" t="s">
-        <v>2795</v>
+        <v>11</v>
       </c>
       <c r="D817" s="25">
-        <v>1852</v>
+        <v>1844</v>
       </c>
       <c r="E817" s="25">
-        <v>1937</v>
+        <v>1930</v>
       </c>
       <c r="F817" s="25" t="s">
-        <v>2796</v>
+        <v>20</v>
       </c>
       <c r="G817" s="25" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H817" s="26" t="s">
-        <v>2797</v>
-      </c>
-      <c r="I817" s="3" t="s">
-        <v>2798</v>
+        <v>2790</v>
+      </c>
+      <c r="I817" s="186" t="s">
+        <v>2791</v>
       </c>
       <c r="J817" s="25" t="s">
-        <v>2799</v>
+        <v>2792</v>
       </c>
       <c r="K817" s="9"/>
       <c r="L817" s="9"/>
@@ -47285,80 +47284,82 @@
       <c r="Y817" s="9"/>
     </row>
     <row r="818" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A818" s="10" t="s">
+      <c r="A818" s="25" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B818" s="26" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C818" s="25" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D818" s="25">
+        <v>1852</v>
+      </c>
+      <c r="E818" s="25">
+        <v>1937</v>
+      </c>
+      <c r="F818" s="25" t="s">
+        <v>2796</v>
+      </c>
+      <c r="G818" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H818" s="26" t="s">
+        <v>2797</v>
+      </c>
+      <c r="I818" s="3" t="s">
+        <v>2798</v>
+      </c>
+      <c r="J818" s="25" t="s">
+        <v>2799</v>
+      </c>
+      <c r="K818" s="9"/>
+      <c r="L818" s="9"/>
+      <c r="M818" s="9"/>
+      <c r="N818" s="9"/>
+      <c r="O818" s="9"/>
+      <c r="P818" s="9"/>
+      <c r="Q818" s="9"/>
+      <c r="R818" s="9"/>
+      <c r="S818" s="9"/>
+      <c r="T818" s="9"/>
+      <c r="U818" s="9"/>
+      <c r="V818" s="9"/>
+      <c r="W818" s="9"/>
+      <c r="X818" s="9"/>
+      <c r="Y818" s="9"/>
+    </row>
+    <row r="819" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A819" s="10" t="s">
         <v>2800</v>
       </c>
-      <c r="B818" s="10" t="s">
+      <c r="B819" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C818" s="10" t="s">
+      <c r="C819" s="10" t="s">
         <v>2801</v>
       </c>
-      <c r="D818" s="10">
+      <c r="D819" s="10">
         <v>1848</v>
       </c>
-      <c r="E818" s="10">
+      <c r="E819" s="10">
         <v>1918</v>
       </c>
-      <c r="F818" s="10" t="s">
+      <c r="F819" s="10" t="s">
         <v>2802</v>
       </c>
-      <c r="G818" s="10" t="s">
+      <c r="G819" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="H818" s="10" t="s">
+      <c r="H819" s="10" t="s">
         <v>2803</v>
       </c>
-      <c r="I818" s="47" t="s">
+      <c r="I819" s="47" t="s">
         <v>2804</v>
       </c>
-      <c r="J818" s="12" t="s">
+      <c r="J819" s="12" t="s">
         <v>2805</v>
-      </c>
-      <c r="K818" s="13"/>
-      <c r="L818" s="13"/>
-      <c r="M818" s="13"/>
-      <c r="N818" s="13"/>
-      <c r="O818" s="13"/>
-      <c r="P818" s="13"/>
-      <c r="Q818" s="13"/>
-      <c r="R818" s="13"/>
-      <c r="S818" s="13"/>
-      <c r="T818" s="13"/>
-      <c r="U818" s="13"/>
-      <c r="V818" s="13"/>
-      <c r="W818" s="13"/>
-      <c r="X818" s="13"/>
-      <c r="Y818" s="13"/>
-    </row>
-    <row r="819" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A819" s="1" t="s">
-        <v>2806</v>
-      </c>
-      <c r="B819" s="1"/>
-      <c r="C819" s="1" t="s">
-        <v>2807</v>
-      </c>
-      <c r="D819" s="1">
-        <v>1862</v>
-      </c>
-      <c r="E819" s="1">
-        <v>1941</v>
-      </c>
-      <c r="F819" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="G819" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H819" s="1" t="s">
-        <v>2808</v>
-      </c>
-      <c r="I819" s="4" t="s">
-        <v>2809</v>
-      </c>
-      <c r="J819" s="13" t="s">
-        <v>2810</v>
       </c>
       <c r="K819" s="13"/>
       <c r="L819" s="13"/>
@@ -47377,115 +47378,113 @@
       <c r="Y819" s="13"/>
     </row>
     <row r="820" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A820" s="85" t="s">
+      <c r="A820" s="1" t="s">
         <v>2806</v>
       </c>
-      <c r="B820" s="85" t="s">
+      <c r="B820" s="1"/>
+      <c r="C820" s="1" t="s">
+        <v>2807</v>
+      </c>
+      <c r="D820" s="1">
+        <v>1862</v>
+      </c>
+      <c r="E820" s="1">
+        <v>1941</v>
+      </c>
+      <c r="F820" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G820" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H820" s="1" t="s">
+        <v>2808</v>
+      </c>
+      <c r="I820" s="4" t="s">
+        <v>2809</v>
+      </c>
+      <c r="J820" s="13" t="s">
+        <v>2810</v>
+      </c>
+      <c r="K820" s="13"/>
+      <c r="L820" s="13"/>
+      <c r="M820" s="13"/>
+      <c r="N820" s="13"/>
+      <c r="O820" s="13"/>
+      <c r="P820" s="13"/>
+      <c r="Q820" s="13"/>
+      <c r="R820" s="13"/>
+      <c r="S820" s="13"/>
+      <c r="T820" s="13"/>
+      <c r="U820" s="13"/>
+      <c r="V820" s="13"/>
+      <c r="W820" s="13"/>
+      <c r="X820" s="13"/>
+      <c r="Y820" s="13"/>
+    </row>
+    <row r="821" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A821" s="85" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B821" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="C820" s="85" t="s">
+      <c r="C821" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D820" s="84"/>
-      <c r="E820" s="84"/>
-      <c r="F820" s="84"/>
-      <c r="G820" s="84"/>
-      <c r="H820" s="85" t="s">
+      <c r="D821" s="84"/>
+      <c r="E821" s="84"/>
+      <c r="F821" s="84"/>
+      <c r="G821" s="84"/>
+      <c r="H821" s="85" t="s">
         <v>2811</v>
       </c>
-      <c r="I820" s="86"/>
-      <c r="J820" s="85" t="s">
+      <c r="I821" s="86"/>
+      <c r="J821" s="85" t="s">
         <v>2812</v>
       </c>
-      <c r="K820" s="120"/>
-      <c r="L820" s="120"/>
-      <c r="M820" s="120"/>
-      <c r="N820" s="120"/>
-      <c r="O820" s="120"/>
-      <c r="P820" s="120"/>
-      <c r="Q820" s="120"/>
-      <c r="R820" s="120"/>
-      <c r="S820" s="120"/>
-      <c r="T820" s="120"/>
-      <c r="U820" s="120"/>
-      <c r="V820" s="120"/>
-      <c r="W820" s="120"/>
-      <c r="X820" s="120"/>
-      <c r="Y820" s="120"/>
-    </row>
-    <row r="821" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A821" s="25" t="s">
+      <c r="K821" s="120"/>
+      <c r="L821" s="120"/>
+      <c r="M821" s="120"/>
+      <c r="N821" s="120"/>
+      <c r="O821" s="120"/>
+      <c r="P821" s="120"/>
+      <c r="Q821" s="120"/>
+      <c r="R821" s="120"/>
+      <c r="S821" s="120"/>
+      <c r="T821" s="120"/>
+      <c r="U821" s="120"/>
+      <c r="V821" s="120"/>
+      <c r="W821" s="120"/>
+      <c r="X821" s="120"/>
+      <c r="Y821" s="120"/>
+    </row>
+    <row r="822" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A822" s="25" t="s">
         <v>2813</v>
       </c>
-      <c r="B821" s="25" t="s">
+      <c r="B822" s="25" t="s">
         <v>479</v>
       </c>
-      <c r="C821" s="25" t="s">
+      <c r="C822" s="25" t="s">
         <v>2814</v>
       </c>
-      <c r="D821" s="25">
+      <c r="D822" s="25">
         <v>1823</v>
       </c>
-      <c r="E821" s="25">
+      <c r="E822" s="25">
         <v>1911</v>
       </c>
-      <c r="F821" s="25"/>
-      <c r="G821" s="25" t="s">
+      <c r="F822" s="25"/>
+      <c r="G822" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H821" s="26" t="s">
+      <c r="H822" s="26" t="s">
         <v>2815</v>
       </c>
-      <c r="I821" s="199"/>
-      <c r="J821" s="25" t="s">
+      <c r="I822" s="199"/>
+      <c r="J822" s="25" t="s">
         <v>2816</v>
-      </c>
-      <c r="K821" s="25"/>
-      <c r="L821" s="25"/>
-      <c r="M821" s="25"/>
-      <c r="N821" s="25"/>
-      <c r="O821" s="25"/>
-      <c r="P821" s="25"/>
-      <c r="Q821" s="25"/>
-      <c r="R821" s="25"/>
-      <c r="S821" s="25"/>
-      <c r="T821" s="25"/>
-      <c r="U821" s="25"/>
-      <c r="V821" s="25"/>
-      <c r="W821" s="25"/>
-      <c r="X821" s="25"/>
-      <c r="Y821" s="25"/>
-    </row>
-    <row r="822" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A822" s="22" t="s">
-        <v>2976</v>
-      </c>
-      <c r="B822" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C822" s="22" t="s">
-        <v>2977</v>
-      </c>
-      <c r="D822" s="22">
-        <v>1832</v>
-      </c>
-      <c r="E822" s="22">
-        <v>1913</v>
-      </c>
-      <c r="F822" s="22" t="s">
-        <v>2978</v>
-      </c>
-      <c r="G822" s="22" t="s">
-        <v>2979</v>
-      </c>
-      <c r="H822" s="23" t="s">
-        <v>2980</v>
-      </c>
-      <c r="I822" s="129" t="s">
-        <v>2981</v>
-      </c>
-      <c r="J822" s="22" t="s">
-        <v>2982</v>
       </c>
       <c r="K822" s="25"/>
       <c r="L822" s="25"/>
@@ -47504,280 +47503,288 @@
       <c r="Y822" s="25"/>
     </row>
     <row r="823" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A823" t="s">
-        <v>4316</v>
-      </c>
-      <c r="B823" t="s">
+      <c r="A823" s="22" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B823" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C823" t="s">
-        <v>4317</v>
-      </c>
-      <c r="D823">
-        <v>1838</v>
-      </c>
-      <c r="E823">
-        <v>1901</v>
-      </c>
-      <c r="F823" t="s">
-        <v>20</v>
-      </c>
-      <c r="G823" t="s">
-        <v>122</v>
-      </c>
-      <c r="H823" s="137" t="s">
-        <v>4318</v>
-      </c>
-      <c r="I823" t="s">
-        <v>4319</v>
-      </c>
-      <c r="J823" t="s">
-        <v>4320</v>
-      </c>
+      <c r="C823" s="22" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D823" s="22">
+        <v>1832</v>
+      </c>
+      <c r="E823" s="22">
+        <v>1913</v>
+      </c>
+      <c r="F823" s="22" t="s">
+        <v>2978</v>
+      </c>
+      <c r="G823" s="22" t="s">
+        <v>2979</v>
+      </c>
+      <c r="H823" s="23" t="s">
+        <v>2980</v>
+      </c>
+      <c r="I823" s="129" t="s">
+        <v>2981</v>
+      </c>
+      <c r="J823" s="22" t="s">
+        <v>2982</v>
+      </c>
+      <c r="K823" s="25"/>
+      <c r="L823" s="25"/>
+      <c r="M823" s="25"/>
+      <c r="N823" s="25"/>
+      <c r="O823" s="25"/>
+      <c r="P823" s="25"/>
+      <c r="Q823" s="25"/>
+      <c r="R823" s="25"/>
+      <c r="S823" s="25"/>
+      <c r="T823" s="25"/>
+      <c r="U823" s="25"/>
+      <c r="V823" s="25"/>
+      <c r="W823" s="25"/>
+      <c r="X823" s="25"/>
+      <c r="Y823" s="25"/>
     </row>
     <row r="824" spans="1:25" ht="15.75" customHeight="1">
       <c r="A824" t="s">
+        <v>4316</v>
+      </c>
+      <c r="B824" t="s">
+        <v>18</v>
+      </c>
+      <c r="C824" t="s">
+        <v>4317</v>
+      </c>
+      <c r="D824">
+        <v>1838</v>
+      </c>
+      <c r="E824">
+        <v>1901</v>
+      </c>
+      <c r="F824" t="s">
+        <v>20</v>
+      </c>
+      <c r="G824" t="s">
+        <v>122</v>
+      </c>
+      <c r="H824" s="137" t="s">
+        <v>4318</v>
+      </c>
+      <c r="I824" t="s">
+        <v>4319</v>
+      </c>
+      <c r="J824" t="s">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="825" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A825" t="s">
         <v>3499</v>
       </c>
-      <c r="C824" t="s">
+      <c r="C825" t="s">
         <v>34</v>
       </c>
-      <c r="D824">
+      <c r="D825">
         <v>1846</v>
       </c>
-      <c r="E824">
+      <c r="E825">
         <v>1912</v>
       </c>
-      <c r="F824" t="s">
+      <c r="F825" t="s">
         <v>2615</v>
       </c>
-      <c r="G824" t="s">
+      <c r="G825" t="s">
         <v>20</v>
       </c>
-      <c r="H824" s="135" t="s">
+      <c r="H825" s="135" t="s">
         <v>3500</v>
       </c>
-      <c r="J824" t="s">
+      <c r="J825" t="s">
         <v>3501</v>
       </c>
     </row>
-    <row r="825" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A825" s="1" t="s">
+    <row r="826" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A826" s="1" t="s">
         <v>2817</v>
       </c>
-      <c r="B825" s="1" t="s">
+      <c r="B826" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C825" s="1" t="s">
+      <c r="C826" s="1" t="s">
         <v>2818</v>
       </c>
-      <c r="D825" s="1">
+      <c r="D826" s="1">
         <v>1849</v>
       </c>
-      <c r="E825" s="1">
+      <c r="E826" s="1">
         <v>1934</v>
       </c>
-      <c r="F825" s="1" t="s">
+      <c r="F826" s="1" t="s">
         <v>2819</v>
       </c>
-      <c r="G825" s="1" t="s">
+      <c r="G826" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="H825" s="1" t="s">
+      <c r="H826" s="1" t="s">
         <v>2820</v>
       </c>
-      <c r="I825" s="17" t="s">
+      <c r="I826" s="17" t="s">
         <v>2821</v>
       </c>
-      <c r="J825" s="1" t="s">
+      <c r="J826" s="1" t="s">
         <v>2822</v>
       </c>
-      <c r="K825" s="1"/>
-      <c r="L825" s="1"/>
-      <c r="M825" s="1"/>
-      <c r="N825" s="1"/>
-      <c r="O825" s="1"/>
-      <c r="P825" s="1"/>
-      <c r="Q825" s="1"/>
-      <c r="R825" s="1"/>
-      <c r="S825" s="1"/>
-      <c r="T825" s="1"/>
-      <c r="U825" s="1"/>
-      <c r="V825" s="1"/>
-      <c r="W825" s="1"/>
-      <c r="X825" s="1"/>
-      <c r="Y825" s="1"/>
-    </row>
-    <row r="826" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A826" t="s">
+      <c r="K826" s="1"/>
+      <c r="L826" s="1"/>
+      <c r="M826" s="1"/>
+      <c r="N826" s="1"/>
+      <c r="O826" s="1"/>
+      <c r="P826" s="1"/>
+      <c r="Q826" s="1"/>
+      <c r="R826" s="1"/>
+      <c r="S826" s="1"/>
+      <c r="T826" s="1"/>
+      <c r="U826" s="1"/>
+      <c r="V826" s="1"/>
+      <c r="W826" s="1"/>
+      <c r="X826" s="1"/>
+      <c r="Y826" s="1"/>
+    </row>
+    <row r="827" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A827" t="s">
         <v>4077</v>
       </c>
-      <c r="C826" t="s">
+      <c r="C827" t="s">
         <v>4078</v>
       </c>
-      <c r="D826">
+      <c r="D827">
         <v>1868</v>
       </c>
-      <c r="E826">
+      <c r="E827">
         <v>1913</v>
       </c>
-      <c r="F826" t="s">
+      <c r="F827" t="s">
         <v>29</v>
       </c>
-      <c r="G826" t="s">
+      <c r="G827" t="s">
         <v>567</v>
       </c>
-      <c r="H826" t="s">
+      <c r="H827" t="s">
         <v>4079</v>
       </c>
-      <c r="I826" s="124" t="s">
+      <c r="I827" s="124" t="s">
         <v>4080</v>
       </c>
-      <c r="J826" t="s">
+      <c r="J827" t="s">
         <v>4081</v>
       </c>
     </row>
-    <row r="827" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A827" s="25" t="s">
+    <row r="828" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A828" s="25" t="s">
         <v>2823</v>
       </c>
-      <c r="B827" s="25" t="s">
+      <c r="B828" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="C827" s="25" t="s">
+      <c r="C828" s="25" t="s">
         <v>2824</v>
       </c>
-      <c r="D827" s="25">
+      <c r="D828" s="25">
         <v>1842</v>
       </c>
-      <c r="E827" s="25">
+      <c r="E828" s="25">
         <v>1907</v>
       </c>
-      <c r="F827" s="25" t="s">
+      <c r="F828" s="25" t="s">
         <v>906</v>
       </c>
-      <c r="G827" s="25" t="s">
+      <c r="G828" s="25" t="s">
         <v>906</v>
       </c>
-      <c r="H827" s="26" t="s">
+      <c r="H828" s="26" t="s">
         <v>2825</v>
       </c>
-      <c r="I827" s="186" t="s">
+      <c r="I828" s="186" t="s">
         <v>2826</v>
       </c>
-      <c r="J827" s="25" t="s">
+      <c r="J828" s="25" t="s">
         <v>2827</v>
       </c>
-      <c r="K827" s="25"/>
-      <c r="L827" s="25"/>
-      <c r="M827" s="25"/>
-      <c r="N827" s="25"/>
-      <c r="O827" s="25"/>
-      <c r="P827" s="25"/>
-      <c r="Q827" s="25"/>
-      <c r="R827" s="25"/>
-      <c r="S827" s="25"/>
-      <c r="T827" s="25"/>
-      <c r="U827" s="25"/>
-      <c r="V827" s="25"/>
-      <c r="W827" s="25"/>
-      <c r="X827" s="25"/>
-      <c r="Y827" s="25"/>
-    </row>
-    <row r="828" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A828" t="s">
+      <c r="K828" s="25"/>
+      <c r="L828" s="25"/>
+      <c r="M828" s="25"/>
+      <c r="N828" s="25"/>
+      <c r="O828" s="25"/>
+      <c r="P828" s="25"/>
+      <c r="Q828" s="25"/>
+      <c r="R828" s="25"/>
+      <c r="S828" s="25"/>
+      <c r="T828" s="25"/>
+      <c r="U828" s="25"/>
+      <c r="V828" s="25"/>
+      <c r="W828" s="25"/>
+      <c r="X828" s="25"/>
+      <c r="Y828" s="25"/>
+    </row>
+    <row r="829" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A829" t="s">
         <v>4321</v>
       </c>
-      <c r="C828" t="s">
+      <c r="C829" t="s">
         <v>4322</v>
       </c>
-      <c r="D828">
+      <c r="D829">
         <v>1819</v>
       </c>
-      <c r="E828">
+      <c r="E829">
         <v>1884</v>
       </c>
-      <c r="F828" t="s">
+      <c r="F829" t="s">
         <v>3828</v>
       </c>
-      <c r="G828" t="s">
+      <c r="G829" t="s">
         <v>420</v>
       </c>
-      <c r="H828" s="137" t="s">
+      <c r="H829" s="137" t="s">
         <v>4323</v>
       </c>
-      <c r="I828" t="s">
+      <c r="I829" t="s">
         <v>4324</v>
       </c>
-      <c r="J828" t="s">
+      <c r="J829" t="s">
         <v>4325</v>
       </c>
     </row>
-    <row r="829" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A829" s="2" t="s">
+    <row r="830" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A830" s="2" t="s">
         <v>2828</v>
       </c>
-      <c r="B829" s="2"/>
-      <c r="C829" s="2" t="s">
+      <c r="B830" s="2"/>
+      <c r="C830" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D829" s="2">
+      <c r="D830" s="2">
         <v>1830</v>
       </c>
-      <c r="E829" s="2">
+      <c r="E830" s="2">
         <v>1902</v>
       </c>
-      <c r="F829" s="2" t="s">
+      <c r="F830" s="2" t="s">
         <v>2829</v>
       </c>
-      <c r="G829" s="2" t="s">
+      <c r="G830" s="2" t="s">
         <v>2830</v>
       </c>
-      <c r="H829" s="2" t="s">
+      <c r="H830" s="2" t="s">
         <v>2831</v>
       </c>
-      <c r="I829" s="18"/>
-      <c r="J829" s="2" t="s">
+      <c r="I830" s="18"/>
+      <c r="J830" s="2" t="s">
         <v>2832</v>
-      </c>
-      <c r="K829" s="1"/>
-      <c r="L829" s="1"/>
-      <c r="M829" s="1"/>
-      <c r="N829" s="1"/>
-      <c r="O829" s="1"/>
-      <c r="P829" s="1"/>
-      <c r="Q829" s="1"/>
-      <c r="R829" s="1"/>
-      <c r="S829" s="1"/>
-      <c r="T829" s="1"/>
-      <c r="U829" s="1"/>
-      <c r="V829" s="1"/>
-      <c r="W829" s="1"/>
-      <c r="X829" s="1"/>
-      <c r="Y829" s="1"/>
-    </row>
-    <row r="830" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A830" s="132" t="s">
-        <v>2983</v>
-      </c>
-      <c r="B830" s="132"/>
-      <c r="C830" s="132" t="s">
-        <v>2984</v>
-      </c>
-      <c r="D830" s="132">
-        <v>1851</v>
-      </c>
-      <c r="E830" s="132">
-        <v>1922</v>
-      </c>
-      <c r="F830" s="132"/>
-      <c r="G830" s="132"/>
-      <c r="H830" s="132" t="s">
-        <v>2985</v>
-      </c>
-      <c r="I830" s="134"/>
-      <c r="J830" s="132" t="s">
-        <v>3532</v>
       </c>
       <c r="K830" s="1"/>
       <c r="L830" s="1"/>
@@ -47796,104 +47803,96 @@
       <c r="Y830" s="1"/>
     </row>
     <row r="831" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A831" t="s">
+      <c r="A831" s="132" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B831" s="132"/>
+      <c r="C831" s="132" t="s">
+        <v>2984</v>
+      </c>
+      <c r="D831" s="132">
+        <v>1851</v>
+      </c>
+      <c r="E831" s="132">
+        <v>1922</v>
+      </c>
+      <c r="F831" s="132"/>
+      <c r="G831" s="132"/>
+      <c r="H831" s="132" t="s">
+        <v>2985</v>
+      </c>
+      <c r="I831" s="134"/>
+      <c r="J831" s="132" t="s">
+        <v>3532</v>
+      </c>
+      <c r="K831" s="1"/>
+      <c r="L831" s="1"/>
+      <c r="M831" s="1"/>
+      <c r="N831" s="1"/>
+      <c r="O831" s="1"/>
+      <c r="P831" s="1"/>
+      <c r="Q831" s="1"/>
+      <c r="R831" s="1"/>
+      <c r="S831" s="1"/>
+      <c r="T831" s="1"/>
+      <c r="U831" s="1"/>
+      <c r="V831" s="1"/>
+      <c r="W831" s="1"/>
+      <c r="X831" s="1"/>
+      <c r="Y831" s="1"/>
+    </row>
+    <row r="832" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A832" t="s">
         <v>3502</v>
       </c>
-      <c r="B831" t="s">
+      <c r="B832" t="s">
         <v>18</v>
       </c>
-      <c r="C831" t="s">
+      <c r="C832" t="s">
         <v>437</v>
       </c>
-      <c r="D831">
+      <c r="D832">
         <v>1838</v>
       </c>
-      <c r="E831">
+      <c r="E832">
         <v>1917</v>
       </c>
-      <c r="F831" t="s">
+      <c r="F832" t="s">
         <v>3503</v>
       </c>
-      <c r="G831" t="s">
+      <c r="G832" t="s">
         <v>13</v>
       </c>
-      <c r="H831" s="135" t="s">
+      <c r="H832" s="135" t="s">
         <v>3504</v>
       </c>
-      <c r="I831" t="s">
+      <c r="I832" t="s">
         <v>3505</v>
       </c>
-      <c r="J831" t="s">
+      <c r="J832" t="s">
         <v>3506</v>
       </c>
     </row>
-    <row r="832" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A832" s="2" t="s">
+    <row r="833" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A833" s="2" t="s">
         <v>2833</v>
       </c>
-      <c r="B832" s="2" t="s">
+      <c r="B833" s="2" t="s">
         <v>2834</v>
       </c>
-      <c r="C832" s="2" t="s">
+      <c r="C833" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D832" s="2"/>
-      <c r="E832" s="2"/>
-      <c r="F832" s="2"/>
-      <c r="G832" s="2"/>
-      <c r="H832" s="2" t="s">
+      <c r="D833" s="2"/>
+      <c r="E833" s="2"/>
+      <c r="F833" s="2"/>
+      <c r="G833" s="2"/>
+      <c r="H833" s="2" t="s">
         <v>2835</v>
       </c>
-      <c r="I832" s="18"/>
-      <c r="J832" s="2" t="s">
+      <c r="I833" s="18"/>
+      <c r="J833" s="2" t="s">
         <v>2836</v>
-      </c>
-      <c r="K832" s="1"/>
-      <c r="L832" s="1"/>
-      <c r="M832" s="1"/>
-      <c r="N832" s="1"/>
-      <c r="O832" s="1"/>
-      <c r="P832" s="1"/>
-      <c r="Q832" s="1"/>
-      <c r="R832" s="1"/>
-      <c r="S832" s="1"/>
-      <c r="T832" s="1"/>
-      <c r="U832" s="1"/>
-      <c r="V832" s="1"/>
-      <c r="W832" s="1"/>
-      <c r="X832" s="1"/>
-      <c r="Y832" s="1"/>
-    </row>
-    <row r="833" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A833" s="1" t="s">
-        <v>2837</v>
-      </c>
-      <c r="B833" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C833" s="1" t="s">
-        <v>2838</v>
-      </c>
-      <c r="D833" s="1">
-        <v>1864</v>
-      </c>
-      <c r="E833" s="1">
-        <v>1937</v>
-      </c>
-      <c r="F833" s="1" t="s">
-        <v>2839</v>
-      </c>
-      <c r="G833" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H833" s="1" t="s">
-        <v>2840</v>
-      </c>
-      <c r="I833" s="15" t="s">
-        <v>2841</v>
-      </c>
-      <c r="J833" s="1" t="s">
-        <v>2842</v>
       </c>
       <c r="K833" s="1"/>
       <c r="L833" s="1"/>
@@ -47912,346 +47911,360 @@
       <c r="Y833" s="1"/>
     </row>
     <row r="834" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A834" t="s">
-        <v>4082</v>
-      </c>
-      <c r="C834" t="s">
-        <v>4083</v>
-      </c>
-      <c r="D834">
-        <v>1852</v>
-      </c>
-      <c r="E834">
-        <v>1925</v>
-      </c>
-      <c r="F834" t="s">
-        <v>20</v>
-      </c>
-      <c r="G834" t="s">
-        <v>20</v>
-      </c>
-      <c r="H834" t="s">
-        <v>4084</v>
-      </c>
-      <c r="I834" t="s">
-        <v>4085</v>
-      </c>
-      <c r="J834" t="s">
-        <v>4086</v>
-      </c>
+      <c r="A834" s="1" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D834" s="1">
+        <v>1864</v>
+      </c>
+      <c r="E834" s="1">
+        <v>1937</v>
+      </c>
+      <c r="F834" s="1" t="s">
+        <v>2839</v>
+      </c>
+      <c r="G834" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H834" s="1" t="s">
+        <v>2840</v>
+      </c>
+      <c r="I834" s="15" t="s">
+        <v>2841</v>
+      </c>
+      <c r="J834" s="1" t="s">
+        <v>2842</v>
+      </c>
+      <c r="K834" s="1"/>
+      <c r="L834" s="1"/>
+      <c r="M834" s="1"/>
+      <c r="N834" s="1"/>
+      <c r="O834" s="1"/>
+      <c r="P834" s="1"/>
+      <c r="Q834" s="1"/>
+      <c r="R834" s="1"/>
+      <c r="S834" s="1"/>
+      <c r="T834" s="1"/>
+      <c r="U834" s="1"/>
+      <c r="V834" s="1"/>
+      <c r="W834" s="1"/>
+      <c r="X834" s="1"/>
+      <c r="Y834" s="1"/>
     </row>
     <row r="835" spans="1:25" ht="15.75" customHeight="1">
       <c r="A835" t="s">
         <v>4082</v>
       </c>
       <c r="C835" t="s">
-        <v>4087</v>
+        <v>4083</v>
       </c>
       <c r="D835">
-        <v>1847</v>
+        <v>1852</v>
       </c>
       <c r="E835">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F835" t="s">
-        <v>4088</v>
+        <v>20</v>
       </c>
       <c r="G835" t="s">
         <v>20</v>
       </c>
       <c r="H835" t="s">
-        <v>4089</v>
-      </c>
-      <c r="I835" s="124" t="s">
-        <v>4090</v>
+        <v>4084</v>
+      </c>
+      <c r="I835" t="s">
+        <v>4085</v>
       </c>
       <c r="J835" t="s">
-        <v>4091</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="836" spans="1:25" ht="15.75" customHeight="1">
       <c r="A836" t="s">
+        <v>4082</v>
+      </c>
+      <c r="C836" t="s">
+        <v>4087</v>
+      </c>
+      <c r="D836">
+        <v>1847</v>
+      </c>
+      <c r="E836">
+        <v>1927</v>
+      </c>
+      <c r="F836" t="s">
+        <v>4088</v>
+      </c>
+      <c r="G836" t="s">
+        <v>20</v>
+      </c>
+      <c r="H836" t="s">
+        <v>4089</v>
+      </c>
+      <c r="I836" s="124" t="s">
+        <v>4090</v>
+      </c>
+      <c r="J836" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="837" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A837" t="s">
         <v>3507</v>
       </c>
-      <c r="C836" t="s">
+      <c r="C837" t="s">
         <v>1050</v>
       </c>
-      <c r="D836">
+      <c r="D837">
         <v>1858</v>
       </c>
-      <c r="E836">
+      <c r="E837">
         <v>1929</v>
       </c>
-      <c r="F836" t="s">
+      <c r="F837" t="s">
         <v>3508</v>
       </c>
-      <c r="G836" t="s">
+      <c r="G837" t="s">
         <v>3509</v>
       </c>
-      <c r="H836" s="135" t="s">
+      <c r="H837" s="135" t="s">
         <v>3510</v>
       </c>
-      <c r="I836" t="s">
+      <c r="I837" t="s">
         <v>3511</v>
       </c>
-      <c r="J836" t="s">
+      <c r="J837" t="s">
         <v>3512</v>
       </c>
     </row>
-    <row r="837" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A837" s="10" t="s">
+    <row r="838" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A838" s="10" t="s">
         <v>2843</v>
       </c>
-      <c r="B837" s="10" t="s">
+      <c r="B838" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C837" s="10" t="s">
+      <c r="C838" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D837" s="10">
+      <c r="D838" s="10">
         <v>1853</v>
       </c>
-      <c r="E837" s="10">
+      <c r="E838" s="10">
         <v>1925</v>
       </c>
-      <c r="F837" s="10" t="s">
+      <c r="F838" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G837" s="10" t="s">
+      <c r="G838" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H837" s="10" t="s">
+      <c r="H838" s="10" t="s">
         <v>2844</v>
       </c>
-      <c r="I837" s="47" t="s">
+      <c r="I838" s="47" t="s">
         <v>2845</v>
       </c>
-      <c r="J837" s="10" t="s">
+      <c r="J838" s="10" t="s">
         <v>2846</v>
       </c>
-      <c r="K837" s="1"/>
-      <c r="L837" s="1"/>
-      <c r="M837" s="1"/>
-      <c r="N837" s="1"/>
-      <c r="O837" s="1"/>
-      <c r="P837" s="1"/>
-      <c r="Q837" s="1"/>
-      <c r="R837" s="1"/>
-      <c r="S837" s="1"/>
-      <c r="T837" s="1"/>
-      <c r="U837" s="1"/>
-      <c r="V837" s="1"/>
-      <c r="W837" s="1"/>
-      <c r="X837" s="1"/>
-      <c r="Y837" s="1"/>
-    </row>
-    <row r="838" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A838" s="117"/>
-      <c r="B838" s="117"/>
-      <c r="C838" s="117" t="s">
+      <c r="K838" s="1"/>
+      <c r="L838" s="1"/>
+      <c r="M838" s="1"/>
+      <c r="N838" s="1"/>
+      <c r="O838" s="1"/>
+      <c r="P838" s="1"/>
+      <c r="Q838" s="1"/>
+      <c r="R838" s="1"/>
+      <c r="S838" s="1"/>
+      <c r="T838" s="1"/>
+      <c r="U838" s="1"/>
+      <c r="V838" s="1"/>
+      <c r="W838" s="1"/>
+      <c r="X838" s="1"/>
+      <c r="Y838" s="1"/>
+    </row>
+    <row r="839" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A839" s="117"/>
+      <c r="B839" s="117"/>
+      <c r="C839" s="117" t="s">
         <v>805</v>
       </c>
-      <c r="D838" s="117"/>
-      <c r="E838" s="117"/>
-      <c r="F838" s="117"/>
-      <c r="G838" s="117"/>
-      <c r="H838" s="117"/>
-      <c r="I838" s="47"/>
-      <c r="J838" s="115" t="s">
+      <c r="D839" s="117"/>
+      <c r="E839" s="117"/>
+      <c r="F839" s="117"/>
+      <c r="G839" s="117"/>
+      <c r="H839" s="117"/>
+      <c r="I839" s="47"/>
+      <c r="J839" s="115" t="s">
         <v>805</v>
       </c>
-      <c r="K838" s="116"/>
-      <c r="L838" s="116"/>
-      <c r="M838" s="116"/>
-      <c r="N838" s="116"/>
-      <c r="O838" s="116"/>
-      <c r="P838" s="116"/>
-      <c r="Q838" s="116"/>
-      <c r="R838" s="116"/>
-      <c r="S838" s="116"/>
-      <c r="T838" s="116"/>
-      <c r="U838" s="116"/>
-      <c r="V838" s="116"/>
-      <c r="W838" s="116"/>
-      <c r="X838" s="116"/>
-      <c r="Y838" s="116"/>
-    </row>
-    <row r="839" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A839" s="1"/>
-      <c r="B839" s="1"/>
-      <c r="C839" s="1"/>
-      <c r="D839" s="1"/>
-      <c r="E839" s="1"/>
-      <c r="F839" s="1"/>
-      <c r="G839" s="1"/>
-      <c r="H839" s="1"/>
-      <c r="I839" s="1"/>
-      <c r="J839" s="1"/>
-      <c r="K839" s="1"/>
-      <c r="L839" s="1"/>
-      <c r="M839" s="1"/>
-      <c r="N839" s="1"/>
-      <c r="O839" s="1"/>
-      <c r="P839" s="1"/>
-      <c r="Q839" s="1"/>
-      <c r="R839" s="1"/>
-      <c r="S839" s="1"/>
-      <c r="T839" s="1"/>
-      <c r="U839" s="1"/>
-      <c r="V839" s="1"/>
-      <c r="W839" s="1"/>
-      <c r="X839" s="1"/>
-      <c r="Y839" s="1"/>
+      <c r="K839" s="116"/>
+      <c r="L839" s="116"/>
+      <c r="M839" s="116"/>
+      <c r="N839" s="116"/>
+      <c r="O839" s="116"/>
+      <c r="P839" s="116"/>
+      <c r="Q839" s="116"/>
+      <c r="R839" s="116"/>
+      <c r="S839" s="116"/>
+      <c r="T839" s="116"/>
+      <c r="U839" s="116"/>
+      <c r="V839" s="116"/>
+      <c r="W839" s="116"/>
+      <c r="X839" s="116"/>
+      <c r="Y839" s="116"/>
     </row>
     <row r="840" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A840" s="10"/>
-      <c r="B840" s="12" t="s">
+      <c r="A840" s="1"/>
+      <c r="B840" s="1"/>
+      <c r="C840" s="1"/>
+      <c r="D840" s="1"/>
+      <c r="E840" s="1"/>
+      <c r="F840" s="1"/>
+      <c r="G840" s="1"/>
+      <c r="H840" s="1"/>
+      <c r="I840" s="1"/>
+      <c r="J840" s="1"/>
+      <c r="K840" s="1"/>
+      <c r="L840" s="1"/>
+      <c r="M840" s="1"/>
+      <c r="N840" s="1"/>
+      <c r="O840" s="1"/>
+      <c r="P840" s="1"/>
+      <c r="Q840" s="1"/>
+      <c r="R840" s="1"/>
+      <c r="S840" s="1"/>
+      <c r="T840" s="1"/>
+      <c r="U840" s="1"/>
+      <c r="V840" s="1"/>
+      <c r="W840" s="1"/>
+      <c r="X840" s="1"/>
+      <c r="Y840" s="1"/>
+    </row>
+    <row r="841" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A841" s="10"/>
+      <c r="B841" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C840" s="12" t="s">
+      <c r="C841" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="D840" s="12">
+      <c r="D841" s="12">
         <v>12</v>
       </c>
-      <c r="E840" s="12">
+      <c r="E841" s="12">
         <v>41</v>
       </c>
-      <c r="F840" s="12" t="s">
+      <c r="F841" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="G840" s="12" t="s">
+      <c r="G841" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="H840" s="10" t="s">
+      <c r="H841" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="I840" s="46" t="s">
+      <c r="I841" s="46" t="s">
         <v>457</v>
       </c>
-      <c r="J840" s="12" t="s">
+      <c r="J841" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="K840" s="13"/>
-      <c r="L840" s="13"/>
-      <c r="M840" s="13"/>
-      <c r="N840" s="13"/>
-      <c r="O840" s="13"/>
-      <c r="P840" s="13"/>
-      <c r="Q840" s="13"/>
-      <c r="R840" s="13"/>
-      <c r="S840" s="13"/>
-      <c r="T840" s="13"/>
-      <c r="U840" s="13"/>
-      <c r="V840" s="13"/>
-      <c r="W840" s="13"/>
-      <c r="X840" s="13"/>
-      <c r="Y840" s="13"/>
-    </row>
-    <row r="841" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A841" s="22"/>
-      <c r="B841" s="22" t="s">
+      <c r="K841" s="13"/>
+      <c r="L841" s="13"/>
+      <c r="M841" s="13"/>
+      <c r="N841" s="13"/>
+      <c r="O841" s="13"/>
+      <c r="P841" s="13"/>
+      <c r="Q841" s="13"/>
+      <c r="R841" s="13"/>
+      <c r="S841" s="13"/>
+      <c r="T841" s="13"/>
+      <c r="U841" s="13"/>
+      <c r="V841" s="13"/>
+      <c r="W841" s="13"/>
+      <c r="X841" s="13"/>
+      <c r="Y841" s="13"/>
+    </row>
+    <row r="842" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A842" s="22"/>
+      <c r="B842" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="C841" s="22" t="s">
+      <c r="C842" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="D841" s="22">
+      <c r="D842" s="22">
         <v>51</v>
       </c>
-      <c r="E841" s="22">
+      <c r="E842" s="22">
         <v>96</v>
       </c>
-      <c r="F841" s="22" t="s">
+      <c r="F842" s="22" t="s">
         <v>426</v>
       </c>
-      <c r="G841" s="22" t="s">
+      <c r="G842" s="22" t="s">
         <v>426</v>
       </c>
-      <c r="H841" s="23" t="s">
+      <c r="H842" s="23" t="s">
         <v>701</v>
       </c>
-      <c r="I841" s="56" t="s">
+      <c r="I842" s="56" t="s">
         <v>702</v>
       </c>
-      <c r="J841" s="22" t="s">
+      <c r="J842" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="K841" s="25"/>
-      <c r="L841" s="25"/>
-      <c r="M841" s="25"/>
-      <c r="N841" s="25"/>
-      <c r="O841" s="25"/>
-      <c r="P841" s="25"/>
-      <c r="Q841" s="25"/>
-      <c r="R841" s="25"/>
-      <c r="S841" s="25"/>
-      <c r="T841" s="25"/>
-      <c r="U841" s="25"/>
-      <c r="V841" s="25"/>
-      <c r="W841" s="25"/>
-      <c r="X841" s="25"/>
-      <c r="Y841" s="25"/>
-    </row>
-    <row r="842" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A842" s="10"/>
-      <c r="B842" s="10" t="s">
+      <c r="K842" s="25"/>
+      <c r="L842" s="25"/>
+      <c r="M842" s="25"/>
+      <c r="N842" s="25"/>
+      <c r="O842" s="25"/>
+      <c r="P842" s="25"/>
+      <c r="Q842" s="25"/>
+      <c r="R842" s="25"/>
+      <c r="S842" s="25"/>
+      <c r="T842" s="25"/>
+      <c r="U842" s="25"/>
+      <c r="V842" s="25"/>
+      <c r="W842" s="25"/>
+      <c r="X842" s="25"/>
+      <c r="Y842" s="25"/>
+    </row>
+    <row r="843" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A843" s="10"/>
+      <c r="B843" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="C842" s="10" t="s">
+      <c r="C843" s="10" t="s">
         <v>755</v>
       </c>
-      <c r="D842" s="10">
+      <c r="D843" s="10">
         <v>1220</v>
       </c>
-      <c r="E842" s="10">
+      <c r="E843" s="10">
         <v>1272</v>
       </c>
-      <c r="F842" s="10"/>
-      <c r="G842" s="10" t="s">
+      <c r="F843" s="10"/>
+      <c r="G843" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="H842" s="10" t="s">
+      <c r="H843" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="I842" s="11" t="s">
+      <c r="I843" s="11" t="s">
         <v>757</v>
       </c>
-      <c r="J842" s="10" t="s">
+      <c r="J843" s="10" t="s">
         <v>755</v>
-      </c>
-      <c r="K842" s="1"/>
-      <c r="L842" s="1"/>
-      <c r="M842" s="1"/>
-      <c r="N842" s="1"/>
-      <c r="O842" s="1"/>
-      <c r="P842" s="1"/>
-      <c r="Q842" s="1"/>
-      <c r="R842" s="1"/>
-      <c r="S842" s="1"/>
-      <c r="T842" s="1"/>
-      <c r="U842" s="1"/>
-      <c r="V842" s="1"/>
-      <c r="W842" s="1"/>
-      <c r="X842" s="1"/>
-      <c r="Y842" s="1"/>
-    </row>
-    <row r="843" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A843" s="1"/>
-      <c r="B843" s="1"/>
-      <c r="C843" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="D843" s="1"/>
-      <c r="E843" s="1"/>
-      <c r="F843" s="1"/>
-      <c r="G843" s="1"/>
-      <c r="H843" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="I843" s="15"/>
-      <c r="J843" s="1" t="s">
-        <v>916</v>
       </c>
       <c r="K843" s="1"/>
       <c r="L843" s="1"/>
@@ -48270,31 +48283,21 @@
       <c r="Y843" s="1"/>
     </row>
     <row r="844" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A844" s="10"/>
-      <c r="B844" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="C844" s="10" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D844" s="10">
-        <v>37</v>
-      </c>
-      <c r="E844" s="10">
-        <v>68</v>
-      </c>
-      <c r="F844" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="G844" s="10"/>
-      <c r="H844" s="10" t="s">
-        <v>1941</v>
-      </c>
-      <c r="I844" s="92" t="s">
-        <v>1942</v>
-      </c>
-      <c r="J844" s="10" t="s">
-        <v>1940</v>
+      <c r="A844" s="1"/>
+      <c r="B844" s="1"/>
+      <c r="C844" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="D844" s="1"/>
+      <c r="E844" s="1"/>
+      <c r="F844" s="1"/>
+      <c r="G844" s="1"/>
+      <c r="H844" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="I844" s="15"/>
+      <c r="J844" s="1" t="s">
+        <v>916</v>
       </c>
       <c r="K844" s="1"/>
       <c r="L844" s="1"/>
@@ -48313,164 +48316,206 @@
       <c r="Y844" s="1"/>
     </row>
     <row r="845" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A845" s="2"/>
-      <c r="B845" s="2"/>
-      <c r="C845" s="2" t="s">
+      <c r="A845" s="10"/>
+      <c r="B845" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="C845" s="10" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D845" s="10">
+        <v>37</v>
+      </c>
+      <c r="E845" s="10">
+        <v>68</v>
+      </c>
+      <c r="F845" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="G845" s="10"/>
+      <c r="H845" s="10" t="s">
+        <v>1941</v>
+      </c>
+      <c r="I845" s="92" t="s">
+        <v>1942</v>
+      </c>
+      <c r="J845" s="10" t="s">
+        <v>1940</v>
+      </c>
+      <c r="K845" s="1"/>
+      <c r="L845" s="1"/>
+      <c r="M845" s="1"/>
+      <c r="N845" s="1"/>
+      <c r="O845" s="1"/>
+      <c r="P845" s="1"/>
+      <c r="Q845" s="1"/>
+      <c r="R845" s="1"/>
+      <c r="S845" s="1"/>
+      <c r="T845" s="1"/>
+      <c r="U845" s="1"/>
+      <c r="V845" s="1"/>
+      <c r="W845" s="1"/>
+      <c r="X845" s="1"/>
+      <c r="Y845" s="1"/>
+    </row>
+    <row r="846" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A846" s="2"/>
+      <c r="B846" s="2"/>
+      <c r="C846" s="2" t="s">
         <v>2057</v>
       </c>
-      <c r="D845" s="2">
+      <c r="D846" s="2">
         <v>1792</v>
       </c>
-      <c r="E845" s="2">
+      <c r="E846" s="2">
         <v>1878</v>
       </c>
-      <c r="F845" s="2" t="s">
+      <c r="F846" s="2" t="s">
         <v>2058</v>
       </c>
-      <c r="G845" s="2" t="s">
+      <c r="G846" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="H845" s="2" t="s">
+      <c r="H846" s="2" t="s">
         <v>2059</v>
       </c>
-      <c r="I845" s="49" t="s">
+      <c r="I846" s="49" t="s">
         <v>2060</v>
       </c>
-      <c r="J845" s="2" t="s">
+      <c r="J846" s="2" t="s">
         <v>2061</v>
       </c>
-      <c r="K845" s="10"/>
-      <c r="L845" s="10"/>
-      <c r="M845" s="10"/>
-      <c r="N845" s="10"/>
-      <c r="O845" s="10"/>
-      <c r="P845" s="10"/>
-      <c r="Q845" s="10"/>
-      <c r="R845" s="10"/>
-      <c r="S845" s="10"/>
-      <c r="T845" s="10"/>
-      <c r="U845" s="10"/>
-      <c r="V845" s="10"/>
-      <c r="W845" s="10"/>
-      <c r="X845" s="10"/>
-      <c r="Y845" s="10"/>
-    </row>
-    <row r="846" spans="1:25" ht="15.75" customHeight="1">
-      <c r="C846" t="s">
-        <v>3219</v>
-      </c>
-      <c r="D846">
-        <v>1810</v>
-      </c>
-      <c r="E846">
-        <v>1903</v>
-      </c>
-      <c r="F846" t="s">
-        <v>3220</v>
-      </c>
-      <c r="G846" t="s">
-        <v>3221</v>
-      </c>
-      <c r="H846" s="135" t="s">
-        <v>3222</v>
-      </c>
-      <c r="I846" s="124" t="s">
-        <v>3223</v>
-      </c>
-      <c r="J846" t="s">
-        <v>3224</v>
-      </c>
+      <c r="K846" s="10"/>
+      <c r="L846" s="10"/>
+      <c r="M846" s="10"/>
+      <c r="N846" s="10"/>
+      <c r="O846" s="10"/>
+      <c r="P846" s="10"/>
+      <c r="Q846" s="10"/>
+      <c r="R846" s="10"/>
+      <c r="S846" s="10"/>
+      <c r="T846" s="10"/>
+      <c r="U846" s="10"/>
+      <c r="V846" s="10"/>
+      <c r="W846" s="10"/>
+      <c r="X846" s="10"/>
+      <c r="Y846" s="10"/>
     </row>
     <row r="847" spans="1:25" ht="15.75" customHeight="1">
       <c r="C847" t="s">
+        <v>3219</v>
+      </c>
+      <c r="D847">
+        <v>1810</v>
+      </c>
+      <c r="E847">
+        <v>1903</v>
+      </c>
+      <c r="F847" t="s">
+        <v>3220</v>
+      </c>
+      <c r="G847" t="s">
+        <v>3221</v>
+      </c>
+      <c r="H847" s="135" t="s">
+        <v>3222</v>
+      </c>
+      <c r="I847" s="124" t="s">
+        <v>3223</v>
+      </c>
+      <c r="J847" t="s">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="848" spans="1:25" ht="15.75" customHeight="1">
+      <c r="C848" t="s">
         <v>3302</v>
       </c>
-      <c r="D847">
+      <c r="D848">
         <v>1835</v>
       </c>
-      <c r="E847">
+      <c r="E848">
         <v>1914</v>
       </c>
-      <c r="F847" t="s">
+      <c r="F848" t="s">
         <v>3303</v>
       </c>
-      <c r="G847" t="s">
+      <c r="G848" t="s">
         <v>426</v>
       </c>
-      <c r="H847" s="135" t="s">
+      <c r="H848" s="135" t="s">
         <v>3304</v>
       </c>
-      <c r="I847" t="s">
+      <c r="I848" t="s">
         <v>3305</v>
       </c>
-      <c r="J847" t="s">
+      <c r="J848" t="s">
         <v>3306</v>
       </c>
     </row>
-    <row r="848" spans="1:25" ht="15.75" customHeight="1">
-      <c r="B848" t="s">
+    <row r="849" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B849" t="s">
         <v>453</v>
       </c>
-      <c r="C848" t="s">
+      <c r="C849" t="s">
         <v>2657</v>
       </c>
-      <c r="D848" t="s">
+      <c r="D849" t="s">
         <v>3625</v>
       </c>
-      <c r="E848">
+      <c r="E849">
         <v>337</v>
       </c>
-      <c r="F848" t="s">
+      <c r="F849" t="s">
         <v>3626</v>
       </c>
-      <c r="G848" t="s">
+      <c r="G849" t="s">
         <v>3627</v>
       </c>
-      <c r="H848" t="s">
+      <c r="H849" t="s">
         <v>3628</v>
       </c>
-      <c r="I848" t="s">
+      <c r="I849" t="s">
         <v>3629</v>
       </c>
-      <c r="J848" t="s">
+      <c r="J849" t="s">
         <v>3630</v>
       </c>
     </row>
-    <row r="849" spans="3:10" ht="15.75" customHeight="1">
-      <c r="C849" t="s">
+    <row r="850" spans="2:10" ht="15.75" customHeight="1">
+      <c r="C850" t="s">
         <v>3650</v>
       </c>
-      <c r="D849">
+      <c r="D850">
         <v>1308</v>
       </c>
-      <c r="E849">
+      <c r="E850">
         <v>1355</v>
       </c>
-      <c r="H849" s="137" t="s">
+      <c r="H850" s="137" t="s">
         <v>3651</v>
       </c>
-      <c r="I849" t="s">
+      <c r="I850" t="s">
         <v>3652</v>
       </c>
-      <c r="J849" t="s">
+      <c r="J850" t="s">
         <v>3653</v>
       </c>
     </row>
-    <row r="850" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="851" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="852" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="853" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="854" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="855" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="856" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="857" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="858" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="859" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="860" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="861" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="862" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="863" spans="3:10" ht="15.75" customHeight="1"/>
-    <row r="864" spans="3:10" ht="15.75" customHeight="1"/>
+    <row r="851" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="852" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="853" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="854" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="855" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="856" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="857" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="858" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="859" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="860" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="861" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="862" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="863" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="864" spans="2:10" ht="15.75" customHeight="1"/>
     <row r="865" ht="15.75" customHeight="1"/>
     <row r="866" ht="15.75" customHeight="1"/>
     <row r="867" ht="15.75" customHeight="1"/>
@@ -49036,6 +49081,7 @@
     <row r="1427" ht="15.75" customHeight="1"/>
     <row r="1428" ht="15.75" customHeight="1"/>
     <row r="1429" ht="15.75" customHeight="1"/>
+    <row r="1430" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -49080,7 +49126,7 @@
     <hyperlink ref="I93" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
     <hyperlink ref="I95" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
     <hyperlink ref="I98" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="I840" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I841" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
     <hyperlink ref="I107" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
     <hyperlink ref="I109" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
     <hyperlink ref="I111" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
@@ -49106,7 +49152,7 @@
     <hyperlink ref="I164" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
     <hyperlink ref="I166" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
     <hyperlink ref="I169" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="I841" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="I842" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="I179" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
     <hyperlink ref="I174" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
     <hyperlink ref="I175" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
@@ -49114,7 +49160,7 @@
     <hyperlink ref="I182" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="I183" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
     <hyperlink ref="I185" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="I842" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="I843" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
     <hyperlink ref="I189" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
     <hyperlink ref="I190" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="I197" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
@@ -49230,7 +49276,7 @@
     <hyperlink ref="I520" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
     <hyperlink ref="I522" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
     <hyperlink ref="I523" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="I844" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="I845" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
     <hyperlink ref="I532" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
     <hyperlink ref="I542" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
     <hyperlink ref="I545" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
@@ -49240,7 +49286,7 @@
     <hyperlink ref="I573" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
     <hyperlink ref="I576" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
     <hyperlink ref="I578" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="I845" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="I846" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="I579" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
     <hyperlink ref="I582" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
     <hyperlink ref="I584" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
@@ -49288,46 +49334,46 @@
     <hyperlink ref="I712" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
     <hyperlink ref="I713" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
     <hyperlink ref="I715" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="I717" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="I722" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="I723" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="I726" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="I725" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="I727" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="I729" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="I731" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="I733" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="I738" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="I741" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="I743" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="I744" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="I746" r:id="rId264" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="I747" r:id="rId265" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="I749" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="I753" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="I755" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="I756" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="I757" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="I766" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="I777" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="I778" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="I779" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="I783" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="I791" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="I797" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="I800" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="I802" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="I807" r:id="rId280" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="I808" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="I811" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="I814" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="I816" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="I817" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="I818" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="I819" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="I825" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="I827" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="I837" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="I718" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I723" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="I724" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="I727" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="I726" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="I728" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I730" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="I732" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="I734" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="I739" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="I742" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I744" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="I745" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="I747" r:id="rId264" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="I748" r:id="rId265" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="I750" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I754" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="I756" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="I757" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="I758" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="I767" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I778" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="I779" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="I780" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="I784" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="I792" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I798" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="I801" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="I803" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="I808" r:id="rId280" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="I809" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I812" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="I815" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="I817" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="I818" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="I819" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I820" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="I826" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="I828" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="I838" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
     <hyperlink ref="I55" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
     <hyperlink ref="I123" r:id="rId292" xr:uid="{5EA5D994-B333-3843-BE27-18F6E6A203CB}"/>
     <hyperlink ref="I140" r:id="rId293" xr:uid="{3CFC94A3-CB56-CF41-A2D6-CFF12F2063F3}"/>
@@ -49341,9 +49387,9 @@
     <hyperlink ref="I587" r:id="rId301" xr:uid="{E9236146-86EA-5941-8165-B45990D536C8}"/>
     <hyperlink ref="I607" r:id="rId302" xr:uid="{21AF71A0-4F59-B243-8034-479DB7E98663}"/>
     <hyperlink ref="I648" r:id="rId303" xr:uid="{843C9DA0-AB58-0D4B-888B-DD524FBA1AF3}"/>
-    <hyperlink ref="I799" r:id="rId304" xr:uid="{C2D13AA1-A69A-AB41-BC17-DF71B69F851F}"/>
-    <hyperlink ref="I815" r:id="rId305" xr:uid="{DC8DA59C-9728-B348-8CBF-E7C3590D3EBA}"/>
-    <hyperlink ref="I822" r:id="rId306" xr:uid="{F45E902F-8511-E24D-AE19-4FB322067B27}"/>
+    <hyperlink ref="I800" r:id="rId304" xr:uid="{C2D13AA1-A69A-AB41-BC17-DF71B69F851F}"/>
+    <hyperlink ref="I816" r:id="rId305" xr:uid="{DC8DA59C-9728-B348-8CBF-E7C3590D3EBA}"/>
+    <hyperlink ref="I823" r:id="rId306" xr:uid="{F45E902F-8511-E24D-AE19-4FB322067B27}"/>
     <hyperlink ref="I66" r:id="rId307" tooltip="https://d-nb.info/gnd/118137948" xr:uid="{8B780818-038B-1C41-BBC6-6D7B0A6D4217}"/>
     <hyperlink ref="I67" r:id="rId308" xr:uid="{B1B306E3-1895-F547-A084-F4AB46C52D26}"/>
     <hyperlink ref="I99" r:id="rId309" tooltip="https://d-nb.info/gnd/124541755" xr:uid="{9AFB9BDC-B838-F046-9A8D-B7CA012FBBA7}"/>
@@ -49377,7 +49423,7 @@
     <hyperlink ref="I411" r:id="rId337" tooltip="https://d-nb.info/gnd/1013724968" xr:uid="{9CA71087-373B-3644-AB95-F068ED442DBB}"/>
     <hyperlink ref="I44" r:id="rId338" tooltip="https://d-nb.info/gnd/130217212" xr:uid="{B52ED2AE-6707-5442-BD8B-8F91D250AD2C}"/>
     <hyperlink ref="I448" r:id="rId339" tooltip="https://d-nb.info/gnd/116852283" xr:uid="{6739103A-CC12-C045-8328-944E2A2FDD6A}"/>
-    <hyperlink ref="I846" r:id="rId340" tooltip="https://d-nb.info/gnd/118727508" xr:uid="{8D0DB2F2-2129-0A4E-AF77-804E97A8BD75}"/>
+    <hyperlink ref="I847" r:id="rId340" tooltip="https://d-nb.info/gnd/118727508" xr:uid="{8D0DB2F2-2129-0A4E-AF77-804E97A8BD75}"/>
     <hyperlink ref="I465" r:id="rId341" tooltip="https://d-nb.info/gnd/118728709" xr:uid="{D464BCE2-BA23-6E47-8ADD-17725D8A271B}"/>
     <hyperlink ref="I490" r:id="rId342" tooltip="https://d-nb.info/gnd/118782096" xr:uid="{D92657DA-62F1-7942-A077-D9C05553727B}"/>
     <hyperlink ref="I495" r:id="rId343" tooltip="https://d-nb.info/gnd/1021177091" xr:uid="{C562707F-4EFD-FF48-9904-3CBCC1C1890A}"/>
@@ -49386,9 +49432,9 @@
     <hyperlink ref="I662" r:id="rId346" tooltip="https://d-nb.info/gnd/129442577" xr:uid="{A7ECFEAF-1EA6-6A48-96DC-48082731A48C}"/>
     <hyperlink ref="I671" r:id="rId347" tooltip="https://d-nb.info/gnd/1033250007" xr:uid="{93F059DA-3D76-1D4C-973C-D0524CC0D9FE}"/>
     <hyperlink ref="I714" r:id="rId348" tooltip="https://d-nb.info/gnd/117246158" xr:uid="{AC9120AB-04B9-1943-A261-E8DC0316FCC3}"/>
-    <hyperlink ref="I721" r:id="rId349" tooltip="https://d-nb.info/gnd/1046079247" xr:uid="{22FCE3CF-4E07-EC43-AFDA-766191D8C1ED}"/>
-    <hyperlink ref="I763" r:id="rId350" tooltip="https://d-nb.info/gnd/124988474" xr:uid="{401D3009-0210-9848-9CCB-0E3F514B9049}"/>
-    <hyperlink ref="I793" r:id="rId351" tooltip="https://d-nb.info/gnd/1161676309" xr:uid="{B504558A-7E8A-6541-BD89-24216F1563A3}"/>
+    <hyperlink ref="I722" r:id="rId349" tooltip="https://d-nb.info/gnd/1046079247" xr:uid="{22FCE3CF-4E07-EC43-AFDA-766191D8C1ED}"/>
+    <hyperlink ref="I764" r:id="rId350" tooltip="https://d-nb.info/gnd/124988474" xr:uid="{401D3009-0210-9848-9CCB-0E3F514B9049}"/>
+    <hyperlink ref="I794" r:id="rId351" tooltip="https://d-nb.info/gnd/1161676309" xr:uid="{B504558A-7E8A-6541-BD89-24216F1563A3}"/>
     <hyperlink ref="I606" r:id="rId352" xr:uid="{221A4C73-7808-AC48-BF73-3828D29E4245}"/>
     <hyperlink ref="I37" r:id="rId353" xr:uid="{5DEF1CC6-62D4-F048-AC18-7C085AB5C8B9}"/>
     <hyperlink ref="I57" r:id="rId354" xr:uid="{DA33FA54-A209-634C-9E1B-0335CEA4F7F6}"/>
@@ -49412,15 +49458,15 @@
     <hyperlink ref="I685" r:id="rId372" tooltip="https://d-nb.info/gnd/117402834" xr:uid="{0AFC3676-B177-FA4F-8983-2B7F244845C0}"/>
     <hyperlink ref="I705" r:id="rId373" tooltip="https://d-nb.info/gnd/117212342" xr:uid="{226CBF97-A7F1-8E4B-BD6C-BEE791227401}"/>
     <hyperlink ref="I536" r:id="rId374" xr:uid="{BBDAC784-297D-3245-811C-589DA346DBEC}"/>
-    <hyperlink ref="I826" r:id="rId375" tooltip="https://d-nb.info/gnd/1268159913" xr:uid="{225F9276-F953-9145-BE3F-CD079A103304}"/>
+    <hyperlink ref="I827" r:id="rId375" tooltip="https://d-nb.info/gnd/1268159913" xr:uid="{225F9276-F953-9145-BE3F-CD079A103304}"/>
     <hyperlink ref="I114" r:id="rId376" tooltip="https://d-nb.info/gnd/138066736" xr:uid="{3F39F859-CDE5-F44C-AE26-F55F5599A0FD}"/>
     <hyperlink ref="I491" r:id="rId377" xr:uid="{F1200265-72D3-0A46-92DF-D711D50C61F1}"/>
     <hyperlink ref="I129" r:id="rId378" xr:uid="{FD0A9C6F-5343-874B-8E05-4B8C06EDAC44}"/>
-    <hyperlink ref="I750" r:id="rId379" xr:uid="{DCED84D7-DAA6-D74C-A942-42BB2D5BFB9A}"/>
+    <hyperlink ref="I751" r:id="rId379" xr:uid="{DCED84D7-DAA6-D74C-A942-42BB2D5BFB9A}"/>
     <hyperlink ref="I496" r:id="rId380" xr:uid="{48DB6153-031C-8D4A-97E3-3158C0B3A541}"/>
     <hyperlink ref="I702" r:id="rId381" tooltip="https://d-nb.info/gnd/117479373" xr:uid="{FA44FC51-97AC-9B45-9DAA-11A2FDA297F2}"/>
-    <hyperlink ref="I792" r:id="rId382" tooltip="https://d-nb.info/gnd/1374712183" xr:uid="{6FD7FD2E-3E04-704E-943B-2E2CF0FC468E}"/>
-    <hyperlink ref="I835" r:id="rId383" xr:uid="{ED669D91-28C2-844B-A050-2C7F1FF142E6}"/>
+    <hyperlink ref="I793" r:id="rId382" tooltip="https://d-nb.info/gnd/1374712183" xr:uid="{6FD7FD2E-3E04-704E-943B-2E2CF0FC468E}"/>
+    <hyperlink ref="I836" r:id="rId383" xr:uid="{ED669D91-28C2-844B-A050-2C7F1FF142E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/xlsx/Baernreither_Personenregister_2024.xlsx
+++ b/data/xlsx/Baernreither_Personenregister_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3134D66-6A96-C844-9C4D-71C29629935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394708F8-D084-5943-B44B-486318B651EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35472,7 +35472,7 @@
       <c r="H506" s="97" t="s">
         <v>1863</v>
       </c>
-      <c r="I506" s="27" t="s">
+      <c r="I506" s="220" t="s">
         <v>1864</v>
       </c>
       <c r="J506" s="155" t="s">
@@ -49467,11 +49467,12 @@
     <hyperlink ref="I702" r:id="rId381" tooltip="https://d-nb.info/gnd/117479373" xr:uid="{FA44FC51-97AC-9B45-9DAA-11A2FDA297F2}"/>
     <hyperlink ref="I793" r:id="rId382" tooltip="https://d-nb.info/gnd/1374712183" xr:uid="{6FD7FD2E-3E04-704E-943B-2E2CF0FC468E}"/>
     <hyperlink ref="I836" r:id="rId383" xr:uid="{ED669D91-28C2-844B-A050-2C7F1FF142E6}"/>
+    <hyperlink ref="I506" r:id="rId384" xr:uid="{436C7ED2-BAE5-8C44-8911-BEF69A083F24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId384"/>
+    <tablePart r:id="rId385"/>
   </tableParts>
 </worksheet>
 </file>